--- a/seo-notes.xlsx
+++ b/seo-notes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\seo-notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766D9167-8F4E-4597-A302-388A81EE9F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F874BEA-7140-4E9C-87A9-74CD17A9A560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="478" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="478" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="نقشه راه" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="2-هاست" sheetId="2" r:id="rId3"/>
     <sheet name="3-سایت" sheetId="4" r:id="rId4"/>
     <sheet name="4-شناسایی کلمات" sheetId="6" r:id="rId5"/>
-    <sheet name="5-ساختار سایت" sheetId="7" r:id="rId6"/>
+    <sheet name="5-قبل از تولید محتوا" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="606">
   <si>
     <t>عدم سوء سابقه</t>
   </si>
@@ -2419,6 +2419,141 @@
   </si>
   <si>
     <t>تعریف صحیح تر: لندینگ پیج یک صفحه هدفمند برای گرفتن واکنش فوری از کاربر است؛ مثل پر کردن فرم، خرید محصول یا کلیک روی یک دکمه. اما مقاله برای آموزش، اطلاع‌رسانی یا افزایش ترافیک سایت از طریق سئو نوشته می‌شود، نه الزاماً برای اقدام فوری. در واقع لندینگ پیج فروشنده‌ای مستقیم و بی‌پرده است، در حالی که مقاله مشاوری صبور و آموزنده است</t>
+  </si>
+  <si>
+    <t>تولید محتوا: 1-ساختار سایت 2- تفکیک کلمات 3-پلن تولید محتوا</t>
+  </si>
+  <si>
+    <t>بخش 1- ساختار سایت</t>
+  </si>
+  <si>
+    <t>بخش 2- تفکیک کلمات</t>
+  </si>
+  <si>
+    <t>قصد کاربر(intent)</t>
+  </si>
+  <si>
+    <t>مهمترین کار در تفکیک کلمات کلیدی شناسایی و درک کردن قصد کاربر از جستجو میباشد. یعنی قصد کاربر از جستجو کردن این کلمه چیه؟ مثال: وقتی "پیتزا" را سرچ میکنیم قصدمون سفارش پیتزا، رسپی پیتزا، عکس پیتزا، تاریخچه پیتزا ، کدوم میباشد؟ گوگل براساس اینکه عموم یا اکثریت مردم با جستجو کردن کلمه "پیتزا" کدام قصد را دارند سرپ خود را میچیند!!!</t>
+  </si>
+  <si>
+    <t>** حالا ما میتوانیم با شناسایی قصد کاربر یک مرحله از گوگل جلوتر باشیم و همان نوع صفحه ای که کاربر میخواهد را در اختیار آن قرار داده باشیم! چطوری؟ حوزه کلمه مورد سرچ مخاطب را بشناسیم</t>
+  </si>
+  <si>
+    <t>انواع قصد کاربر</t>
+  </si>
+  <si>
+    <t>1-Informational</t>
+  </si>
+  <si>
+    <t>2-Navigational</t>
+  </si>
+  <si>
+    <t>3-Commercial</t>
+  </si>
+  <si>
+    <t>4-Transactional</t>
+  </si>
+  <si>
+    <t>کاربر به دنبال پاسخی برای سوالات یا اطلاعات عمومی میباشد. مثلا: چگونه گیتار بزنم؟</t>
+  </si>
+  <si>
+    <t>کاربر به دنبال خرید چیزی میباشد. مثلا: خرید آیفون 13</t>
+  </si>
+  <si>
+    <t>کاربر به دنبال پیداکردن وبسایت موردنظر خود میباشد. مثلا: کفش مردانه کفش ملی - بهترین سایت آموزس سئو - بهترین دکتر زنان سعادت آباد -</t>
+  </si>
+  <si>
+    <t>کاربر به دنبال اطلاعاتی در مورد محصولات، خدمات یا یک برند میباشد. مثلا: بهترین گوشیهای زیر 10 میلیون یا بهترین کفش های گلف زیر 200 دلار - یا استفاده از کلمات رایج فارسی مثل "ارزان" یا "اقتصادی"</t>
+  </si>
+  <si>
+    <t>⚠ نتیجه</t>
+  </si>
+  <si>
+    <t>با استفاده از مواردی که تا الان آموختیم تفکیک کلمات به دو قسمت صورت میگیرد:</t>
+  </si>
+  <si>
+    <t>1- کلمات فروشگاهی یا محصول</t>
+  </si>
+  <si>
+    <t>2- کلمات بلاگی یا راهنما</t>
+  </si>
+  <si>
+    <t>در بخش 2 مثلا در صفحه "بهترین سایت های آموزش سئو" میتوانیم صفحه فروش سایت خودمان را بعنوان یکی از موارد قرار دهیم!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">در بخش 2 و 3 هردو از عباراتی مثل "بهترین…" استفاده شده پس فرق آنها چیه؟ کاربران در مورد 2 با قصد کسب اطلاعات و شناسایی جستجو میکنند ولی در مورد 3 با دید خرید سرچ میکنند </t>
+  </si>
+  <si>
+    <t>محل بکارگیری</t>
+  </si>
+  <si>
+    <t>صفحات CLP, PLP, PDP</t>
+  </si>
+  <si>
+    <t>صفحات PLP, PDP</t>
+  </si>
+  <si>
+    <t>عنوان های داخلی PDP</t>
+  </si>
+  <si>
+    <t>متن و عکس PLP, PDP</t>
+  </si>
+  <si>
+    <t>ویدیو و صوت PDP</t>
+  </si>
+  <si>
+    <t>نوع کلمه</t>
+  </si>
+  <si>
+    <t>کلمه مرکزی : لوازم خانگی بعنوان (CLP)  ==&gt;  "اتو" / "لباسشویی" / "تلویزیون": بعنوان (PLP) یا با عبارت "خرید …" همراه شود و به گروه transactional تبدیل شود ---- مثال 2: خود کلمه مرکزی "آموزش فتوشاپ" خود بر روی یک مجصول یا لندیگ پیج اختصاصی تارگت شود بعنوان PDP. نکته: همه ی کلمات نامبرده کلمه کلیدی مرکزی میباشند!!!</t>
+  </si>
+  <si>
+    <t>کلمه دم دراز: لوازم خانگی بوش / لوازم خانگی فیلیپس بعنوان PLP, PDP ---- مثال 2: جارو برقی بوش بعنوان PDP ==&gt; جارو برقی بوش بدون کیسه / جارو برقی بوش کوچک / جاربرقی بوش شارژی / جارو برقی بوش آلمانی برای عنوان خود PDP و عنوانهای داخلی آن PDP درصورتیکه آن قابلیت را دارا باشد. دیگر برای هریک از دم درازها صفحه نمیزنیم پس. ----- مثال 3: از جارو برقی بوش آلمان در متن و عکس PDP استفاده کنیم و همچنین در متن و عکس PLP ها مثلا در کنسول ps4 هم نسخه fat هم نسخه slim وحود دارد حالا در صفحه دسته بندی ان میتوان هم از نسخه fat هم از نسخه slim صحبت کرد و از هردو عکس گذاشت و مقایسه کرد!!!</t>
+  </si>
+  <si>
+    <t>برای هر کلمه دم دراز و هر کلمه هم خانواده نباید صفحه محصول جدا ایجاد کرد برای اینکه بفهمیم:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- از مدل فعلی گوگل که سرپ را تنظیم کرده است </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- از قصد مخاطب (intent) </t>
+  </si>
+  <si>
+    <t>⚠ چگونگی تشخیص ایجاد صفحه مجزا برای هر کلمه</t>
+  </si>
+  <si>
+    <t>کلمه هم خانواده: مثلا در جاروبرقی رباتیک کلمه هم خانواده آن یعنی نظافت خودکار منزل را در عنوان داخلی PDP و هم در متن و عکس PLP, PDP استفاده کرد ----- مثال 2: نکته:::: استفاده از کلمات هم خانواده در ویدیو و صوت PDP: زیرا کلمات هم خانواده معموالا سرچ بالایی ندارند و همچنین اگر ویدیو ه بخواهند بروند تک صفحه شوند به سختی رتبه میگیرند و با بکار بردن این ویدیو ها در صفحات PDP به وسیله ی اسکیماها میتوان هم در ویدیو های رتبه گرفت و هم در سرپ وب!!!!</t>
+  </si>
+  <si>
+    <t>اگر قصد کاربر در اون حوزه یا حتی بسیار دقیق تر در اون کلمه تشخیص بدیم آنگاه گوگل شیفته ما میشود مثلا "کرم پودر": صفحه PLP "کرم پودر مک": صفحه PDP (زیرا فقط یک محصول دارد) اما "کرم پودر مک اصل": صفحه بلاگ که به نحوه تشخیص اصل و فیک میپردازد و پاره ای از توضیحات را ارائه میدهد اما این شناخت از بررسی رفتار و قصد کاربر بدست آمده و باید اشراف نسبتا خوبی روی حوزه داشت.</t>
+  </si>
+  <si>
+    <t>1-کلمات فروشگاهی یا محصول</t>
+  </si>
+  <si>
+    <t>صفحه مادر یا PP</t>
+  </si>
+  <si>
+    <t>صفحات TC, SC</t>
+  </si>
+  <si>
+    <t>عنوان های داخلی PP, TC, SC</t>
+  </si>
+  <si>
+    <t>متن و عکس  PP, TC, SC</t>
+  </si>
+  <si>
+    <t>ویدیو و صوت PP, TC, SC</t>
+  </si>
+  <si>
+    <t>2-کلمات بلاگی یا راهنما</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کلمات دم دراز در صورتی که سرچ قابل توجهی (در حد کلمه مرکزی خود) داشته باشند خودشان میتوانند صفحه مادر بشوند و یک راه اینکه تشخیص بدیم باید صفحه جدا داشته باشد یا خیر این است که باید خوب قصد کاربر (intent) را درک کنیم و راه دیگر ببینیم دیگر نتایج برتر گوگل برای آن صفحه جدا زدند یا خیر --- یعنی اگر کلمه دم دراز قابلیت مجزا صفحه شدن نداشت به داخل عنوان ها داخلی و متن وعکس سه نوع صفحه قرار میگیرند </t>
+  </si>
+  <si>
+    <t>بخش 3- پلن تولید محتوا</t>
   </si>
 </sst>
 </file>
@@ -2728,7 +2863,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2924,6 +3059,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3457,7 +3616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3783,55 +3942,105 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="2"/>
@@ -3842,11 +4051,26 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
@@ -3872,14 +4096,11 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
@@ -3890,60 +4111,57 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="2"/>
@@ -4032,59 +4250,38 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment readingOrder="2"/>
@@ -4092,8 +4289,8 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="2"/>
@@ -4107,11 +4304,44 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="2"/>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15708,13 +15938,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>326048</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>197827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>32971</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>80597</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -15744,13 +15974,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>552451</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>314326</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15814,13 +16044,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15908,13 +16138,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15985,13 +16215,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16079,13 +16309,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16156,13 +16386,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16250,13 +16480,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16327,13 +16557,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16404,13 +16634,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16481,13 +16711,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -16558,13 +16788,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>3175</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>193675</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16613,13 +16843,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>441325</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>3175</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16668,13 +16898,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>250825</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>441325</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16723,13 +16953,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>193675</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>250825</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16778,13 +17008,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>200026</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16831,13 +17061,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195264</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16884,13 +17114,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16937,13 +17167,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -16990,13 +17220,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>195263</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17043,13 +17273,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17096,13 +17326,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17149,13 +17379,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17202,13 +17432,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17255,13 +17485,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17308,13 +17538,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17361,13 +17591,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17416,13 +17646,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>447676</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>200026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>419101</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>238126</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17471,13 +17701,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>433388</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -17846,11 +18076,11 @@
   </cols>
   <sheetData>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="171" t="s">
+      <c r="A22" s="192" t="s">
         <v>335</v>
       </c>
-      <c r="B22" s="171"/>
-      <c r="C22" s="171"/>
+      <c r="B22" s="192"/>
+      <c r="C22" s="192"/>
       <c r="D22" s="82"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
@@ -17860,37 +18090,37 @@
       <c r="A23" s="82"/>
       <c r="B23" s="82"/>
       <c r="C23" s="82"/>
-      <c r="D23" s="172" t="s">
+      <c r="D23" s="193" t="s">
         <v>336</v>
       </c>
-      <c r="E23" s="172"/>
-      <c r="F23" s="172"/>
-      <c r="G23" s="172"/>
-      <c r="H23" s="172"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="193"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="82"/>
       <c r="B24" s="82"/>
       <c r="C24" s="82"/>
-      <c r="D24" s="172" t="s">
+      <c r="D24" s="193" t="s">
         <v>337</v>
       </c>
-      <c r="E24" s="172"/>
-      <c r="F24" s="172"/>
-      <c r="G24" s="172"/>
-      <c r="H24" s="172"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="193"/>
+      <c r="G24" s="193"/>
+      <c r="H24" s="193"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="82"/>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
-      <c r="D25" s="172" t="s">
+      <c r="D25" s="193" t="s">
         <v>338</v>
       </c>
-      <c r="E25" s="172"/>
-      <c r="F25" s="172"/>
-      <c r="G25" s="172"/>
-      <c r="H25" s="172"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -18211,11 +18441,11 @@
       <c r="B24" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="182" t="s">
+      <c r="C24" s="203" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="182"/>
-      <c r="E24" s="182"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
     </row>
     <row r="25" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A25" s="4">
@@ -18224,11 +18454,11 @@
       <c r="B25" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="183" t="s">
+      <c r="C25" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="183"/>
-      <c r="E25" s="183"/>
+      <c r="D25" s="204"/>
+      <c r="E25" s="204"/>
     </row>
     <row r="26" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A26" s="4">
@@ -18237,11 +18467,11 @@
       <c r="B26" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="183" t="s">
+      <c r="C26" s="204" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="183"/>
-      <c r="E26" s="183"/>
+      <c r="D26" s="204"/>
+      <c r="E26" s="204"/>
     </row>
     <row r="27" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A27" s="4">
@@ -18250,11 +18480,11 @@
       <c r="B27" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="183" t="s">
+      <c r="C27" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="183"/>
-      <c r="E27" s="183"/>
+      <c r="D27" s="204"/>
+      <c r="E27" s="204"/>
     </row>
     <row r="28" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A28" s="4">
@@ -18263,11 +18493,11 @@
       <c r="B28" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="183"/>
-      <c r="E28" s="183"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="204"/>
     </row>
     <row r="29" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A29" s="4">
@@ -18276,11 +18506,11 @@
       <c r="B29" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="183" t="s">
+      <c r="C29" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="183"/>
-      <c r="E29" s="183"/>
+      <c r="D29" s="204"/>
+      <c r="E29" s="204"/>
     </row>
     <row r="30" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A30" s="4">
@@ -18289,11 +18519,11 @@
       <c r="B30" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="183"/>
-      <c r="E30" s="183"/>
+      <c r="D30" s="204"/>
+      <c r="E30" s="204"/>
     </row>
     <row r="31" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A31" s="4">
@@ -18302,11 +18532,11 @@
       <c r="B31" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="183" t="s">
+      <c r="C31" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="183"/>
-      <c r="E31" s="183"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="204"/>
     </row>
     <row r="32" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A32" s="4">
@@ -18315,11 +18545,11 @@
       <c r="B32" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="204" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="183"/>
-      <c r="E32" s="183"/>
+      <c r="D32" s="204"/>
+      <c r="E32" s="204"/>
     </row>
     <row r="33" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A33" s="4">
@@ -18328,11 +18558,11 @@
       <c r="B33" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="183" t="s">
+      <c r="C33" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
+      <c r="D33" s="204"/>
+      <c r="E33" s="204"/>
     </row>
     <row r="34" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A34" s="4">
@@ -18341,11 +18571,11 @@
       <c r="B34" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="183"/>
-      <c r="E34" s="183"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
     </row>
     <row r="35" spans="1:5" ht="22.5" x14ac:dyDescent="0.6">
       <c r="A35" s="4">
@@ -18354,11 +18584,11 @@
       <c r="B35" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="183" t="s">
+      <c r="C35" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="183"/>
-      <c r="E35" s="183"/>
+      <c r="D35" s="204"/>
+      <c r="E35" s="204"/>
     </row>
     <row r="36" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.65">
       <c r="B36" s="40"/>
@@ -18370,32 +18600,32 @@
       <c r="A37" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="173" t="s">
+      <c r="B37" s="194" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="174"/>
-      <c r="D37" s="174"/>
-      <c r="E37" s="175"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="195"/>
+      <c r="E37" s="196"/>
     </row>
     <row r="38" spans="1:5" customFormat="1" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
       <c r="A38" s="2"/>
-      <c r="B38" s="176"/>
-      <c r="C38" s="177"/>
-      <c r="D38" s="177"/>
-      <c r="E38" s="178"/>
+      <c r="B38" s="197"/>
+      <c r="C38" s="198"/>
+      <c r="D38" s="198"/>
+      <c r="E38" s="199"/>
     </row>
     <row r="39" spans="1:5" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A39" s="2"/>
-      <c r="B39" s="176"/>
-      <c r="C39" s="177"/>
-      <c r="D39" s="177"/>
-      <c r="E39" s="178"/>
+      <c r="B39" s="197"/>
+      <c r="C39" s="198"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="199"/>
     </row>
     <row r="40" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B40" s="179"/>
-      <c r="C40" s="180"/>
-      <c r="D40" s="180"/>
-      <c r="E40" s="181"/>
+      <c r="B40" s="200"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="202"/>
     </row>
     <row r="41" spans="1:5" ht="21.75" thickTop="1" x14ac:dyDescent="0.6">
       <c r="B41" s="40"/>
@@ -18746,11 +18976,11 @@
       <c r="B24" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="185" t="s">
+      <c r="C24" s="206" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="185"/>
-      <c r="E24" s="185"/>
+      <c r="D24" s="206"/>
+      <c r="E24" s="206"/>
     </row>
     <row r="25" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
@@ -18759,11 +18989,11 @@
       <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="184" t="s">
+      <c r="C25" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="184"/>
-      <c r="E25" s="184"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="205"/>
     </row>
     <row r="26" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
@@ -18772,11 +19002,11 @@
       <c r="B26" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="184" t="s">
+      <c r="C26" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
+      <c r="D26" s="205"/>
+      <c r="E26" s="205"/>
     </row>
     <row r="27" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
@@ -18785,11 +19015,11 @@
       <c r="B27" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="184" t="s">
+      <c r="C27" s="205" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="205"/>
     </row>
     <row r="28" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
@@ -18798,11 +19028,11 @@
       <c r="B28" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="207" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="187"/>
-      <c r="E28" s="188"/>
+      <c r="D28" s="208"/>
+      <c r="E28" s="209"/>
     </row>
     <row r="29" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
@@ -18811,11 +19041,11 @@
       <c r="B29" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="184" t="s">
+      <c r="C29" s="205" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
+      <c r="D29" s="205"/>
+      <c r="E29" s="205"/>
     </row>
     <row r="30" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
@@ -18824,11 +19054,11 @@
       <c r="B30" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="205" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
+      <c r="D30" s="205"/>
+      <c r="E30" s="205"/>
     </row>
     <row r="31" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
@@ -18837,11 +19067,11 @@
       <c r="B31" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="205" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="184"/>
-      <c r="E31" s="184"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="205"/>
     </row>
     <row r="32" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
@@ -18850,11 +19080,11 @@
       <c r="B32" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="184" t="s">
+      <c r="C32" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
+      <c r="D32" s="205"/>
+      <c r="E32" s="205"/>
     </row>
     <row r="33" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
@@ -18863,11 +19093,11 @@
       <c r="B33" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="184" t="s">
+      <c r="C33" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="184"/>
-      <c r="E33" s="184"/>
+      <c r="D33" s="205"/>
+      <c r="E33" s="205"/>
     </row>
     <row r="34" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
@@ -18876,11 +19106,11 @@
       <c r="B34" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="184" t="s">
+      <c r="C34" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
+      <c r="D34" s="205"/>
+      <c r="E34" s="205"/>
     </row>
     <row r="35" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
@@ -18889,11 +19119,11 @@
       <c r="B35" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="184" t="s">
+      <c r="C35" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
+      <c r="D35" s="205"/>
+      <c r="E35" s="205"/>
     </row>
     <row r="36" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
@@ -18902,11 +19132,11 @@
       <c r="B36" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="184" t="s">
+      <c r="C36" s="205" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
+      <c r="D36" s="205"/>
+      <c r="E36" s="205"/>
     </row>
     <row r="37" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
@@ -18915,11 +19145,11 @@
       <c r="B37" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="184" t="s">
+      <c r="C37" s="205" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
+      <c r="D37" s="205"/>
+      <c r="E37" s="205"/>
     </row>
     <row r="38" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
@@ -18928,11 +19158,11 @@
       <c r="B38" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="184" t="s">
+      <c r="C38" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -19185,28 +19415,28 @@
       <c r="A19" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="189" t="s">
+      <c r="B19" s="210" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="190"/>
-      <c r="D19" s="190"/>
-      <c r="E19" s="191"/>
+      <c r="C19" s="211"/>
+      <c r="D19" s="211"/>
+      <c r="E19" s="212"/>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
       <c r="A20" s="2"/>
-      <c r="B20" s="192"/>
-      <c r="C20" s="193"/>
-      <c r="D20" s="193"/>
-      <c r="E20" s="194"/>
+      <c r="B20" s="213"/>
+      <c r="C20" s="214"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="215"/>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A21" s="2"/>
-      <c r="B21" s="195"/>
-      <c r="C21" s="196"/>
-      <c r="D21" s="196"/>
-      <c r="E21" s="197"/>
+      <c r="B21" s="216"/>
+      <c r="C21" s="217"/>
+      <c r="D21" s="217"/>
+      <c r="E21" s="218"/>
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
@@ -19383,38 +19613,38 @@
       <c r="B35" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="198" t="s">
+      <c r="C35" s="219" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
+      <c r="D35" s="219"/>
+      <c r="E35" s="219"/>
     </row>
     <row r="36" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>1</v>
       </c>
       <c r="B36" s="62"/>
-      <c r="C36" s="199"/>
-      <c r="D36" s="199"/>
-      <c r="E36" s="199"/>
+      <c r="C36" s="220"/>
+      <c r="D36" s="220"/>
+      <c r="E36" s="220"/>
     </row>
     <row r="37" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>2</v>
       </c>
       <c r="B37" s="62"/>
-      <c r="C37" s="199"/>
-      <c r="D37" s="199"/>
-      <c r="E37" s="199"/>
+      <c r="C37" s="220"/>
+      <c r="D37" s="220"/>
+      <c r="E37" s="220"/>
     </row>
     <row r="38" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>3</v>
       </c>
       <c r="B38" s="62"/>
-      <c r="C38" s="199"/>
-      <c r="D38" s="199"/>
-      <c r="E38" s="199"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -19453,69 +19683,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="221" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
     </row>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="205"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="205"/>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="205"/>
-      <c r="M2" s="205"/>
+      <c r="A2" s="221"/>
+      <c r="B2" s="221"/>
+      <c r="C2" s="221"/>
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="221"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
     </row>
     <row r="3" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="4" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="201" t="s">
+      <c r="B4" s="245" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="224" t="s">
+      <c r="C4" s="238" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
+      <c r="D4" s="238"/>
+      <c r="E4" s="238"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
+      <c r="H4" s="238"/>
+      <c r="I4" s="238"/>
+      <c r="J4" s="238"/>
+      <c r="K4" s="238"/>
+      <c r="L4" s="238"/>
+      <c r="M4" s="238"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B5" s="143"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="224"/>
-      <c r="L5" s="224"/>
-      <c r="M5" s="224"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="238"/>
+      <c r="D5" s="238"/>
+      <c r="E5" s="238"/>
+      <c r="F5" s="238"/>
+      <c r="G5" s="238"/>
+      <c r="H5" s="238"/>
+      <c r="I5" s="238"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="238"/>
+      <c r="L5" s="238"/>
+      <c r="M5" s="238"/>
     </row>
     <row r="6" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C6" s="85"/>
@@ -19534,19 +19764,19 @@
       <c r="B7" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="143" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="115"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="143"/>
     </row>
     <row r="8" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.45">
       <c r="D8" s="18"/>
@@ -19583,169 +19813,169 @@
       <c r="B13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="212" t="s">
+      <c r="C13" s="125" t="s">
         <v>188</v>
       </c>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="125"/>
+      <c r="M13" s="125"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B14" s="97"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="212"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="212"/>
-      <c r="I14" s="212"/>
-      <c r="J14" s="212"/>
-      <c r="K14" s="212"/>
-      <c r="L14" s="212"/>
-      <c r="M14" s="212"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="125"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B15" s="97"/>
-      <c r="C15" s="216" t="s">
+      <c r="C15" s="231" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="216"/>
-      <c r="G15" s="216"/>
-      <c r="H15" s="216"/>
-      <c r="I15" s="216"/>
-      <c r="J15" s="216"/>
-      <c r="K15" s="216"/>
-      <c r="L15" s="216"/>
-      <c r="M15" s="216"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
+      <c r="F15" s="231"/>
+      <c r="G15" s="231"/>
+      <c r="H15" s="231"/>
+      <c r="I15" s="231"/>
+      <c r="J15" s="231"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="231"/>
+      <c r="M15" s="231"/>
     </row>
     <row r="16" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="202" t="s">
+      <c r="C16" s="234" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
-      <c r="F16" s="202"/>
-      <c r="G16" s="202"/>
-      <c r="H16" s="202"/>
-      <c r="I16" s="202"/>
-      <c r="J16" s="202"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="202"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="234"/>
+      <c r="G16" s="234"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="234"/>
+      <c r="J16" s="234"/>
+      <c r="K16" s="234"/>
+      <c r="L16" s="234"/>
+      <c r="M16" s="234"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" s="97"/>
-      <c r="C17" s="202"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="202"/>
-      <c r="F17" s="202"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="202"/>
+      <c r="C17" s="234"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
+      <c r="G17" s="234"/>
+      <c r="H17" s="234"/>
+      <c r="I17" s="234"/>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+      <c r="L17" s="234"/>
+      <c r="M17" s="234"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B18" s="97"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="202"/>
-      <c r="F18" s="202"/>
-      <c r="G18" s="202"/>
-      <c r="H18" s="202"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="202"/>
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="202"/>
+      <c r="C18" s="234"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="234"/>
+      <c r="J18" s="234"/>
+      <c r="K18" s="234"/>
+      <c r="L18" s="234"/>
+      <c r="M18" s="234"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="97"/>
-      <c r="C19" s="202" t="s">
+      <c r="C19" s="234" t="s">
         <v>195</v>
       </c>
-      <c r="D19" s="202"/>
-      <c r="E19" s="202"/>
-      <c r="F19" s="202"/>
-      <c r="G19" s="202"/>
-      <c r="H19" s="202"/>
-      <c r="I19" s="202"/>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="202"/>
+      <c r="D19" s="234"/>
+      <c r="E19" s="234"/>
+      <c r="F19" s="234"/>
+      <c r="G19" s="234"/>
+      <c r="H19" s="234"/>
+      <c r="I19" s="234"/>
+      <c r="J19" s="234"/>
+      <c r="K19" s="234"/>
+      <c r="L19" s="234"/>
+      <c r="M19" s="234"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="97"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="202"/>
-      <c r="F20" s="202"/>
-      <c r="G20" s="202"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="202"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="202"/>
+      <c r="C20" s="234"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="234"/>
+      <c r="K20" s="234"/>
+      <c r="L20" s="234"/>
+      <c r="M20" s="234"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="97"/>
-      <c r="C21" s="202" t="s">
+      <c r="C21" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="202"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="202"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="202"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="234"/>
+      <c r="J21" s="234"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="234"/>
+      <c r="M21" s="234"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="97"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="202"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="234"/>
+      <c r="G22" s="234"/>
+      <c r="H22" s="234"/>
+      <c r="I22" s="234"/>
+      <c r="J22" s="234"/>
+      <c r="K22" s="234"/>
+      <c r="L22" s="234"/>
+      <c r="M22" s="234"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="97"/>
-      <c r="C23" s="202"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="202"/>
-      <c r="G23" s="202"/>
-      <c r="H23" s="202"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="202"/>
+      <c r="C23" s="234"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
+      <c r="G23" s="234"/>
+      <c r="H23" s="234"/>
+      <c r="I23" s="234"/>
+      <c r="J23" s="234"/>
+      <c r="K23" s="234"/>
+      <c r="L23" s="234"/>
+      <c r="M23" s="234"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C24" s="21"/>
@@ -19793,83 +20023,83 @@
       <c r="B31" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="218" t="s">
+      <c r="C31" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="218"/>
-      <c r="E31" s="218"/>
-      <c r="F31" s="218"/>
-      <c r="G31" s="218"/>
-      <c r="H31" s="218"/>
-      <c r="I31" s="218"/>
-      <c r="J31" s="218"/>
-      <c r="K31" s="218"/>
-      <c r="L31" s="218"/>
-      <c r="M31" s="218"/>
+      <c r="D31" s="232"/>
+      <c r="E31" s="232"/>
+      <c r="F31" s="232"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="232"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
+      <c r="M31" s="232"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B32" s="98" t="s">
         <v>398</v>
       </c>
-      <c r="C32" s="223" t="s">
+      <c r="C32" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="223"/>
-      <c r="I32" s="223"/>
-      <c r="J32" s="223"/>
-      <c r="K32" s="223"/>
-      <c r="L32" s="223"/>
-      <c r="M32" s="223"/>
+      <c r="D32" s="237"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="237"/>
+      <c r="G32" s="237"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="237"/>
+      <c r="K32" s="237"/>
+      <c r="L32" s="237"/>
+      <c r="M32" s="237"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="97"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="223"/>
-      <c r="K33" s="223"/>
-      <c r="L33" s="223"/>
-      <c r="M33" s="223"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="237"/>
+      <c r="J33" s="237"/>
+      <c r="K33" s="237"/>
+      <c r="L33" s="237"/>
+      <c r="M33" s="237"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B34" s="97"/>
-      <c r="C34" s="217" t="s">
+      <c r="C34" s="228" t="s">
         <v>198</v>
       </c>
-      <c r="D34" s="217"/>
-      <c r="E34" s="217"/>
-      <c r="F34" s="217"/>
-      <c r="G34" s="217"/>
-      <c r="H34" s="217"/>
-      <c r="I34" s="217"/>
-      <c r="J34" s="217"/>
-      <c r="K34" s="217"/>
-      <c r="L34" s="217"/>
-      <c r="M34" s="217"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="228"/>
+      <c r="F34" s="228"/>
+      <c r="G34" s="228"/>
+      <c r="H34" s="228"/>
+      <c r="I34" s="228"/>
+      <c r="J34" s="228"/>
+      <c r="K34" s="228"/>
+      <c r="L34" s="228"/>
+      <c r="M34" s="228"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="97"/>
-      <c r="C35" s="217" t="s">
+      <c r="C35" s="228" t="s">
         <v>199</v>
       </c>
-      <c r="D35" s="217"/>
-      <c r="E35" s="217"/>
-      <c r="F35" s="217"/>
-      <c r="G35" s="217"/>
-      <c r="H35" s="217"/>
-      <c r="I35" s="217"/>
-      <c r="J35" s="217"/>
-      <c r="K35" s="217"/>
-      <c r="L35" s="217"/>
-      <c r="M35" s="217"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="228"/>
+      <c r="F35" s="228"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="228"/>
+      <c r="I35" s="228"/>
+      <c r="J35" s="228"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C36" s="24"/>
@@ -19917,97 +20147,97 @@
       <c r="B44" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C44" s="217" t="s">
+      <c r="C44" s="228" t="s">
         <v>209</v>
       </c>
-      <c r="D44" s="217"/>
-      <c r="E44" s="217"/>
-      <c r="F44" s="217"/>
-      <c r="G44" s="217"/>
-      <c r="H44" s="217"/>
-      <c r="I44" s="217"/>
-      <c r="J44" s="217"/>
-      <c r="K44" s="217"/>
-      <c r="L44" s="217"/>
-      <c r="M44" s="217"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="228"/>
+      <c r="F44" s="228"/>
+      <c r="G44" s="228"/>
+      <c r="H44" s="228"/>
+      <c r="I44" s="228"/>
+      <c r="J44" s="228"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="228"/>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B45" s="98" t="s">
         <v>399</v>
       </c>
-      <c r="C45" s="202" t="s">
+      <c r="C45" s="234" t="s">
         <v>400</v>
       </c>
-      <c r="D45" s="202"/>
-      <c r="E45" s="202"/>
-      <c r="F45" s="202"/>
-      <c r="G45" s="202"/>
-      <c r="H45" s="202"/>
-      <c r="I45" s="202"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="202"/>
-      <c r="L45" s="202"/>
-      <c r="M45" s="202"/>
+      <c r="D45" s="234"/>
+      <c r="E45" s="234"/>
+      <c r="F45" s="234"/>
+      <c r="G45" s="234"/>
+      <c r="H45" s="234"/>
+      <c r="I45" s="234"/>
+      <c r="J45" s="234"/>
+      <c r="K45" s="234"/>
+      <c r="L45" s="234"/>
+      <c r="M45" s="234"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B46" s="97"/>
-      <c r="C46" s="202"/>
-      <c r="D46" s="202"/>
-      <c r="E46" s="202"/>
-      <c r="F46" s="202"/>
-      <c r="G46" s="202"/>
-      <c r="H46" s="202"/>
-      <c r="I46" s="202"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="202"/>
-      <c r="L46" s="202"/>
-      <c r="M46" s="202"/>
+      <c r="C46" s="234"/>
+      <c r="D46" s="234"/>
+      <c r="E46" s="234"/>
+      <c r="F46" s="234"/>
+      <c r="G46" s="234"/>
+      <c r="H46" s="234"/>
+      <c r="I46" s="234"/>
+      <c r="J46" s="234"/>
+      <c r="K46" s="234"/>
+      <c r="L46" s="234"/>
+      <c r="M46" s="234"/>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B47" s="97"/>
-      <c r="C47" s="202" t="s">
+      <c r="C47" s="234" t="s">
         <v>210</v>
       </c>
-      <c r="D47" s="202"/>
-      <c r="E47" s="202"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="202"/>
-      <c r="H47" s="202"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="202"/>
-      <c r="L47" s="202"/>
-      <c r="M47" s="202"/>
+      <c r="D47" s="234"/>
+      <c r="E47" s="234"/>
+      <c r="F47" s="234"/>
+      <c r="G47" s="234"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="234"/>
+      <c r="J47" s="234"/>
+      <c r="K47" s="234"/>
+      <c r="L47" s="234"/>
+      <c r="M47" s="234"/>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B48" s="97"/>
-      <c r="C48" s="202" t="s">
+      <c r="C48" s="234" t="s">
         <v>401</v>
       </c>
-      <c r="D48" s="202"/>
-      <c r="E48" s="202"/>
-      <c r="F48" s="202"/>
-      <c r="G48" s="202"/>
-      <c r="H48" s="202"/>
-      <c r="I48" s="202"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="L48" s="202"/>
-      <c r="M48" s="202"/>
+      <c r="D48" s="234"/>
+      <c r="E48" s="234"/>
+      <c r="F48" s="234"/>
+      <c r="G48" s="234"/>
+      <c r="H48" s="234"/>
+      <c r="I48" s="234"/>
+      <c r="J48" s="234"/>
+      <c r="K48" s="234"/>
+      <c r="L48" s="234"/>
+      <c r="M48" s="234"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B49" s="97"/>
-      <c r="C49" s="202"/>
-      <c r="D49" s="202"/>
-      <c r="E49" s="202"/>
-      <c r="F49" s="202"/>
-      <c r="G49" s="202"/>
-      <c r="H49" s="202"/>
-      <c r="I49" s="202"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="202"/>
-      <c r="L49" s="202"/>
-      <c r="M49" s="202"/>
+      <c r="C49" s="234"/>
+      <c r="D49" s="234"/>
+      <c r="E49" s="234"/>
+      <c r="F49" s="234"/>
+      <c r="G49" s="234"/>
+      <c r="H49" s="234"/>
+      <c r="I49" s="234"/>
+      <c r="J49" s="234"/>
+      <c r="K49" s="234"/>
+      <c r="L49" s="234"/>
+      <c r="M49" s="234"/>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.45">
       <c r="D51" s="22" t="s">
@@ -20047,19 +20277,19 @@
       <c r="B58" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C58" s="138" t="s">
+      <c r="C58" s="161" t="s">
         <v>218</v>
       </c>
-      <c r="D58" s="138"/>
-      <c r="E58" s="138"/>
-      <c r="F58" s="138"/>
-      <c r="G58" s="138"/>
-      <c r="H58" s="138"/>
-      <c r="I58" s="138"/>
-      <c r="J58" s="138"/>
-      <c r="K58" s="138"/>
-      <c r="L58" s="138"/>
-      <c r="M58" s="138"/>
+      <c r="D58" s="161"/>
+      <c r="E58" s="161"/>
+      <c r="F58" s="161"/>
+      <c r="G58" s="161"/>
+      <c r="H58" s="161"/>
+      <c r="I58" s="161"/>
+      <c r="J58" s="161"/>
+      <c r="K58" s="161"/>
+      <c r="L58" s="161"/>
+      <c r="M58" s="161"/>
     </row>
     <row r="59" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="60" spans="2:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -20069,27 +20299,27 @@
       <c r="C60" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="D60" s="213" t="s">
+      <c r="D60" s="242" t="s">
         <v>402</v>
       </c>
-      <c r="E60" s="214"/>
-      <c r="F60" s="214"/>
-      <c r="G60" s="214"/>
-      <c r="H60" s="214"/>
-      <c r="I60" s="214"/>
-      <c r="J60" s="214"/>
-      <c r="K60" s="214"/>
-      <c r="L60" s="214"/>
-      <c r="M60" s="215"/>
+      <c r="E60" s="243"/>
+      <c r="F60" s="243"/>
+      <c r="G60" s="243"/>
+      <c r="H60" s="243"/>
+      <c r="I60" s="243"/>
+      <c r="J60" s="243"/>
+      <c r="K60" s="243"/>
+      <c r="L60" s="243"/>
+      <c r="M60" s="244"/>
     </row>
     <row r="61" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C61" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="221" t="s">
+      <c r="D61" s="235" t="s">
         <v>222</v>
       </c>
-      <c r="E61" s="222"/>
+      <c r="E61" s="236"/>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C62" s="26" t="s">
@@ -20107,45 +20337,45 @@
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="C66" s="202" t="s">
+      <c r="C66" s="234" t="s">
         <v>403</v>
       </c>
-      <c r="D66" s="202"/>
-      <c r="E66" s="202"/>
-      <c r="F66" s="202"/>
-      <c r="G66" s="202"/>
-      <c r="H66" s="202"/>
-      <c r="I66" s="202"/>
-      <c r="J66" s="202"/>
-      <c r="K66" s="202"/>
-      <c r="L66" s="202"/>
-      <c r="M66" s="202"/>
+      <c r="D66" s="234"/>
+      <c r="E66" s="234"/>
+      <c r="F66" s="234"/>
+      <c r="G66" s="234"/>
+      <c r="H66" s="234"/>
+      <c r="I66" s="234"/>
+      <c r="J66" s="234"/>
+      <c r="K66" s="234"/>
+      <c r="L66" s="234"/>
+      <c r="M66" s="234"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="C67" s="202"/>
-      <c r="D67" s="202"/>
-      <c r="E67" s="202"/>
-      <c r="F67" s="202"/>
-      <c r="G67" s="202"/>
-      <c r="H67" s="202"/>
-      <c r="I67" s="202"/>
-      <c r="J67" s="202"/>
-      <c r="K67" s="202"/>
-      <c r="L67" s="202"/>
-      <c r="M67" s="202"/>
+      <c r="C67" s="234"/>
+      <c r="D67" s="234"/>
+      <c r="E67" s="234"/>
+      <c r="F67" s="234"/>
+      <c r="G67" s="234"/>
+      <c r="H67" s="234"/>
+      <c r="I67" s="234"/>
+      <c r="J67" s="234"/>
+      <c r="K67" s="234"/>
+      <c r="L67" s="234"/>
+      <c r="M67" s="234"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="C68" s="202"/>
-      <c r="D68" s="202"/>
-      <c r="E68" s="202"/>
-      <c r="F68" s="202"/>
-      <c r="G68" s="202"/>
-      <c r="H68" s="202"/>
-      <c r="I68" s="202"/>
-      <c r="J68" s="202"/>
-      <c r="K68" s="202"/>
-      <c r="L68" s="202"/>
-      <c r="M68" s="202"/>
+      <c r="C68" s="234"/>
+      <c r="D68" s="234"/>
+      <c r="E68" s="234"/>
+      <c r="F68" s="234"/>
+      <c r="G68" s="234"/>
+      <c r="H68" s="234"/>
+      <c r="I68" s="234"/>
+      <c r="J68" s="234"/>
+      <c r="K68" s="234"/>
+      <c r="L68" s="234"/>
+      <c r="M68" s="234"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B69" s="66" t="s">
@@ -20164,36 +20394,36 @@
       <c r="M69" s="21"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A71" s="205" t="s">
+      <c r="A71" s="221" t="s">
         <v>270</v>
       </c>
-      <c r="B71" s="205"/>
-      <c r="C71" s="205"/>
-      <c r="D71" s="205"/>
-      <c r="E71" s="205"/>
-      <c r="F71" s="205"/>
-      <c r="G71" s="205"/>
-      <c r="H71" s="205"/>
-      <c r="I71" s="205"/>
-      <c r="J71" s="205"/>
-      <c r="K71" s="205"/>
-      <c r="L71" s="205"/>
-      <c r="M71" s="205"/>
+      <c r="B71" s="221"/>
+      <c r="C71" s="221"/>
+      <c r="D71" s="221"/>
+      <c r="E71" s="221"/>
+      <c r="F71" s="221"/>
+      <c r="G71" s="221"/>
+      <c r="H71" s="221"/>
+      <c r="I71" s="221"/>
+      <c r="J71" s="221"/>
+      <c r="K71" s="221"/>
+      <c r="L71" s="221"/>
+      <c r="M71" s="221"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A72" s="205"/>
-      <c r="B72" s="205"/>
-      <c r="C72" s="205"/>
-      <c r="D72" s="205"/>
-      <c r="E72" s="205"/>
-      <c r="F72" s="205"/>
-      <c r="G72" s="205"/>
-      <c r="H72" s="205"/>
-      <c r="I72" s="205"/>
-      <c r="J72" s="205"/>
-      <c r="K72" s="205"/>
-      <c r="L72" s="205"/>
-      <c r="M72" s="205"/>
+      <c r="A72" s="221"/>
+      <c r="B72" s="221"/>
+      <c r="C72" s="221"/>
+      <c r="D72" s="221"/>
+      <c r="E72" s="221"/>
+      <c r="F72" s="221"/>
+      <c r="G72" s="221"/>
+      <c r="H72" s="221"/>
+      <c r="I72" s="221"/>
+      <c r="J72" s="221"/>
+      <c r="K72" s="221"/>
+      <c r="L72" s="221"/>
+      <c r="M72" s="221"/>
     </row>
     <row r="74" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="24"/>
@@ -20283,19 +20513,19 @@
       <c r="B79" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C79" s="220" t="s">
+      <c r="C79" s="128" t="s">
         <v>265</v>
       </c>
-      <c r="D79" s="220"/>
-      <c r="E79" s="220"/>
-      <c r="F79" s="220"/>
-      <c r="G79" s="220"/>
-      <c r="H79" s="220"/>
-      <c r="I79" s="220"/>
-      <c r="J79" s="220"/>
-      <c r="K79" s="220"/>
-      <c r="L79" s="220"/>
-      <c r="M79" s="220"/>
+      <c r="D79" s="128"/>
+      <c r="E79" s="128"/>
+      <c r="F79" s="128"/>
+      <c r="G79" s="128"/>
+      <c r="H79" s="128"/>
+      <c r="I79" s="128"/>
+      <c r="J79" s="128"/>
+      <c r="K79" s="128"/>
+      <c r="L79" s="128"/>
+      <c r="M79" s="128"/>
     </row>
     <row r="80" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A80" s="24"/>
@@ -20558,10 +20788,10 @@
       <c r="B94" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="C94" s="211" t="s">
+      <c r="C94" s="224" t="s">
         <v>252</v>
       </c>
-      <c r="D94" s="211"/>
+      <c r="D94" s="224"/>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24"/>
@@ -20591,52 +20821,52 @@
       <c r="A96" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="B96" s="219" t="s">
+      <c r="B96" s="233" t="s">
         <v>269</v>
       </c>
-      <c r="C96" s="138" t="s">
+      <c r="C96" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="D96" s="138"/>
-      <c r="E96" s="138"/>
-      <c r="F96" s="138"/>
-      <c r="G96" s="138"/>
-      <c r="H96" s="138"/>
-      <c r="I96" s="138"/>
-      <c r="J96" s="138"/>
-      <c r="K96" s="138"/>
-      <c r="L96" s="138"/>
-      <c r="M96" s="138"/>
+      <c r="D96" s="161"/>
+      <c r="E96" s="161"/>
+      <c r="F96" s="161"/>
+      <c r="G96" s="161"/>
+      <c r="H96" s="161"/>
+      <c r="I96" s="161"/>
+      <c r="J96" s="161"/>
+      <c r="K96" s="161"/>
+      <c r="L96" s="161"/>
+      <c r="M96" s="161"/>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A97" s="24"/>
-      <c r="B97" s="219"/>
-      <c r="C97" s="138"/>
-      <c r="D97" s="138"/>
-      <c r="E97" s="138"/>
-      <c r="F97" s="138"/>
-      <c r="G97" s="138"/>
-      <c r="H97" s="138"/>
-      <c r="I97" s="138"/>
-      <c r="J97" s="138"/>
-      <c r="K97" s="138"/>
-      <c r="L97" s="138"/>
-      <c r="M97" s="138"/>
+      <c r="B97" s="233"/>
+      <c r="C97" s="161"/>
+      <c r="D97" s="161"/>
+      <c r="E97" s="161"/>
+      <c r="F97" s="161"/>
+      <c r="G97" s="161"/>
+      <c r="H97" s="161"/>
+      <c r="I97" s="161"/>
+      <c r="J97" s="161"/>
+      <c r="K97" s="161"/>
+      <c r="L97" s="161"/>
+      <c r="M97" s="161"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A98" s="24"/>
-      <c r="B98" s="219"/>
-      <c r="C98" s="138"/>
-      <c r="D98" s="138"/>
-      <c r="E98" s="138"/>
-      <c r="F98" s="138"/>
-      <c r="G98" s="138"/>
-      <c r="H98" s="138"/>
-      <c r="I98" s="138"/>
-      <c r="J98" s="138"/>
-      <c r="K98" s="138"/>
-      <c r="L98" s="138"/>
-      <c r="M98" s="138"/>
+      <c r="B98" s="233"/>
+      <c r="C98" s="161"/>
+      <c r="D98" s="161"/>
+      <c r="E98" s="161"/>
+      <c r="F98" s="161"/>
+      <c r="G98" s="161"/>
+      <c r="H98" s="161"/>
+      <c r="I98" s="161"/>
+      <c r="J98" s="161"/>
+      <c r="K98" s="161"/>
+      <c r="L98" s="161"/>
+      <c r="M98" s="161"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A99" s="24"/>
@@ -20784,36 +21014,36 @@
       <c r="M105" s="24"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A106" s="205" t="s">
+      <c r="A106" s="221" t="s">
         <v>271</v>
       </c>
-      <c r="B106" s="205"/>
-      <c r="C106" s="205"/>
-      <c r="D106" s="205"/>
-      <c r="E106" s="205"/>
-      <c r="F106" s="205"/>
-      <c r="G106" s="205"/>
-      <c r="H106" s="205"/>
-      <c r="I106" s="205"/>
-      <c r="J106" s="205"/>
-      <c r="K106" s="205"/>
-      <c r="L106" s="205"/>
-      <c r="M106" s="205"/>
+      <c r="B106" s="221"/>
+      <c r="C106" s="221"/>
+      <c r="D106" s="221"/>
+      <c r="E106" s="221"/>
+      <c r="F106" s="221"/>
+      <c r="G106" s="221"/>
+      <c r="H106" s="221"/>
+      <c r="I106" s="221"/>
+      <c r="J106" s="221"/>
+      <c r="K106" s="221"/>
+      <c r="L106" s="221"/>
+      <c r="M106" s="221"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A107" s="205"/>
-      <c r="B107" s="205"/>
-      <c r="C107" s="205"/>
-      <c r="D107" s="205"/>
-      <c r="E107" s="205"/>
-      <c r="F107" s="205"/>
-      <c r="G107" s="205"/>
-      <c r="H107" s="205"/>
-      <c r="I107" s="205"/>
-      <c r="J107" s="205"/>
-      <c r="K107" s="205"/>
-      <c r="L107" s="205"/>
-      <c r="M107" s="205"/>
+      <c r="A107" s="221"/>
+      <c r="B107" s="221"/>
+      <c r="C107" s="221"/>
+      <c r="D107" s="221"/>
+      <c r="E107" s="221"/>
+      <c r="F107" s="221"/>
+      <c r="G107" s="221"/>
+      <c r="H107" s="221"/>
+      <c r="I107" s="221"/>
+      <c r="J107" s="221"/>
+      <c r="K107" s="221"/>
+      <c r="L107" s="221"/>
+      <c r="M107" s="221"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A108" s="24"/>
@@ -20832,35 +21062,35 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A109" s="24"/>
-      <c r="B109" s="210" t="s">
+      <c r="B109" s="241" t="s">
         <v>273</v>
       </c>
-      <c r="C109" s="210"/>
-      <c r="D109" s="210"/>
-      <c r="E109" s="210"/>
-      <c r="F109" s="210"/>
-      <c r="G109" s="210"/>
-      <c r="H109" s="210"/>
-      <c r="I109" s="210"/>
-      <c r="J109" s="210"/>
-      <c r="K109" s="210"/>
-      <c r="L109" s="210"/>
-      <c r="M109" s="210"/>
+      <c r="C109" s="241"/>
+      <c r="D109" s="241"/>
+      <c r="E109" s="241"/>
+      <c r="F109" s="241"/>
+      <c r="G109" s="241"/>
+      <c r="H109" s="241"/>
+      <c r="I109" s="241"/>
+      <c r="J109" s="241"/>
+      <c r="K109" s="241"/>
+      <c r="L109" s="241"/>
+      <c r="M109" s="241"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A110" s="24"/>
-      <c r="B110" s="210"/>
-      <c r="C110" s="210"/>
-      <c r="D110" s="210"/>
-      <c r="E110" s="210"/>
-      <c r="F110" s="210"/>
-      <c r="G110" s="210"/>
-      <c r="H110" s="210"/>
-      <c r="I110" s="210"/>
-      <c r="J110" s="210"/>
-      <c r="K110" s="210"/>
-      <c r="L110" s="210"/>
-      <c r="M110" s="210"/>
+      <c r="B110" s="241"/>
+      <c r="C110" s="241"/>
+      <c r="D110" s="241"/>
+      <c r="E110" s="241"/>
+      <c r="F110" s="241"/>
+      <c r="G110" s="241"/>
+      <c r="H110" s="241"/>
+      <c r="I110" s="241"/>
+      <c r="J110" s="241"/>
+      <c r="K110" s="241"/>
+      <c r="L110" s="241"/>
+      <c r="M110" s="241"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A111" s="24"/>
@@ -20871,13 +21101,13 @@
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
       <c r="H111" s="24"/>
-      <c r="I111" s="204" t="s">
+      <c r="I111" s="229" t="s">
         <v>288</v>
       </c>
-      <c r="J111" s="204"/>
-      <c r="K111" s="204"/>
-      <c r="L111" s="204"/>
-      <c r="M111" s="204"/>
+      <c r="J111" s="229"/>
+      <c r="K111" s="229"/>
+      <c r="L111" s="229"/>
+      <c r="M111" s="229"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A112" s="24"/>
@@ -20892,11 +21122,11 @@
       <c r="F112" s="24"/>
       <c r="G112" s="24"/>
       <c r="H112" s="24"/>
-      <c r="I112" s="204"/>
-      <c r="J112" s="204"/>
-      <c r="K112" s="204"/>
-      <c r="L112" s="204"/>
-      <c r="M112" s="204"/>
+      <c r="I112" s="229"/>
+      <c r="J112" s="229"/>
+      <c r="K112" s="229"/>
+      <c r="L112" s="229"/>
+      <c r="M112" s="229"/>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A113" s="24"/>
@@ -20909,11 +21139,11 @@
       <c r="F113" s="24"/>
       <c r="G113" s="24"/>
       <c r="H113" s="24"/>
-      <c r="I113" s="204"/>
-      <c r="J113" s="204"/>
-      <c r="K113" s="204"/>
-      <c r="L113" s="204"/>
-      <c r="M113" s="204"/>
+      <c r="I113" s="229"/>
+      <c r="J113" s="229"/>
+      <c r="K113" s="229"/>
+      <c r="L113" s="229"/>
+      <c r="M113" s="229"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A114" s="24"/>
@@ -20988,72 +21218,72 @@
       <c r="B118" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="C118" s="209" t="s">
+      <c r="C118" s="223" t="s">
         <v>274</v>
       </c>
-      <c r="D118" s="209"/>
-      <c r="E118" s="209"/>
-      <c r="F118" s="209"/>
-      <c r="G118" s="209"/>
-      <c r="H118" s="208" t="s">
+      <c r="D118" s="223"/>
+      <c r="E118" s="223"/>
+      <c r="F118" s="223"/>
+      <c r="G118" s="223"/>
+      <c r="H118" s="240" t="s">
         <v>290</v>
       </c>
-      <c r="I118" s="208"/>
-      <c r="J118" s="208"/>
-      <c r="K118" s="208"/>
-      <c r="L118" s="208"/>
-      <c r="M118" s="208"/>
+      <c r="I118" s="240"/>
+      <c r="J118" s="240"/>
+      <c r="K118" s="240"/>
+      <c r="L118" s="240"/>
+      <c r="M118" s="240"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A119" s="24"/>
       <c r="B119" s="24"/>
-      <c r="C119" s="209" t="s">
+      <c r="C119" s="223" t="s">
         <v>275</v>
       </c>
-      <c r="D119" s="209"/>
-      <c r="E119" s="209"/>
-      <c r="F119" s="209"/>
-      <c r="G119" s="209"/>
-      <c r="H119" s="208"/>
-      <c r="I119" s="208"/>
-      <c r="J119" s="208"/>
-      <c r="K119" s="208"/>
-      <c r="L119" s="208"/>
-      <c r="M119" s="208"/>
+      <c r="D119" s="223"/>
+      <c r="E119" s="223"/>
+      <c r="F119" s="223"/>
+      <c r="G119" s="223"/>
+      <c r="H119" s="240"/>
+      <c r="I119" s="240"/>
+      <c r="J119" s="240"/>
+      <c r="K119" s="240"/>
+      <c r="L119" s="240"/>
+      <c r="M119" s="240"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A120" s="24"/>
       <c r="B120" s="24"/>
-      <c r="C120" s="209" t="s">
+      <c r="C120" s="223" t="s">
         <v>276</v>
       </c>
-      <c r="D120" s="209"/>
-      <c r="E120" s="209"/>
-      <c r="F120" s="209"/>
-      <c r="G120" s="209"/>
-      <c r="H120" s="208"/>
-      <c r="I120" s="208"/>
-      <c r="J120" s="208"/>
-      <c r="K120" s="208"/>
-      <c r="L120" s="208"/>
-      <c r="M120" s="208"/>
+      <c r="D120" s="223"/>
+      <c r="E120" s="223"/>
+      <c r="F120" s="223"/>
+      <c r="G120" s="223"/>
+      <c r="H120" s="240"/>
+      <c r="I120" s="240"/>
+      <c r="J120" s="240"/>
+      <c r="K120" s="240"/>
+      <c r="L120" s="240"/>
+      <c r="M120" s="240"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A121" s="24"/>
       <c r="B121" s="24"/>
-      <c r="C121" s="209" t="s">
+      <c r="C121" s="223" t="s">
         <v>283</v>
       </c>
-      <c r="D121" s="209"/>
-      <c r="E121" s="209"/>
-      <c r="F121" s="209"/>
-      <c r="G121" s="209"/>
-      <c r="H121" s="208"/>
-      <c r="I121" s="208"/>
-      <c r="J121" s="208"/>
-      <c r="K121" s="208"/>
-      <c r="L121" s="208"/>
-      <c r="M121" s="208"/>
+      <c r="D121" s="223"/>
+      <c r="E121" s="223"/>
+      <c r="F121" s="223"/>
+      <c r="G121" s="223"/>
+      <c r="H121" s="240"/>
+      <c r="I121" s="240"/>
+      <c r="J121" s="240"/>
+      <c r="K121" s="240"/>
+      <c r="L121" s="240"/>
+      <c r="M121" s="240"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A122" s="24"/>
@@ -21264,35 +21494,35 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A131" s="24"/>
-      <c r="B131" s="203" t="s">
+      <c r="B131" s="230" t="s">
         <v>289</v>
       </c>
-      <c r="C131" s="203"/>
-      <c r="D131" s="203"/>
-      <c r="E131" s="203"/>
-      <c r="F131" s="203"/>
-      <c r="G131" s="203"/>
-      <c r="H131" s="203"/>
-      <c r="I131" s="203"/>
-      <c r="J131" s="203"/>
-      <c r="K131" s="203"/>
-      <c r="L131" s="203"/>
-      <c r="M131" s="203"/>
+      <c r="C131" s="230"/>
+      <c r="D131" s="230"/>
+      <c r="E131" s="230"/>
+      <c r="F131" s="230"/>
+      <c r="G131" s="230"/>
+      <c r="H131" s="230"/>
+      <c r="I131" s="230"/>
+      <c r="J131" s="230"/>
+      <c r="K131" s="230"/>
+      <c r="L131" s="230"/>
+      <c r="M131" s="230"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A132" s="24"/>
-      <c r="B132" s="203"/>
-      <c r="C132" s="203"/>
-      <c r="D132" s="203"/>
-      <c r="E132" s="203"/>
-      <c r="F132" s="203"/>
-      <c r="G132" s="203"/>
-      <c r="H132" s="203"/>
-      <c r="I132" s="203"/>
-      <c r="J132" s="203"/>
-      <c r="K132" s="203"/>
-      <c r="L132" s="203"/>
-      <c r="M132" s="203"/>
+      <c r="B132" s="230"/>
+      <c r="C132" s="230"/>
+      <c r="D132" s="230"/>
+      <c r="E132" s="230"/>
+      <c r="F132" s="230"/>
+      <c r="G132" s="230"/>
+      <c r="H132" s="230"/>
+      <c r="I132" s="230"/>
+      <c r="J132" s="230"/>
+      <c r="K132" s="230"/>
+      <c r="L132" s="230"/>
+      <c r="M132" s="230"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A133" s="24"/>
@@ -21310,36 +21540,36 @@
       <c r="M133" s="24"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A134" s="205" t="s">
+      <c r="A134" s="221" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="205"/>
-      <c r="C134" s="205"/>
-      <c r="D134" s="205"/>
-      <c r="E134" s="205"/>
-      <c r="F134" s="205"/>
-      <c r="G134" s="205"/>
-      <c r="H134" s="205"/>
-      <c r="I134" s="205"/>
-      <c r="J134" s="205"/>
-      <c r="K134" s="205"/>
-      <c r="L134" s="205"/>
-      <c r="M134" s="205"/>
+      <c r="B134" s="221"/>
+      <c r="C134" s="221"/>
+      <c r="D134" s="221"/>
+      <c r="E134" s="221"/>
+      <c r="F134" s="221"/>
+      <c r="G134" s="221"/>
+      <c r="H134" s="221"/>
+      <c r="I134" s="221"/>
+      <c r="J134" s="221"/>
+      <c r="K134" s="221"/>
+      <c r="L134" s="221"/>
+      <c r="M134" s="221"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A135" s="205"/>
-      <c r="B135" s="205"/>
-      <c r="C135" s="205"/>
-      <c r="D135" s="205"/>
-      <c r="E135" s="205"/>
-      <c r="F135" s="205"/>
-      <c r="G135" s="205"/>
-      <c r="H135" s="205"/>
-      <c r="I135" s="205"/>
-      <c r="J135" s="205"/>
-      <c r="K135" s="205"/>
-      <c r="L135" s="205"/>
-      <c r="M135" s="205"/>
+      <c r="A135" s="221"/>
+      <c r="B135" s="221"/>
+      <c r="C135" s="221"/>
+      <c r="D135" s="221"/>
+      <c r="E135" s="221"/>
+      <c r="F135" s="221"/>
+      <c r="G135" s="221"/>
+      <c r="H135" s="221"/>
+      <c r="I135" s="221"/>
+      <c r="J135" s="221"/>
+      <c r="K135" s="221"/>
+      <c r="L135" s="221"/>
+      <c r="M135" s="221"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A136" s="24"/>
@@ -21358,35 +21588,35 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A137" s="24"/>
-      <c r="B137" s="210" t="s">
+      <c r="B137" s="241" t="s">
         <v>294</v>
       </c>
-      <c r="C137" s="210"/>
-      <c r="D137" s="210"/>
-      <c r="E137" s="210"/>
-      <c r="F137" s="210"/>
-      <c r="G137" s="210"/>
-      <c r="H137" s="210"/>
-      <c r="I137" s="210"/>
-      <c r="J137" s="210"/>
-      <c r="K137" s="210"/>
-      <c r="L137" s="210"/>
-      <c r="M137" s="210"/>
+      <c r="C137" s="241"/>
+      <c r="D137" s="241"/>
+      <c r="E137" s="241"/>
+      <c r="F137" s="241"/>
+      <c r="G137" s="241"/>
+      <c r="H137" s="241"/>
+      <c r="I137" s="241"/>
+      <c r="J137" s="241"/>
+      <c r="K137" s="241"/>
+      <c r="L137" s="241"/>
+      <c r="M137" s="241"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A138" s="24"/>
-      <c r="B138" s="210"/>
-      <c r="C138" s="210"/>
-      <c r="D138" s="210"/>
-      <c r="E138" s="210"/>
-      <c r="F138" s="210"/>
-      <c r="G138" s="210"/>
-      <c r="H138" s="210"/>
-      <c r="I138" s="210"/>
-      <c r="J138" s="210"/>
-      <c r="K138" s="210"/>
-      <c r="L138" s="210"/>
-      <c r="M138" s="210"/>
+      <c r="B138" s="241"/>
+      <c r="C138" s="241"/>
+      <c r="D138" s="241"/>
+      <c r="E138" s="241"/>
+      <c r="F138" s="241"/>
+      <c r="G138" s="241"/>
+      <c r="H138" s="241"/>
+      <c r="I138" s="241"/>
+      <c r="J138" s="241"/>
+      <c r="K138" s="241"/>
+      <c r="L138" s="241"/>
+      <c r="M138" s="241"/>
     </row>
     <row r="139" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="24"/>
@@ -21397,13 +21627,13 @@
       <c r="F139" s="24"/>
       <c r="G139" s="24"/>
       <c r="H139" s="24"/>
-      <c r="I139" s="204" t="s">
+      <c r="I139" s="229" t="s">
         <v>295</v>
       </c>
-      <c r="J139" s="204"/>
-      <c r="K139" s="204"/>
-      <c r="L139" s="204"/>
-      <c r="M139" s="204"/>
+      <c r="J139" s="229"/>
+      <c r="K139" s="229"/>
+      <c r="L139" s="229"/>
+      <c r="M139" s="229"/>
     </row>
     <row r="140" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="24"/>
@@ -21411,11 +21641,11 @@
       <c r="F140" s="24"/>
       <c r="G140" s="24"/>
       <c r="H140" s="24"/>
-      <c r="I140" s="204"/>
-      <c r="J140" s="204"/>
-      <c r="K140" s="204"/>
-      <c r="L140" s="204"/>
-      <c r="M140" s="204"/>
+      <c r="I140" s="229"/>
+      <c r="J140" s="229"/>
+      <c r="K140" s="229"/>
+      <c r="L140" s="229"/>
+      <c r="M140" s="229"/>
     </row>
     <row r="141" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="24"/>
@@ -21423,11 +21653,11 @@
       <c r="F141" s="24"/>
       <c r="G141" s="24"/>
       <c r="H141" s="24"/>
-      <c r="I141" s="204"/>
-      <c r="J141" s="204"/>
-      <c r="K141" s="204"/>
-      <c r="L141" s="204"/>
-      <c r="M141" s="204"/>
+      <c r="I141" s="229"/>
+      <c r="J141" s="229"/>
+      <c r="K141" s="229"/>
+      <c r="L141" s="229"/>
+      <c r="M141" s="229"/>
     </row>
     <row r="142" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="24"/>
@@ -21527,34 +21757,34 @@
       <c r="B147" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="C147" s="203" t="s">
+      <c r="C147" s="230" t="s">
         <v>296</v>
       </c>
-      <c r="D147" s="203"/>
-      <c r="E147" s="203"/>
-      <c r="F147" s="203"/>
-      <c r="G147" s="203"/>
-      <c r="H147" s="203"/>
-      <c r="I147" s="203"/>
-      <c r="J147" s="203"/>
-      <c r="K147" s="203"/>
-      <c r="L147" s="203"/>
-      <c r="M147" s="203"/>
+      <c r="D147" s="230"/>
+      <c r="E147" s="230"/>
+      <c r="F147" s="230"/>
+      <c r="G147" s="230"/>
+      <c r="H147" s="230"/>
+      <c r="I147" s="230"/>
+      <c r="J147" s="230"/>
+      <c r="K147" s="230"/>
+      <c r="L147" s="230"/>
+      <c r="M147" s="230"/>
     </row>
     <row r="148" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="24"/>
       <c r="B148" s="76"/>
-      <c r="C148" s="203"/>
-      <c r="D148" s="203"/>
-      <c r="E148" s="203"/>
-      <c r="F148" s="203"/>
-      <c r="G148" s="203"/>
-      <c r="H148" s="203"/>
-      <c r="I148" s="203"/>
-      <c r="J148" s="203"/>
-      <c r="K148" s="203"/>
-      <c r="L148" s="203"/>
-      <c r="M148" s="203"/>
+      <c r="C148" s="230"/>
+      <c r="D148" s="230"/>
+      <c r="E148" s="230"/>
+      <c r="F148" s="230"/>
+      <c r="G148" s="230"/>
+      <c r="H148" s="230"/>
+      <c r="I148" s="230"/>
+      <c r="J148" s="230"/>
+      <c r="K148" s="230"/>
+      <c r="L148" s="230"/>
+      <c r="M148" s="230"/>
     </row>
     <row r="149" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A149" s="24"/>
@@ -21892,72 +22122,72 @@
       <c r="B168" s="77" t="s">
         <v>287</v>
       </c>
-      <c r="C168" s="207" t="s">
+      <c r="C168" s="225" t="s">
         <v>297</v>
       </c>
-      <c r="D168" s="207"/>
-      <c r="E168" s="207"/>
-      <c r="F168" s="207"/>
-      <c r="G168" s="207"/>
-      <c r="H168" s="208" t="s">
+      <c r="D168" s="225"/>
+      <c r="E168" s="225"/>
+      <c r="F168" s="225"/>
+      <c r="G168" s="225"/>
+      <c r="H168" s="240" t="s">
         <v>291</v>
       </c>
-      <c r="I168" s="208"/>
-      <c r="J168" s="208"/>
-      <c r="K168" s="208"/>
-      <c r="L168" s="208"/>
-      <c r="M168" s="208"/>
+      <c r="I168" s="240"/>
+      <c r="J168" s="240"/>
+      <c r="K168" s="240"/>
+      <c r="L168" s="240"/>
+      <c r="M168" s="240"/>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A169" s="24"/>
       <c r="B169" s="24"/>
-      <c r="C169" s="209" t="s">
+      <c r="C169" s="223" t="s">
         <v>314</v>
       </c>
-      <c r="D169" s="209"/>
-      <c r="E169" s="209"/>
-      <c r="F169" s="209"/>
-      <c r="G169" s="209"/>
-      <c r="H169" s="208"/>
-      <c r="I169" s="208"/>
-      <c r="J169" s="208"/>
-      <c r="K169" s="208"/>
-      <c r="L169" s="208"/>
-      <c r="M169" s="208"/>
+      <c r="D169" s="223"/>
+      <c r="E169" s="223"/>
+      <c r="F169" s="223"/>
+      <c r="G169" s="223"/>
+      <c r="H169" s="240"/>
+      <c r="I169" s="240"/>
+      <c r="J169" s="240"/>
+      <c r="K169" s="240"/>
+      <c r="L169" s="240"/>
+      <c r="M169" s="240"/>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A170" s="24"/>
       <c r="B170" s="24"/>
-      <c r="C170" s="209" t="s">
+      <c r="C170" s="223" t="s">
         <v>315</v>
       </c>
-      <c r="D170" s="209"/>
-      <c r="E170" s="209"/>
-      <c r="F170" s="209"/>
-      <c r="G170" s="209"/>
-      <c r="H170" s="208"/>
-      <c r="I170" s="208"/>
-      <c r="J170" s="208"/>
-      <c r="K170" s="208"/>
-      <c r="L170" s="208"/>
-      <c r="M170" s="208"/>
+      <c r="D170" s="223"/>
+      <c r="E170" s="223"/>
+      <c r="F170" s="223"/>
+      <c r="G170" s="223"/>
+      <c r="H170" s="240"/>
+      <c r="I170" s="240"/>
+      <c r="J170" s="240"/>
+      <c r="K170" s="240"/>
+      <c r="L170" s="240"/>
+      <c r="M170" s="240"/>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A171" s="24"/>
       <c r="B171" s="24"/>
-      <c r="C171" s="209" t="s">
+      <c r="C171" s="223" t="s">
         <v>316</v>
       </c>
-      <c r="D171" s="209"/>
-      <c r="E171" s="209"/>
-      <c r="F171" s="209"/>
-      <c r="G171" s="209"/>
-      <c r="H171" s="208"/>
-      <c r="I171" s="208"/>
-      <c r="J171" s="208"/>
-      <c r="K171" s="208"/>
-      <c r="L171" s="208"/>
-      <c r="M171" s="208"/>
+      <c r="D171" s="223"/>
+      <c r="E171" s="223"/>
+      <c r="F171" s="223"/>
+      <c r="G171" s="223"/>
+      <c r="H171" s="240"/>
+      <c r="I171" s="240"/>
+      <c r="J171" s="240"/>
+      <c r="K171" s="240"/>
+      <c r="L171" s="240"/>
+      <c r="M171" s="240"/>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A172" s="24"/>
@@ -21988,11 +22218,11 @@
       <c r="K173" s="24"/>
       <c r="L173" s="24"/>
       <c r="M173" s="24"/>
-      <c r="N173" s="200" t="s">
+      <c r="N173" s="239" t="s">
         <v>396</v>
       </c>
-      <c r="O173" s="200"/>
-      <c r="P173" s="200"/>
+      <c r="O173" s="239"/>
+      <c r="P173" s="239"/>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A174" s="24"/>
@@ -22237,36 +22467,36 @@
       <c r="M180" s="24"/>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A181" s="205" t="s">
+      <c r="A181" s="221" t="s">
         <v>351</v>
       </c>
-      <c r="B181" s="205"/>
-      <c r="C181" s="205"/>
-      <c r="D181" s="205"/>
-      <c r="E181" s="205"/>
-      <c r="F181" s="205"/>
-      <c r="G181" s="205"/>
-      <c r="H181" s="205"/>
-      <c r="I181" s="205"/>
-      <c r="J181" s="205"/>
-      <c r="K181" s="205"/>
-      <c r="L181" s="205"/>
-      <c r="M181" s="205"/>
+      <c r="B181" s="221"/>
+      <c r="C181" s="221"/>
+      <c r="D181" s="221"/>
+      <c r="E181" s="221"/>
+      <c r="F181" s="221"/>
+      <c r="G181" s="221"/>
+      <c r="H181" s="221"/>
+      <c r="I181" s="221"/>
+      <c r="J181" s="221"/>
+      <c r="K181" s="221"/>
+      <c r="L181" s="221"/>
+      <c r="M181" s="221"/>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A182" s="205"/>
-      <c r="B182" s="205"/>
-      <c r="C182" s="205"/>
-      <c r="D182" s="205"/>
-      <c r="E182" s="205"/>
-      <c r="F182" s="205"/>
-      <c r="G182" s="205"/>
-      <c r="H182" s="205"/>
-      <c r="I182" s="205"/>
-      <c r="J182" s="205"/>
-      <c r="K182" s="205"/>
-      <c r="L182" s="205"/>
-      <c r="M182" s="205"/>
+      <c r="A182" s="221"/>
+      <c r="B182" s="221"/>
+      <c r="C182" s="221"/>
+      <c r="D182" s="221"/>
+      <c r="E182" s="221"/>
+      <c r="F182" s="221"/>
+      <c r="G182" s="221"/>
+      <c r="H182" s="221"/>
+      <c r="I182" s="221"/>
+      <c r="J182" s="221"/>
+      <c r="K182" s="221"/>
+      <c r="L182" s="221"/>
+      <c r="M182" s="221"/>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A183" s="24"/>
@@ -22285,35 +22515,35 @@
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A184" s="24"/>
-      <c r="B184" s="206" t="s">
+      <c r="B184" s="226" t="s">
         <v>339</v>
       </c>
-      <c r="C184" s="206"/>
-      <c r="D184" s="206"/>
-      <c r="E184" s="206"/>
-      <c r="F184" s="206"/>
-      <c r="G184" s="206"/>
-      <c r="H184" s="206"/>
-      <c r="I184" s="206"/>
-      <c r="J184" s="206"/>
-      <c r="K184" s="206"/>
-      <c r="L184" s="206"/>
-      <c r="M184" s="206"/>
+      <c r="C184" s="226"/>
+      <c r="D184" s="226"/>
+      <c r="E184" s="226"/>
+      <c r="F184" s="226"/>
+      <c r="G184" s="226"/>
+      <c r="H184" s="226"/>
+      <c r="I184" s="226"/>
+      <c r="J184" s="226"/>
+      <c r="K184" s="226"/>
+      <c r="L184" s="226"/>
+      <c r="M184" s="226"/>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A185" s="24"/>
-      <c r="B185" s="206"/>
-      <c r="C185" s="206"/>
-      <c r="D185" s="206"/>
-      <c r="E185" s="206"/>
-      <c r="F185" s="206"/>
-      <c r="G185" s="206"/>
-      <c r="H185" s="206"/>
-      <c r="I185" s="206"/>
-      <c r="J185" s="206"/>
-      <c r="K185" s="206"/>
-      <c r="L185" s="206"/>
-      <c r="M185" s="206"/>
+      <c r="B185" s="226"/>
+      <c r="C185" s="226"/>
+      <c r="D185" s="226"/>
+      <c r="E185" s="226"/>
+      <c r="F185" s="226"/>
+      <c r="G185" s="226"/>
+      <c r="H185" s="226"/>
+      <c r="I185" s="226"/>
+      <c r="J185" s="226"/>
+      <c r="K185" s="226"/>
+      <c r="L185" s="226"/>
+      <c r="M185" s="226"/>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A186" s="24"/>
@@ -22324,32 +22554,32 @@
       <c r="F186" s="24"/>
       <c r="G186" s="24"/>
       <c r="H186" s="24"/>
-      <c r="I186" s="204" t="s">
+      <c r="I186" s="229" t="s">
         <v>352</v>
       </c>
-      <c r="J186" s="204"/>
-      <c r="K186" s="204"/>
-      <c r="L186" s="204"/>
-      <c r="M186" s="204"/>
+      <c r="J186" s="229"/>
+      <c r="K186" s="229"/>
+      <c r="L186" s="229"/>
+      <c r="M186" s="229"/>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A187" s="24"/>
-      <c r="B187" s="225" t="s">
+      <c r="B187" s="227" t="s">
         <v>344</v>
       </c>
-      <c r="C187" s="225"/>
+      <c r="C187" s="227"/>
       <c r="D187" s="83"/>
       <c r="E187" s="24"/>
       <c r="F187" s="24"/>
       <c r="G187" s="24"/>
       <c r="H187" s="24"/>
-      <c r="I187" s="204" t="s">
+      <c r="I187" s="229" t="s">
         <v>353</v>
       </c>
-      <c r="J187" s="204"/>
-      <c r="K187" s="204"/>
-      <c r="L187" s="204"/>
-      <c r="M187" s="204"/>
+      <c r="J187" s="229"/>
+      <c r="K187" s="229"/>
+      <c r="L187" s="229"/>
+      <c r="M187" s="229"/>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A188" s="24"/>
@@ -22362,13 +22592,13 @@
       <c r="F188" s="24"/>
       <c r="G188" s="24"/>
       <c r="H188" s="24"/>
-      <c r="I188" s="204" t="s">
+      <c r="I188" s="229" t="s">
         <v>354</v>
       </c>
-      <c r="J188" s="204"/>
-      <c r="K188" s="204"/>
-      <c r="L188" s="204"/>
-      <c r="M188" s="204"/>
+      <c r="J188" s="229"/>
+      <c r="K188" s="229"/>
+      <c r="L188" s="229"/>
+      <c r="M188" s="229"/>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A189" s="24"/>
@@ -22481,19 +22711,19 @@
       <c r="B195" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="C195" s="211" t="s">
+      <c r="C195" s="224" t="s">
         <v>355</v>
       </c>
-      <c r="D195" s="211"/>
-      <c r="E195" s="211"/>
-      <c r="F195" s="211"/>
-      <c r="G195" s="211"/>
-      <c r="H195" s="211"/>
-      <c r="I195" s="211"/>
-      <c r="J195" s="211"/>
-      <c r="K195" s="211"/>
-      <c r="L195" s="211"/>
-      <c r="M195" s="211"/>
+      <c r="D195" s="224"/>
+      <c r="E195" s="224"/>
+      <c r="F195" s="224"/>
+      <c r="G195" s="224"/>
+      <c r="H195" s="224"/>
+      <c r="I195" s="224"/>
+      <c r="J195" s="224"/>
+      <c r="K195" s="224"/>
+      <c r="L195" s="224"/>
+      <c r="M195" s="224"/>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A196" s="24"/>
@@ -22517,30 +22747,30 @@
       <c r="B197" s="77" t="s">
         <v>287</v>
       </c>
-      <c r="C197" s="209" t="s">
+      <c r="C197" s="223" t="s">
         <v>383</v>
       </c>
-      <c r="D197" s="209"/>
-      <c r="E197" s="209"/>
-      <c r="F197" s="209"/>
-      <c r="G197" s="209"/>
-      <c r="H197" s="209"/>
-      <c r="I197" s="209"/>
-      <c r="J197" s="209"/>
-      <c r="K197" s="209"/>
-      <c r="L197" s="209"/>
-      <c r="M197" s="209"/>
+      <c r="D197" s="223"/>
+      <c r="E197" s="223"/>
+      <c r="F197" s="223"/>
+      <c r="G197" s="223"/>
+      <c r="H197" s="223"/>
+      <c r="I197" s="223"/>
+      <c r="J197" s="223"/>
+      <c r="K197" s="223"/>
+      <c r="L197" s="223"/>
+      <c r="M197" s="223"/>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A198" s="24"/>
       <c r="B198" s="24"/>
-      <c r="C198" s="209" t="s">
+      <c r="C198" s="223" t="s">
         <v>350</v>
       </c>
-      <c r="D198" s="209"/>
-      <c r="E198" s="209"/>
-      <c r="F198" s="209"/>
-      <c r="G198" s="209"/>
+      <c r="D198" s="223"/>
+      <c r="E198" s="223"/>
+      <c r="F198" s="223"/>
+      <c r="G198" s="223"/>
       <c r="H198" s="85"/>
       <c r="I198" s="85"/>
       <c r="J198" s="85"/>
@@ -22551,13 +22781,13 @@
     <row r="199" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A199" s="24"/>
       <c r="B199" s="24"/>
-      <c r="C199" s="209" t="s">
+      <c r="C199" s="223" t="s">
         <v>381</v>
       </c>
-      <c r="D199" s="209"/>
-      <c r="E199" s="209"/>
-      <c r="F199" s="209"/>
-      <c r="G199" s="209"/>
+      <c r="D199" s="223"/>
+      <c r="E199" s="223"/>
+      <c r="F199" s="223"/>
+      <c r="G199" s="223"/>
       <c r="H199" s="85"/>
       <c r="I199" s="85"/>
       <c r="J199" s="85"/>
@@ -22568,13 +22798,13 @@
     <row r="200" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A200" s="24"/>
       <c r="B200" s="24"/>
-      <c r="C200" s="207" t="s">
+      <c r="C200" s="225" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="207"/>
-      <c r="E200" s="207"/>
-      <c r="F200" s="207"/>
-      <c r="G200" s="207"/>
+      <c r="D200" s="225"/>
+      <c r="E200" s="225"/>
+      <c r="F200" s="225"/>
+      <c r="G200" s="225"/>
       <c r="H200" s="21"/>
       <c r="I200" s="21"/>
       <c r="J200" s="21"/>
@@ -22596,11 +22826,11 @@
       <c r="K201" s="24"/>
       <c r="L201" s="24"/>
       <c r="M201" s="24"/>
-      <c r="P201" s="200" t="s">
+      <c r="P201" s="239" t="s">
         <v>396</v>
       </c>
-      <c r="Q201" s="200"/>
-      <c r="R201" s="200"/>
+      <c r="Q201" s="239"/>
+      <c r="R201" s="239"/>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A202" s="24"/>
@@ -22886,36 +23116,36 @@
       <c r="M209" s="24"/>
     </row>
     <row r="210" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A210" s="205" t="s">
+      <c r="A210" s="221" t="s">
         <v>405</v>
       </c>
-      <c r="B210" s="205"/>
-      <c r="C210" s="205"/>
-      <c r="D210" s="205"/>
-      <c r="E210" s="205"/>
-      <c r="F210" s="205"/>
-      <c r="G210" s="205"/>
-      <c r="H210" s="205"/>
-      <c r="I210" s="205"/>
-      <c r="J210" s="205"/>
-      <c r="K210" s="205"/>
-      <c r="L210" s="205"/>
-      <c r="M210" s="205"/>
+      <c r="B210" s="221"/>
+      <c r="C210" s="221"/>
+      <c r="D210" s="221"/>
+      <c r="E210" s="221"/>
+      <c r="F210" s="221"/>
+      <c r="G210" s="221"/>
+      <c r="H210" s="221"/>
+      <c r="I210" s="221"/>
+      <c r="J210" s="221"/>
+      <c r="K210" s="221"/>
+      <c r="L210" s="221"/>
+      <c r="M210" s="221"/>
     </row>
     <row r="211" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A211" s="205"/>
-      <c r="B211" s="205"/>
-      <c r="C211" s="205"/>
-      <c r="D211" s="205"/>
-      <c r="E211" s="205"/>
-      <c r="F211" s="205"/>
-      <c r="G211" s="205"/>
-      <c r="H211" s="205"/>
-      <c r="I211" s="205"/>
-      <c r="J211" s="205"/>
-      <c r="K211" s="205"/>
-      <c r="L211" s="205"/>
-      <c r="M211" s="205"/>
+      <c r="A211" s="221"/>
+      <c r="B211" s="221"/>
+      <c r="C211" s="221"/>
+      <c r="D211" s="221"/>
+      <c r="E211" s="221"/>
+      <c r="F211" s="221"/>
+      <c r="G211" s="221"/>
+      <c r="H211" s="221"/>
+      <c r="I211" s="221"/>
+      <c r="J211" s="221"/>
+      <c r="K211" s="221"/>
+      <c r="L211" s="221"/>
+      <c r="M211" s="221"/>
     </row>
     <row r="212" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A212" s="24"/>
@@ -22933,35 +23163,35 @@
     </row>
     <row r="213" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A213" s="24"/>
-      <c r="B213" s="206" t="s">
+      <c r="B213" s="226" t="s">
         <v>406</v>
       </c>
-      <c r="C213" s="206"/>
-      <c r="D213" s="206"/>
-      <c r="E213" s="206"/>
-      <c r="F213" s="206"/>
-      <c r="G213" s="206"/>
-      <c r="H213" s="206"/>
-      <c r="I213" s="206"/>
-      <c r="J213" s="206"/>
-      <c r="K213" s="206"/>
-      <c r="L213" s="206"/>
-      <c r="M213" s="206"/>
+      <c r="C213" s="226"/>
+      <c r="D213" s="226"/>
+      <c r="E213" s="226"/>
+      <c r="F213" s="226"/>
+      <c r="G213" s="226"/>
+      <c r="H213" s="226"/>
+      <c r="I213" s="226"/>
+      <c r="J213" s="226"/>
+      <c r="K213" s="226"/>
+      <c r="L213" s="226"/>
+      <c r="M213" s="226"/>
     </row>
     <row r="214" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A214" s="24"/>
-      <c r="B214" s="206"/>
-      <c r="C214" s="206"/>
-      <c r="D214" s="206"/>
-      <c r="E214" s="206"/>
-      <c r="F214" s="206"/>
-      <c r="G214" s="206"/>
-      <c r="H214" s="206"/>
-      <c r="I214" s="206"/>
-      <c r="J214" s="206"/>
-      <c r="K214" s="206"/>
-      <c r="L214" s="206"/>
-      <c r="M214" s="206"/>
+      <c r="B214" s="226"/>
+      <c r="C214" s="226"/>
+      <c r="D214" s="226"/>
+      <c r="E214" s="226"/>
+      <c r="F214" s="226"/>
+      <c r="G214" s="226"/>
+      <c r="H214" s="226"/>
+      <c r="I214" s="226"/>
+      <c r="J214" s="226"/>
+      <c r="K214" s="226"/>
+      <c r="L214" s="226"/>
+      <c r="M214" s="226"/>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A215" s="24"/>
@@ -22972,13 +23202,13 @@
       <c r="F215" s="24"/>
       <c r="G215" s="24"/>
       <c r="H215" s="24"/>
-      <c r="I215" s="204" t="s">
+      <c r="I215" s="229" t="s">
         <v>369</v>
       </c>
-      <c r="J215" s="204"/>
-      <c r="K215" s="204"/>
-      <c r="L215" s="204"/>
-      <c r="M215" s="204"/>
+      <c r="J215" s="229"/>
+      <c r="K215" s="229"/>
+      <c r="L215" s="229"/>
+      <c r="M215" s="229"/>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A216" s="24"/>
@@ -22991,11 +23221,11 @@
       <c r="F216" s="24"/>
       <c r="G216" s="24"/>
       <c r="H216" s="24"/>
-      <c r="I216" s="204"/>
-      <c r="J216" s="204"/>
-      <c r="K216" s="204"/>
-      <c r="L216" s="204"/>
-      <c r="M216" s="204"/>
+      <c r="I216" s="229"/>
+      <c r="J216" s="229"/>
+      <c r="K216" s="229"/>
+      <c r="L216" s="229"/>
+      <c r="M216" s="229"/>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A217" s="24"/>
@@ -23010,11 +23240,11 @@
       <c r="F217" s="24"/>
       <c r="G217" s="24"/>
       <c r="H217" s="24"/>
-      <c r="I217" s="204"/>
-      <c r="J217" s="204"/>
-      <c r="K217" s="204"/>
-      <c r="L217" s="204"/>
-      <c r="M217" s="204"/>
+      <c r="I217" s="229"/>
+      <c r="J217" s="229"/>
+      <c r="K217" s="229"/>
+      <c r="L217" s="229"/>
+      <c r="M217" s="229"/>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A218" s="24"/>
@@ -23105,19 +23335,19 @@
       <c r="B223" s="75" t="s">
         <v>363</v>
       </c>
-      <c r="C223" s="211" t="s">
+      <c r="C223" s="224" t="s">
         <v>364</v>
       </c>
-      <c r="D223" s="211"/>
-      <c r="E223" s="211"/>
-      <c r="F223" s="211"/>
-      <c r="G223" s="211"/>
-      <c r="H223" s="211"/>
-      <c r="I223" s="211"/>
-      <c r="J223" s="211"/>
-      <c r="K223" s="211"/>
-      <c r="L223" s="211"/>
-      <c r="M223" s="211"/>
+      <c r="D223" s="224"/>
+      <c r="E223" s="224"/>
+      <c r="F223" s="224"/>
+      <c r="G223" s="224"/>
+      <c r="H223" s="224"/>
+      <c r="I223" s="224"/>
+      <c r="J223" s="224"/>
+      <c r="K223" s="224"/>
+      <c r="L223" s="224"/>
+      <c r="M223" s="224"/>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A224" s="24"/>
@@ -23139,19 +23369,19 @@
       <c r="B225" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="C225" s="211" t="s">
+      <c r="C225" s="224" t="s">
         <v>365</v>
       </c>
-      <c r="D225" s="211"/>
-      <c r="E225" s="211"/>
-      <c r="F225" s="211"/>
-      <c r="G225" s="211"/>
-      <c r="H225" s="211"/>
-      <c r="I225" s="211"/>
-      <c r="J225" s="211"/>
-      <c r="K225" s="211"/>
-      <c r="L225" s="211"/>
-      <c r="M225" s="211"/>
+      <c r="D225" s="224"/>
+      <c r="E225" s="224"/>
+      <c r="F225" s="224"/>
+      <c r="G225" s="224"/>
+      <c r="H225" s="224"/>
+      <c r="I225" s="224"/>
+      <c r="J225" s="224"/>
+      <c r="K225" s="224"/>
+      <c r="L225" s="224"/>
+      <c r="M225" s="224"/>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A226" s="24"/>
@@ -23173,19 +23403,19 @@
       <c r="B227" s="75" t="s">
         <v>366</v>
       </c>
-      <c r="C227" s="211" t="s">
+      <c r="C227" s="224" t="s">
         <v>367</v>
       </c>
-      <c r="D227" s="211"/>
-      <c r="E227" s="211"/>
-      <c r="F227" s="211"/>
-      <c r="G227" s="211"/>
-      <c r="H227" s="211"/>
-      <c r="I227" s="211"/>
-      <c r="J227" s="211"/>
-      <c r="K227" s="211"/>
-      <c r="L227" s="211"/>
-      <c r="M227" s="211"/>
+      <c r="D227" s="224"/>
+      <c r="E227" s="224"/>
+      <c r="F227" s="224"/>
+      <c r="G227" s="224"/>
+      <c r="H227" s="224"/>
+      <c r="I227" s="224"/>
+      <c r="J227" s="224"/>
+      <c r="K227" s="224"/>
+      <c r="L227" s="224"/>
+      <c r="M227" s="224"/>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A228" s="24"/>
@@ -23204,26 +23434,26 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A229" s="24"/>
-      <c r="B229" s="145" t="s">
+      <c r="B229" s="168" t="s">
         <v>374</v>
       </c>
-      <c r="C229" s="211" t="s">
+      <c r="C229" s="224" t="s">
         <v>375</v>
       </c>
-      <c r="D229" s="211"/>
-      <c r="E229" s="211"/>
-      <c r="F229" s="211"/>
-      <c r="G229" s="211"/>
-      <c r="H229" s="211"/>
-      <c r="I229" s="211"/>
-      <c r="J229" s="211"/>
-      <c r="K229" s="211"/>
-      <c r="L229" s="211"/>
-      <c r="M229" s="211"/>
+      <c r="D229" s="224"/>
+      <c r="E229" s="224"/>
+      <c r="F229" s="224"/>
+      <c r="G229" s="224"/>
+      <c r="H229" s="224"/>
+      <c r="I229" s="224"/>
+      <c r="J229" s="224"/>
+      <c r="K229" s="224"/>
+      <c r="L229" s="224"/>
+      <c r="M229" s="224"/>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A230" s="24"/>
-      <c r="B230" s="141"/>
+      <c r="B230" s="164"/>
       <c r="C230" s="26" t="s">
         <v>407</v>
       </c>
@@ -23240,7 +23470,7 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A231" s="24"/>
-      <c r="B231" s="141"/>
+      <c r="B231" s="164"/>
       <c r="C231" s="26" t="s">
         <v>376</v>
       </c>
@@ -23275,19 +23505,19 @@
       <c r="B233" s="100" t="s">
         <v>377</v>
       </c>
-      <c r="C233" s="211" t="s">
+      <c r="C233" s="224" t="s">
         <v>378</v>
       </c>
-      <c r="D233" s="211"/>
-      <c r="E233" s="211"/>
-      <c r="F233" s="211"/>
-      <c r="G233" s="211"/>
-      <c r="H233" s="211"/>
-      <c r="I233" s="211"/>
-      <c r="J233" s="211"/>
-      <c r="K233" s="211"/>
-      <c r="L233" s="211"/>
-      <c r="M233" s="211"/>
+      <c r="D233" s="224"/>
+      <c r="E233" s="224"/>
+      <c r="F233" s="224"/>
+      <c r="G233" s="224"/>
+      <c r="H233" s="224"/>
+      <c r="I233" s="224"/>
+      <c r="J233" s="224"/>
+      <c r="K233" s="224"/>
+      <c r="L233" s="224"/>
+      <c r="M233" s="224"/>
     </row>
     <row r="234" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A234" s="24"/>
@@ -23305,37 +23535,37 @@
     </row>
     <row r="235" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A235" s="24"/>
-      <c r="B235" s="226" t="s">
+      <c r="B235" s="222" t="s">
         <v>379</v>
       </c>
-      <c r="C235" s="138" t="s">
+      <c r="C235" s="161" t="s">
         <v>380</v>
       </c>
-      <c r="D235" s="138"/>
-      <c r="E235" s="138"/>
-      <c r="F235" s="138"/>
-      <c r="G235" s="138"/>
-      <c r="H235" s="138"/>
-      <c r="I235" s="138"/>
-      <c r="J235" s="138"/>
-      <c r="K235" s="138"/>
-      <c r="L235" s="138"/>
-      <c r="M235" s="138"/>
+      <c r="D235" s="161"/>
+      <c r="E235" s="161"/>
+      <c r="F235" s="161"/>
+      <c r="G235" s="161"/>
+      <c r="H235" s="161"/>
+      <c r="I235" s="161"/>
+      <c r="J235" s="161"/>
+      <c r="K235" s="161"/>
+      <c r="L235" s="161"/>
+      <c r="M235" s="161"/>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A236" s="24"/>
-      <c r="B236" s="139"/>
-      <c r="C236" s="138"/>
-      <c r="D236" s="138"/>
-      <c r="E236" s="138"/>
-      <c r="F236" s="138"/>
-      <c r="G236" s="138"/>
-      <c r="H236" s="138"/>
-      <c r="I236" s="138"/>
-      <c r="J236" s="138"/>
-      <c r="K236" s="138"/>
-      <c r="L236" s="138"/>
-      <c r="M236" s="138"/>
+      <c r="B236" s="162"/>
+      <c r="C236" s="161"/>
+      <c r="D236" s="161"/>
+      <c r="E236" s="161"/>
+      <c r="F236" s="161"/>
+      <c r="G236" s="161"/>
+      <c r="H236" s="161"/>
+      <c r="I236" s="161"/>
+      <c r="J236" s="161"/>
+      <c r="K236" s="161"/>
+      <c r="L236" s="161"/>
+      <c r="M236" s="161"/>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A237" s="24"/>
@@ -23358,30 +23588,30 @@
       <c r="B238" s="77" t="s">
         <v>287</v>
       </c>
-      <c r="C238" s="209" t="s">
+      <c r="C238" s="223" t="s">
         <v>371</v>
       </c>
-      <c r="D238" s="209"/>
-      <c r="E238" s="209"/>
-      <c r="F238" s="209"/>
-      <c r="G238" s="209"/>
-      <c r="H238" s="209"/>
-      <c r="I238" s="209"/>
-      <c r="J238" s="209"/>
-      <c r="K238" s="209"/>
-      <c r="L238" s="209"/>
-      <c r="M238" s="209"/>
+      <c r="D238" s="223"/>
+      <c r="E238" s="223"/>
+      <c r="F238" s="223"/>
+      <c r="G238" s="223"/>
+      <c r="H238" s="223"/>
+      <c r="I238" s="223"/>
+      <c r="J238" s="223"/>
+      <c r="K238" s="223"/>
+      <c r="L238" s="223"/>
+      <c r="M238" s="223"/>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A239" s="24"/>
       <c r="B239" s="24"/>
-      <c r="C239" s="209" t="s">
+      <c r="C239" s="223" t="s">
         <v>372</v>
       </c>
-      <c r="D239" s="209"/>
-      <c r="E239" s="209"/>
-      <c r="F239" s="209"/>
-      <c r="G239" s="209"/>
+      <c r="D239" s="223"/>
+      <c r="E239" s="223"/>
+      <c r="F239" s="223"/>
+      <c r="G239" s="223"/>
       <c r="H239" s="85"/>
       <c r="I239" s="85"/>
       <c r="J239" s="85"/>
@@ -23392,13 +23622,13 @@
     <row r="240" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A240" s="24"/>
       <c r="B240" s="24"/>
-      <c r="C240" s="209" t="s">
+      <c r="C240" s="223" t="s">
         <v>373</v>
       </c>
-      <c r="D240" s="209"/>
-      <c r="E240" s="209"/>
-      <c r="F240" s="209"/>
-      <c r="G240" s="209"/>
+      <c r="D240" s="223"/>
+      <c r="E240" s="223"/>
+      <c r="F240" s="223"/>
+      <c r="G240" s="223"/>
       <c r="H240" s="85"/>
       <c r="I240" s="85"/>
       <c r="J240" s="85"/>
@@ -23420,11 +23650,11 @@
       <c r="K241" s="24"/>
       <c r="L241" s="24"/>
       <c r="M241" s="24"/>
-      <c r="R241" s="200" t="s">
+      <c r="R241" s="239" t="s">
         <v>396</v>
       </c>
-      <c r="S241" s="200"/>
-      <c r="T241" s="200"/>
+      <c r="S241" s="239"/>
+      <c r="T241" s="239"/>
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A242" s="24"/>
@@ -23710,36 +23940,36 @@
       <c r="M247" s="24"/>
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A248" s="205" t="s">
+      <c r="A248" s="221" t="s">
         <v>409</v>
       </c>
-      <c r="B248" s="205"/>
-      <c r="C248" s="205"/>
-      <c r="D248" s="205"/>
-      <c r="E248" s="205"/>
-      <c r="F248" s="205"/>
-      <c r="G248" s="205"/>
-      <c r="H248" s="205"/>
-      <c r="I248" s="205"/>
-      <c r="J248" s="205"/>
-      <c r="K248" s="205"/>
-      <c r="L248" s="205"/>
-      <c r="M248" s="205"/>
+      <c r="B248" s="221"/>
+      <c r="C248" s="221"/>
+      <c r="D248" s="221"/>
+      <c r="E248" s="221"/>
+      <c r="F248" s="221"/>
+      <c r="G248" s="221"/>
+      <c r="H248" s="221"/>
+      <c r="I248" s="221"/>
+      <c r="J248" s="221"/>
+      <c r="K248" s="221"/>
+      <c r="L248" s="221"/>
+      <c r="M248" s="221"/>
     </row>
     <row r="249" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A249" s="205"/>
-      <c r="B249" s="205"/>
-      <c r="C249" s="205"/>
-      <c r="D249" s="205"/>
-      <c r="E249" s="205"/>
-      <c r="F249" s="205"/>
-      <c r="G249" s="205"/>
-      <c r="H249" s="205"/>
-      <c r="I249" s="205"/>
-      <c r="J249" s="205"/>
-      <c r="K249" s="205"/>
-      <c r="L249" s="205"/>
-      <c r="M249" s="205"/>
+      <c r="A249" s="221"/>
+      <c r="B249" s="221"/>
+      <c r="C249" s="221"/>
+      <c r="D249" s="221"/>
+      <c r="E249" s="221"/>
+      <c r="F249" s="221"/>
+      <c r="G249" s="221"/>
+      <c r="H249" s="221"/>
+      <c r="I249" s="221"/>
+      <c r="J249" s="221"/>
+      <c r="K249" s="221"/>
+      <c r="L249" s="221"/>
+      <c r="M249" s="221"/>
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A250" s="24"/>
@@ -25258,6 +25488,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="N173:P173"/>
+    <mergeCell ref="R241:T241"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C16:M18"/>
+    <mergeCell ref="B131:M132"/>
+    <mergeCell ref="I111:M113"/>
+    <mergeCell ref="A210:M211"/>
+    <mergeCell ref="I215:M217"/>
+    <mergeCell ref="B213:M214"/>
+    <mergeCell ref="A134:M135"/>
+    <mergeCell ref="C168:G168"/>
+    <mergeCell ref="H168:M171"/>
+    <mergeCell ref="C169:G169"/>
+    <mergeCell ref="C170:G170"/>
+    <mergeCell ref="C171:G171"/>
+    <mergeCell ref="B137:M138"/>
+    <mergeCell ref="P201:R201"/>
+    <mergeCell ref="C120:G120"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="H118:M121"/>
+    <mergeCell ref="C13:M14"/>
+    <mergeCell ref="B109:M110"/>
+    <mergeCell ref="C48:M49"/>
+    <mergeCell ref="C58:M58"/>
+    <mergeCell ref="D60:M60"/>
+    <mergeCell ref="C66:M68"/>
+    <mergeCell ref="C45:M46"/>
+    <mergeCell ref="I186:M186"/>
+    <mergeCell ref="I187:M187"/>
+    <mergeCell ref="I188:M188"/>
+    <mergeCell ref="C195:M195"/>
+    <mergeCell ref="A181:M182"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="A106:M107"/>
+    <mergeCell ref="C15:M15"/>
+    <mergeCell ref="C44:M44"/>
+    <mergeCell ref="C31:M31"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:M98"/>
+    <mergeCell ref="A71:M72"/>
+    <mergeCell ref="C19:M20"/>
+    <mergeCell ref="C21:M23"/>
+    <mergeCell ref="C79:M79"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="C32:M33"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="C4:M5"/>
+    <mergeCell ref="C47:M47"/>
+    <mergeCell ref="B184:M185"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="C34:M34"/>
+    <mergeCell ref="C35:M35"/>
+    <mergeCell ref="I139:M141"/>
+    <mergeCell ref="C147:M148"/>
+    <mergeCell ref="C118:G118"/>
+    <mergeCell ref="C119:G119"/>
+    <mergeCell ref="C121:G121"/>
     <mergeCell ref="A248:M249"/>
     <mergeCell ref="B235:B236"/>
     <mergeCell ref="C197:M197"/>
@@ -25274,63 +25561,6 @@
     <mergeCell ref="C225:M225"/>
     <mergeCell ref="C227:M227"/>
     <mergeCell ref="C200:G200"/>
-    <mergeCell ref="B184:M185"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="C34:M34"/>
-    <mergeCell ref="C35:M35"/>
-    <mergeCell ref="I139:M141"/>
-    <mergeCell ref="C147:M148"/>
-    <mergeCell ref="C118:G118"/>
-    <mergeCell ref="C119:G119"/>
-    <mergeCell ref="C121:G121"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="A106:M107"/>
-    <mergeCell ref="C15:M15"/>
-    <mergeCell ref="C44:M44"/>
-    <mergeCell ref="C31:M31"/>
-    <mergeCell ref="B96:B98"/>
-    <mergeCell ref="C96:M98"/>
-    <mergeCell ref="A71:M72"/>
-    <mergeCell ref="C19:M20"/>
-    <mergeCell ref="C21:M23"/>
-    <mergeCell ref="C79:M79"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="C32:M33"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="C4:M5"/>
-    <mergeCell ref="C47:M47"/>
-    <mergeCell ref="P201:R201"/>
-    <mergeCell ref="C120:G120"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="H118:M121"/>
-    <mergeCell ref="C13:M14"/>
-    <mergeCell ref="B109:M110"/>
-    <mergeCell ref="C48:M49"/>
-    <mergeCell ref="C58:M58"/>
-    <mergeCell ref="D60:M60"/>
-    <mergeCell ref="C66:M68"/>
-    <mergeCell ref="C45:M46"/>
-    <mergeCell ref="I186:M186"/>
-    <mergeCell ref="I187:M187"/>
-    <mergeCell ref="I188:M188"/>
-    <mergeCell ref="C195:M195"/>
-    <mergeCell ref="A181:M182"/>
-    <mergeCell ref="N173:P173"/>
-    <mergeCell ref="R241:T241"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C16:M18"/>
-    <mergeCell ref="B131:M132"/>
-    <mergeCell ref="I111:M113"/>
-    <mergeCell ref="A210:M211"/>
-    <mergeCell ref="I215:M217"/>
-    <mergeCell ref="B213:M214"/>
-    <mergeCell ref="A134:M135"/>
-    <mergeCell ref="C168:G168"/>
-    <mergeCell ref="H168:M171"/>
-    <mergeCell ref="C169:G169"/>
-    <mergeCell ref="C170:G170"/>
-    <mergeCell ref="C171:G171"/>
-    <mergeCell ref="B137:M138"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -25345,2347 +25575,3218 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F997EAFD-9AFC-4C98-AC33-58FE0B7C6306}">
-  <dimension ref="B2:T175"/>
+  <dimension ref="B1:U240"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B1" s="174" t="s">
+        <v>561</v>
+      </c>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+    </row>
     <row r="2" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B4" s="175" t="s">
+        <v>562</v>
+      </c>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+    </row>
+    <row r="7" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="164" t="s">
         <v>414</v>
       </c>
-      <c r="C2" s="142" t="s">
+      <c r="C7" s="165" t="s">
         <v>415</v>
       </c>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="142"/>
-      <c r="O2" s="142"/>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="142"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="142"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B3" s="141"/>
-      <c r="C3" s="142"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
-      <c r="O3" s="142"/>
-      <c r="P3" s="142"/>
-      <c r="Q3" s="142"/>
-      <c r="R3" s="142"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="142"/>
-    </row>
-    <row r="5" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="143" t="s">
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="165"/>
+      <c r="L7" s="165"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="165"/>
+      <c r="O7" s="165"/>
+      <c r="P7" s="165"/>
+      <c r="Q7" s="165"/>
+      <c r="R7" s="165"/>
+      <c r="S7" s="165"/>
+      <c r="T7" s="165"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B8" s="164"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="165"/>
+      <c r="L8" s="165"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="165"/>
+      <c r="R8" s="165"/>
+      <c r="S8" s="165"/>
+      <c r="T8" s="165"/>
+    </row>
+    <row r="10" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B10" s="166" t="s">
         <v>416</v>
       </c>
-      <c r="C5" s="143"/>
-      <c r="D5" s="142" t="s">
+      <c r="C10" s="166"/>
+      <c r="D10" s="165" t="s">
         <v>453</v>
       </c>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="142"/>
-      <c r="N5" s="142"/>
-      <c r="O5" s="142"/>
-      <c r="P5" s="142"/>
-      <c r="Q5" s="142"/>
-      <c r="R5" s="142"/>
-      <c r="S5" s="142"/>
-      <c r="T5" s="142"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B6" s="143"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="142"/>
-      <c r="E6" s="142"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="142"/>
-      <c r="I6" s="142"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="142"/>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="142"/>
-      <c r="Q6" s="142"/>
-      <c r="R6" s="142"/>
-      <c r="S6" s="142"/>
-      <c r="T6" s="142"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B8" s="15"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="146" t="s">
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="165"/>
+      <c r="L10" s="165"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="165"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="165"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="165"/>
+      <c r="K11" s="165"/>
+      <c r="L11" s="165"/>
+      <c r="M11" s="165"/>
+      <c r="N11" s="165"/>
+      <c r="O11" s="165"/>
+      <c r="P11" s="165"/>
+      <c r="Q11" s="165"/>
+      <c r="R11" s="165"/>
+      <c r="S11" s="165"/>
+      <c r="T11" s="165"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B13" s="15"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="158" t="s">
         <v>419</v>
       </c>
-      <c r="E8" s="147"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="40" t="s">
+      <c r="E13" s="159"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="40" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B9" s="131" t="s">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B14" s="169" t="s">
         <v>417</v>
       </c>
-      <c r="C9" s="132"/>
-      <c r="D9" s="133" t="s">
+      <c r="C14" s="170"/>
+      <c r="D14" s="151" t="s">
         <v>418</v>
       </c>
-      <c r="E9" s="134"/>
-      <c r="F9" s="135"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B10" s="15"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="133" t="s">
+      <c r="E14" s="152"/>
+      <c r="F14" s="153"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B15" s="15"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="151" t="s">
         <v>420</v>
       </c>
-      <c r="E10" s="134"/>
-      <c r="F10" s="135"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D11" s="133" t="s">
+      <c r="E15" s="152"/>
+      <c r="F15" s="153"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D16" s="151" t="s">
         <v>421</v>
       </c>
-      <c r="E11" s="134"/>
-      <c r="F11" s="135"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D12" s="133" t="s">
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D17" s="151" t="s">
         <v>471</v>
       </c>
-      <c r="E12" s="134"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="40" t="s">
+      <c r="E17" s="152"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="40" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="145" t="s">
+    <row r="18" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" spans="2:20" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="B19" s="168" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C19" s="167" t="s">
         <v>424</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B15" s="141"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="144"/>
-      <c r="Q15" s="144"/>
-      <c r="R15" s="144"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="144"/>
-    </row>
-    <row r="17" spans="2:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="140" t="s">
+      <c r="D19" s="167"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="167"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="167"/>
+      <c r="L19" s="167"/>
+      <c r="M19" s="167"/>
+      <c r="N19" s="167"/>
+      <c r="O19" s="167"/>
+      <c r="P19" s="167"/>
+      <c r="Q19" s="167"/>
+      <c r="R19" s="167"/>
+      <c r="S19" s="167"/>
+      <c r="T19" s="167"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B20" s="164"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
+      <c r="O20" s="167"/>
+      <c r="P20" s="167"/>
+      <c r="Q20" s="167"/>
+      <c r="R20" s="167"/>
+      <c r="S20" s="167"/>
+      <c r="T20" s="167"/>
+    </row>
+    <row r="22" spans="2:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="163" t="s">
         <v>425</v>
       </c>
-      <c r="C17" s="140"/>
-      <c r="D17" s="138" t="s">
+      <c r="C22" s="163"/>
+      <c r="D22" s="161" t="s">
         <v>426</v>
       </c>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138"/>
-      <c r="R17" s="138"/>
-      <c r="S17" s="138"/>
-      <c r="T17" s="138"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B18" s="140"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
-      <c r="S18" s="138"/>
-      <c r="T18" s="138"/>
-    </row>
-    <row r="20" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="149" t="s">
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="161"/>
+      <c r="M22" s="161"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="161"/>
+      <c r="P22" s="161"/>
+      <c r="Q22" s="161"/>
+      <c r="R22" s="161"/>
+      <c r="S22" s="161"/>
+      <c r="T22" s="161"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B23" s="163"/>
+      <c r="C23" s="163"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="161"/>
+      <c r="K23" s="161"/>
+      <c r="L23" s="161"/>
+      <c r="M23" s="161"/>
+      <c r="N23" s="161"/>
+      <c r="O23" s="161"/>
+      <c r="P23" s="161"/>
+      <c r="Q23" s="161"/>
+      <c r="R23" s="161"/>
+      <c r="S23" s="161"/>
+      <c r="T23" s="161"/>
+    </row>
+    <row r="25" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="171" t="s">
         <v>450</v>
       </c>
-      <c r="C20" s="149"/>
-      <c r="D20" s="146" t="s">
+      <c r="C25" s="171"/>
+      <c r="D25" s="158" t="s">
         <v>438</v>
       </c>
-      <c r="E20" s="147"/>
-      <c r="F20" s="148"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B21" s="149"/>
-      <c r="C21" s="149"/>
-      <c r="D21" s="133" t="s">
+      <c r="E25" s="159"/>
+      <c r="F25" s="160"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B26" s="171"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="151" t="s">
         <v>439</v>
       </c>
-      <c r="E21" s="134"/>
-      <c r="F21" s="135"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="133" t="s">
+      <c r="E26" s="152"/>
+      <c r="F26" s="153"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B27" s="171"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="151" t="s">
         <v>440</v>
       </c>
-      <c r="E22" s="134"/>
-      <c r="F22" s="135"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B23" s="103"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="133" t="s">
+      <c r="E27" s="152"/>
+      <c r="F27" s="153"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B28" s="103"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="151" t="s">
         <v>441</v>
       </c>
-      <c r="E23" s="134"/>
-      <c r="F23" s="135"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D24" s="133" t="s">
+      <c r="E28" s="152"/>
+      <c r="F28" s="153"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D29" s="151" t="s">
         <v>442</v>
       </c>
-      <c r="E24" s="134"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="40" t="s">
+      <c r="E29" s="152"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="40" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D25" s="133" t="s">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D30" s="151" t="s">
         <v>443</v>
       </c>
-      <c r="E25" s="134"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="40" t="s">
+      <c r="E30" s="152"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="40" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D26" s="133" t="s">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D31" s="151" t="s">
         <v>444</v>
       </c>
-      <c r="E26" s="134"/>
-      <c r="F26" s="135"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B28" s="152" t="s">
+      <c r="E31" s="152"/>
+      <c r="F31" s="153"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+    </row>
+    <row r="33" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="126" t="s">
         <v>447</v>
       </c>
-      <c r="C28" s="153"/>
-      <c r="D28" s="138" t="s">
+      <c r="C33" s="127"/>
+      <c r="D33" s="161" t="s">
         <v>449</v>
       </c>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138"/>
-      <c r="O28" s="138"/>
-      <c r="P28" s="138"/>
-      <c r="Q28" s="138"/>
-      <c r="R28" s="138"/>
-      <c r="S28" s="138"/>
-      <c r="T28" s="138"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B29" s="153" t="s">
+      <c r="E33" s="161"/>
+      <c r="F33" s="161"/>
+      <c r="G33" s="161"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="161"/>
+      <c r="K33" s="161"/>
+      <c r="L33" s="161"/>
+      <c r="M33" s="161"/>
+      <c r="N33" s="161"/>
+      <c r="O33" s="161"/>
+      <c r="P33" s="161"/>
+      <c r="Q33" s="161"/>
+      <c r="R33" s="161"/>
+      <c r="S33" s="161"/>
+      <c r="T33" s="161"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B34" s="127" t="s">
         <v>448</v>
       </c>
-      <c r="C29" s="153"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="138"/>
-      <c r="N29" s="138"/>
-      <c r="O29" s="138"/>
-      <c r="P29" s="138"/>
-      <c r="Q29" s="138"/>
-      <c r="R29" s="138"/>
-      <c r="S29" s="138"/>
-      <c r="T29" s="138"/>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B31" s="150" t="s">
+      <c r="C34" s="127"/>
+      <c r="D34" s="161"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="161"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="161"/>
+      <c r="J34" s="161"/>
+      <c r="K34" s="161"/>
+      <c r="L34" s="161"/>
+      <c r="M34" s="161"/>
+      <c r="N34" s="161"/>
+      <c r="O34" s="161"/>
+      <c r="P34" s="161"/>
+      <c r="Q34" s="161"/>
+      <c r="R34" s="161"/>
+      <c r="S34" s="161"/>
+      <c r="T34" s="161"/>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B36" s="172" t="s">
         <v>427</v>
       </c>
-      <c r="C31" s="151"/>
-      <c r="D31" s="146" t="s">
+      <c r="C36" s="173"/>
+      <c r="D36" s="158" t="s">
         <v>428</v>
       </c>
-      <c r="E31" s="147"/>
-      <c r="F31" s="148"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D32" s="133" t="s">
+      <c r="E36" s="159"/>
+      <c r="F36" s="160"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D37" s="151" t="s">
         <v>429</v>
       </c>
-      <c r="E32" s="134"/>
-      <c r="F32" s="135"/>
-      <c r="G32" s="40" t="s">
+      <c r="E37" s="152"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="40" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B33" s="15"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="133" t="s">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B38" s="15"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="151" t="s">
         <v>431</v>
       </c>
-      <c r="E33" s="134"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="40" t="s">
+      <c r="E38" s="152"/>
+      <c r="F38" s="153"/>
+      <c r="G38" s="40" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D34" s="133" t="s">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D39" s="151" t="s">
         <v>432</v>
       </c>
-      <c r="E34" s="134"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="40" t="s">
+      <c r="E39" s="152"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="40" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D35" s="133" t="s">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D40" s="151" t="s">
         <v>434</v>
       </c>
-      <c r="E35" s="134"/>
-      <c r="F35" s="135"/>
-      <c r="G35" s="40" t="s">
+      <c r="E40" s="152"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="40" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D36" s="133" t="s">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D41" s="151" t="s">
         <v>436</v>
       </c>
-      <c r="E36" s="134"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="40" t="s">
+      <c r="E41" s="152"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="40" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="39" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="140" t="s">
+    <row r="44" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B44" s="163" t="s">
         <v>452</v>
       </c>
-      <c r="C39" s="140"/>
-      <c r="D39" s="138" t="s">
+      <c r="C44" s="163"/>
+      <c r="D44" s="161" t="s">
         <v>451</v>
       </c>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
-      <c r="L39" s="138"/>
-      <c r="M39" s="138"/>
-      <c r="N39" s="138"/>
-      <c r="O39" s="138"/>
-      <c r="P39" s="138"/>
-      <c r="Q39" s="138"/>
-      <c r="R39" s="138"/>
-      <c r="S39" s="138"/>
-      <c r="T39" s="138"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B40" s="140"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="138"/>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="138"/>
-      <c r="L40" s="138"/>
-      <c r="M40" s="138"/>
-      <c r="N40" s="138"/>
-      <c r="O40" s="138"/>
-      <c r="P40" s="138"/>
-      <c r="Q40" s="138"/>
-      <c r="R40" s="138"/>
-      <c r="S40" s="138"/>
-      <c r="T40" s="138"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B41" s="140"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
-      <c r="K41" s="138"/>
-      <c r="L41" s="138"/>
-      <c r="M41" s="138"/>
-      <c r="N41" s="138"/>
-      <c r="O41" s="138"/>
-      <c r="P41" s="138"/>
-      <c r="Q41" s="138"/>
-      <c r="R41" s="138"/>
-      <c r="S41" s="138"/>
-      <c r="T41" s="138"/>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D43" s="106" t="s">
+      <c r="E44" s="161"/>
+      <c r="F44" s="161"/>
+      <c r="G44" s="161"/>
+      <c r="H44" s="161"/>
+      <c r="I44" s="161"/>
+      <c r="J44" s="161"/>
+      <c r="K44" s="161"/>
+      <c r="L44" s="161"/>
+      <c r="M44" s="161"/>
+      <c r="N44" s="161"/>
+      <c r="O44" s="161"/>
+      <c r="P44" s="161"/>
+      <c r="Q44" s="161"/>
+      <c r="R44" s="161"/>
+      <c r="S44" s="161"/>
+      <c r="T44" s="161"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B45" s="163"/>
+      <c r="C45" s="163"/>
+      <c r="D45" s="161"/>
+      <c r="E45" s="161"/>
+      <c r="F45" s="161"/>
+      <c r="G45" s="161"/>
+      <c r="H45" s="161"/>
+      <c r="I45" s="161"/>
+      <c r="J45" s="161"/>
+      <c r="K45" s="161"/>
+      <c r="L45" s="161"/>
+      <c r="M45" s="161"/>
+      <c r="N45" s="161"/>
+      <c r="O45" s="161"/>
+      <c r="P45" s="161"/>
+      <c r="Q45" s="161"/>
+      <c r="R45" s="161"/>
+      <c r="S45" s="161"/>
+      <c r="T45" s="161"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B46" s="163"/>
+      <c r="C46" s="163"/>
+      <c r="D46" s="161"/>
+      <c r="E46" s="161"/>
+      <c r="F46" s="161"/>
+      <c r="G46" s="161"/>
+      <c r="H46" s="161"/>
+      <c r="I46" s="161"/>
+      <c r="J46" s="161"/>
+      <c r="K46" s="161"/>
+      <c r="L46" s="161"/>
+      <c r="M46" s="161"/>
+      <c r="N46" s="161"/>
+      <c r="O46" s="161"/>
+      <c r="P46" s="161"/>
+      <c r="Q46" s="161"/>
+      <c r="R46" s="161"/>
+      <c r="S46" s="161"/>
+      <c r="T46" s="161"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D48" s="106" t="s">
         <v>455</v>
       </c>
-      <c r="E43" s="106"/>
-      <c r="F43" s="107" t="s">
+      <c r="E48" s="106"/>
+      <c r="F48" s="107" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D44" s="106" t="s">
+    <row r="49" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D49" s="106" t="s">
         <v>456</v>
       </c>
-      <c r="E44" s="106"/>
-      <c r="F44" s="107" t="s">
+      <c r="E49" s="106"/>
+      <c r="F49" s="107" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="45" spans="2:20" ht="20.25" x14ac:dyDescent="0.5">
-      <c r="B45" s="137" t="s">
+    <row r="50" spans="2:20" ht="20.25" x14ac:dyDescent="0.5">
+      <c r="B50" s="189" t="s">
         <v>454</v>
       </c>
-      <c r="C45" s="137"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="107"/>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D46" s="106" t="s">
+      <c r="C50" s="189"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="107"/>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D51" s="106" t="s">
         <v>457</v>
       </c>
-      <c r="E46" s="106"/>
-      <c r="F46" s="107" t="s">
+      <c r="E51" s="106"/>
+      <c r="F51" s="107" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D47" s="136" t="s">
+    <row r="52" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D52" s="188" t="s">
         <v>458</v>
       </c>
-      <c r="E47" s="136"/>
-      <c r="F47" s="107" t="s">
+      <c r="E52" s="188"/>
+      <c r="F52" s="107" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B49" s="139" t="s">
+    <row r="54" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B54" s="162" t="s">
         <v>465</v>
       </c>
-      <c r="C49" s="139"/>
-      <c r="D49" s="138" t="s">
+      <c r="C54" s="162"/>
+      <c r="D54" s="161" t="s">
         <v>464</v>
       </c>
-      <c r="E49" s="138"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="138"/>
-      <c r="H49" s="138"/>
-      <c r="I49" s="138"/>
-      <c r="J49" s="138"/>
-      <c r="K49" s="138"/>
-      <c r="L49" s="138"/>
-      <c r="M49" s="138"/>
-      <c r="N49" s="138"/>
-      <c r="O49" s="138"/>
-      <c r="P49" s="138"/>
-      <c r="Q49" s="138"/>
-      <c r="R49" s="138"/>
-      <c r="S49" s="138"/>
-      <c r="T49" s="138"/>
-    </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B50" s="139"/>
-      <c r="C50" s="139"/>
-      <c r="D50" s="138"/>
-      <c r="E50" s="138"/>
-      <c r="F50" s="138"/>
-      <c r="G50" s="138"/>
-      <c r="H50" s="138"/>
-      <c r="I50" s="138"/>
-      <c r="J50" s="138"/>
-      <c r="K50" s="138"/>
-      <c r="L50" s="138"/>
-      <c r="M50" s="138"/>
-      <c r="N50" s="138"/>
-      <c r="O50" s="138"/>
-      <c r="P50" s="138"/>
-      <c r="Q50" s="138"/>
-      <c r="R50" s="138"/>
-      <c r="S50" s="138"/>
-      <c r="T50" s="138"/>
-    </row>
-    <row r="51" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="17" t="s">
+      <c r="E54" s="161"/>
+      <c r="F54" s="161"/>
+      <c r="G54" s="161"/>
+      <c r="H54" s="161"/>
+      <c r="I54" s="161"/>
+      <c r="J54" s="161"/>
+      <c r="K54" s="161"/>
+      <c r="L54" s="161"/>
+      <c r="M54" s="161"/>
+      <c r="N54" s="161"/>
+      <c r="O54" s="161"/>
+      <c r="P54" s="161"/>
+      <c r="Q54" s="161"/>
+      <c r="R54" s="161"/>
+      <c r="S54" s="161"/>
+      <c r="T54" s="161"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B55" s="162"/>
+      <c r="C55" s="162"/>
+      <c r="D55" s="161"/>
+      <c r="E55" s="161"/>
+      <c r="F55" s="161"/>
+      <c r="G55" s="161"/>
+      <c r="H55" s="161"/>
+      <c r="I55" s="161"/>
+      <c r="J55" s="161"/>
+      <c r="K55" s="161"/>
+      <c r="L55" s="161"/>
+      <c r="M55" s="161"/>
+      <c r="N55" s="161"/>
+      <c r="O55" s="161"/>
+      <c r="P55" s="161"/>
+      <c r="Q55" s="161"/>
+      <c r="R55" s="161"/>
+      <c r="S55" s="161"/>
+      <c r="T55" s="161"/>
+    </row>
+    <row r="56" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="57" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C52" s="115" t="s">
+      <c r="C57" s="143" t="s">
         <v>466</v>
       </c>
-      <c r="D52" s="115"/>
-      <c r="E52" s="115"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="115"/>
-      <c r="H52" s="115"/>
-      <c r="I52" s="115"/>
-      <c r="J52" s="115"/>
-      <c r="K52" s="115"/>
-      <c r="L52" s="115"/>
-      <c r="M52" s="115"/>
-      <c r="N52" s="115"/>
-      <c r="O52" s="115"/>
-      <c r="P52" s="115"/>
-      <c r="Q52" s="115"/>
-      <c r="R52" s="115"/>
-      <c r="S52" s="115"/>
-      <c r="T52" s="115"/>
-    </row>
-    <row r="53" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5"/>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B54" s="139" t="s">
+      <c r="D57" s="143"/>
+      <c r="E57" s="143"/>
+      <c r="F57" s="143"/>
+      <c r="G57" s="143"/>
+      <c r="H57" s="143"/>
+      <c r="I57" s="143"/>
+      <c r="J57" s="143"/>
+      <c r="K57" s="143"/>
+      <c r="L57" s="143"/>
+      <c r="M57" s="143"/>
+      <c r="N57" s="143"/>
+      <c r="O57" s="143"/>
+      <c r="P57" s="143"/>
+      <c r="Q57" s="143"/>
+      <c r="R57" s="143"/>
+      <c r="S57" s="143"/>
+      <c r="T57" s="143"/>
+    </row>
+    <row r="58" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="59" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B59" s="162" t="s">
         <v>467</v>
       </c>
-      <c r="C54" s="139"/>
-      <c r="D54" s="138" t="s">
+      <c r="C59" s="162"/>
+      <c r="D59" s="161" t="s">
         <v>468</v>
       </c>
-      <c r="E54" s="138"/>
-      <c r="F54" s="138"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="138"/>
-      <c r="I54" s="138"/>
-      <c r="J54" s="138"/>
-      <c r="K54" s="138"/>
-      <c r="L54" s="138"/>
-      <c r="M54" s="138"/>
-      <c r="N54" s="138"/>
-      <c r="O54" s="138"/>
-      <c r="P54" s="138"/>
-      <c r="Q54" s="138"/>
-      <c r="R54" s="138"/>
-      <c r="S54" s="138"/>
-      <c r="T54" s="138"/>
-    </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
-      <c r="D55" s="138"/>
-      <c r="E55" s="138"/>
-      <c r="F55" s="138"/>
-      <c r="G55" s="138"/>
-      <c r="H55" s="138"/>
-      <c r="I55" s="138"/>
-      <c r="J55" s="138"/>
-      <c r="K55" s="138"/>
-      <c r="L55" s="138"/>
-      <c r="M55" s="138"/>
-      <c r="N55" s="138"/>
-      <c r="O55" s="138"/>
-      <c r="P55" s="138"/>
-      <c r="Q55" s="138"/>
-      <c r="R55" s="138"/>
-      <c r="S55" s="138"/>
-      <c r="T55" s="138"/>
-    </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B58" s="15"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="128" t="s">
+      <c r="E59" s="161"/>
+      <c r="F59" s="161"/>
+      <c r="G59" s="161"/>
+      <c r="H59" s="161"/>
+      <c r="I59" s="161"/>
+      <c r="J59" s="161"/>
+      <c r="K59" s="161"/>
+      <c r="L59" s="161"/>
+      <c r="M59" s="161"/>
+      <c r="N59" s="161"/>
+      <c r="O59" s="161"/>
+      <c r="P59" s="161"/>
+      <c r="Q59" s="161"/>
+      <c r="R59" s="161"/>
+      <c r="S59" s="161"/>
+      <c r="T59" s="161"/>
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B60" s="162"/>
+      <c r="C60" s="162"/>
+      <c r="D60" s="161"/>
+      <c r="E60" s="161"/>
+      <c r="F60" s="161"/>
+      <c r="G60" s="161"/>
+      <c r="H60" s="161"/>
+      <c r="I60" s="161"/>
+      <c r="J60" s="161"/>
+      <c r="K60" s="161"/>
+      <c r="L60" s="161"/>
+      <c r="M60" s="161"/>
+      <c r="N60" s="161"/>
+      <c r="O60" s="161"/>
+      <c r="P60" s="161"/>
+      <c r="Q60" s="161"/>
+      <c r="R60" s="161"/>
+      <c r="S60" s="161"/>
+      <c r="T60" s="161"/>
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B63" s="15"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="176" t="s">
         <v>470</v>
       </c>
-      <c r="E58" s="129"/>
-      <c r="F58" s="129"/>
-      <c r="G58" s="130"/>
-    </row>
-    <row r="59" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D59" s="128" t="s">
+      <c r="E63" s="176"/>
+      <c r="F63" s="176"/>
+      <c r="G63" s="176"/>
+      <c r="H63" s="176"/>
+    </row>
+    <row r="64" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D64" s="176" t="s">
         <v>472</v>
       </c>
-      <c r="E59" s="129"/>
-      <c r="F59" s="129"/>
-      <c r="G59" s="130"/>
-    </row>
-    <row r="60" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B60" s="131" t="s">
+      <c r="E64" s="176"/>
+      <c r="F64" s="176"/>
+      <c r="G64" s="176"/>
+      <c r="H64" s="176"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="B65" s="169" t="s">
         <v>469</v>
       </c>
-      <c r="C60" s="132"/>
-      <c r="D60" s="128" t="s">
+      <c r="C65" s="170"/>
+      <c r="D65" s="176" t="s">
         <v>473</v>
       </c>
-      <c r="E60" s="129"/>
-      <c r="F60" s="129"/>
-      <c r="G60" s="130"/>
-    </row>
-    <row r="61" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D61" s="128" t="s">
+      <c r="E65" s="176"/>
+      <c r="F65" s="176"/>
+      <c r="G65" s="176"/>
+      <c r="H65" s="176"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="D66" s="176" t="s">
         <v>474</v>
       </c>
-      <c r="E61" s="129"/>
-      <c r="F61" s="129"/>
-      <c r="G61" s="130"/>
-    </row>
-    <row r="62" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D62" s="128" t="s">
+      <c r="E66" s="176"/>
+      <c r="F66" s="176"/>
+      <c r="G66" s="176"/>
+      <c r="H66" s="176"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="D67" s="176" t="s">
         <v>475</v>
       </c>
-      <c r="E62" s="129"/>
-      <c r="F62" s="129"/>
-      <c r="G62" s="130"/>
-    </row>
-    <row r="64" spans="2:20" ht="22.5" x14ac:dyDescent="0.6">
-      <c r="B64" s="126" t="s">
+      <c r="E67" s="176"/>
+      <c r="F67" s="176"/>
+      <c r="G67" s="176"/>
+      <c r="H67" s="176"/>
+    </row>
+    <row r="69" spans="2:19" ht="22.5" x14ac:dyDescent="0.6">
+      <c r="B69" s="184" t="s">
         <v>476</v>
       </c>
-      <c r="C64" s="126"/>
-      <c r="D64" s="126"/>
-      <c r="E64" s="126"/>
-      <c r="F64" s="126"/>
-    </row>
-    <row r="65" spans="2:19" ht="25.5" x14ac:dyDescent="0.6">
-      <c r="B65" s="109" t="s">
+      <c r="C69" s="184"/>
+      <c r="D69" s="184"/>
+      <c r="E69" s="184"/>
+      <c r="F69" s="184"/>
+    </row>
+    <row r="70" spans="2:19" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B70" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="124" t="s">
+      <c r="C70" s="182" t="s">
         <v>59</v>
       </c>
-      <c r="D65" s="124"/>
-      <c r="E65" s="124"/>
-      <c r="F65" s="124"/>
-      <c r="G65" s="124"/>
-      <c r="H65" s="124"/>
-      <c r="I65" s="124"/>
-      <c r="J65" s="124"/>
-      <c r="K65" s="125" t="s">
+      <c r="D70" s="182"/>
+      <c r="E70" s="182"/>
+      <c r="F70" s="182"/>
+      <c r="G70" s="182"/>
+      <c r="H70" s="182"/>
+      <c r="I70" s="182"/>
+      <c r="J70" s="182"/>
+      <c r="K70" s="183" t="s">
         <v>482</v>
       </c>
-      <c r="L65" s="125"/>
-      <c r="M65" s="125"/>
-      <c r="N65" s="125"/>
-      <c r="O65" s="125"/>
-      <c r="P65" s="125"/>
-      <c r="Q65" s="125"/>
-      <c r="R65" s="125"/>
-      <c r="S65" s="125"/>
-    </row>
-    <row r="66" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B66" s="108">
-        <v>1</v>
-      </c>
-      <c r="C66" s="122" t="s">
-        <v>477</v>
-      </c>
-      <c r="D66" s="123"/>
-      <c r="E66" s="123"/>
-      <c r="F66" s="123"/>
-      <c r="G66" s="123"/>
-      <c r="H66" s="123"/>
-      <c r="I66" s="123"/>
-      <c r="J66" s="123"/>
-      <c r="K66" s="111" t="s">
-        <v>490</v>
-      </c>
-      <c r="L66" s="110"/>
-      <c r="M66" s="110"/>
-      <c r="N66" s="110"/>
-      <c r="O66" s="110"/>
-      <c r="P66" s="110"/>
-      <c r="Q66" s="110"/>
-      <c r="R66" s="110"/>
-      <c r="S66" s="110"/>
-    </row>
-    <row r="67" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B67" s="108">
-        <v>2</v>
-      </c>
-      <c r="C67" s="120" t="s">
-        <v>478</v>
-      </c>
-      <c r="D67" s="121"/>
-      <c r="E67" s="121"/>
-      <c r="F67" s="121"/>
-      <c r="G67" s="121"/>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
-      <c r="J67" s="121"/>
-      <c r="K67" s="112" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="68" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B68" s="108">
-        <v>3</v>
-      </c>
-      <c r="C68" s="122" t="s">
-        <v>479</v>
-      </c>
-      <c r="D68" s="123"/>
-      <c r="E68" s="123"/>
-      <c r="F68" s="123"/>
-      <c r="G68" s="123"/>
-      <c r="H68" s="123"/>
-      <c r="I68" s="123"/>
-      <c r="J68" s="123"/>
-      <c r="K68" s="111" t="s">
-        <v>485</v>
-      </c>
-      <c r="L68" s="110"/>
-      <c r="M68" s="110"/>
-      <c r="N68" s="110"/>
-      <c r="O68" s="110"/>
-      <c r="P68" s="110"/>
-      <c r="Q68" s="110"/>
-      <c r="R68" s="110"/>
-      <c r="S68" s="110"/>
-    </row>
-    <row r="69" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B69" s="108">
-        <v>4</v>
-      </c>
-      <c r="C69" s="120" t="s">
-        <v>483</v>
-      </c>
-      <c r="D69" s="121"/>
-      <c r="E69" s="121"/>
-      <c r="F69" s="121"/>
-      <c r="G69" s="121"/>
-      <c r="H69" s="121"/>
-      <c r="I69" s="121"/>
-      <c r="J69" s="121"/>
-      <c r="K69" s="112" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="70" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B70" s="108">
-        <v>5</v>
-      </c>
-      <c r="C70" s="122" t="s">
-        <v>480</v>
-      </c>
-      <c r="D70" s="123"/>
-      <c r="E70" s="123"/>
-      <c r="F70" s="123"/>
-      <c r="G70" s="123"/>
-      <c r="H70" s="123"/>
-      <c r="I70" s="123"/>
-      <c r="J70" s="123"/>
-      <c r="K70" s="111" t="s">
-        <v>487</v>
-      </c>
-      <c r="L70" s="110"/>
-      <c r="M70" s="110"/>
-      <c r="N70" s="110"/>
-      <c r="O70" s="110"/>
-      <c r="P70" s="110"/>
-      <c r="Q70" s="110"/>
-      <c r="R70" s="110"/>
-      <c r="S70" s="110"/>
+      <c r="L70" s="183"/>
+      <c r="M70" s="183"/>
+      <c r="N70" s="183"/>
+      <c r="O70" s="183"/>
+      <c r="P70" s="183"/>
+      <c r="Q70" s="183"/>
+      <c r="R70" s="183"/>
+      <c r="S70" s="183"/>
     </row>
     <row r="71" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
       <c r="B71" s="108">
-        <v>6</v>
-      </c>
-      <c r="C71" s="120" t="s">
-        <v>481</v>
-      </c>
-      <c r="D71" s="121"/>
-      <c r="E71" s="121"/>
-      <c r="F71" s="121"/>
-      <c r="G71" s="121"/>
-      <c r="H71" s="121"/>
-      <c r="I71" s="121"/>
-      <c r="J71" s="121"/>
-      <c r="K71" s="112" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="74" spans="2:19" ht="22.5" x14ac:dyDescent="0.6">
-      <c r="B74" s="126" t="s">
-        <v>489</v>
-      </c>
-      <c r="C74" s="126"/>
-      <c r="D74" s="126"/>
-      <c r="E74" s="126"/>
-      <c r="F74" s="126"/>
-    </row>
-    <row r="75" spans="2:19" ht="25.5" x14ac:dyDescent="0.6">
-      <c r="B75" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="C75" s="124" t="s">
-        <v>59</v>
-      </c>
-      <c r="D75" s="124"/>
-      <c r="E75" s="124"/>
-      <c r="F75" s="124"/>
-      <c r="G75" s="124"/>
-      <c r="H75" s="124"/>
-      <c r="I75" s="124"/>
-      <c r="J75" s="124"/>
-      <c r="K75" s="125" t="s">
-        <v>482</v>
-      </c>
-      <c r="L75" s="125"/>
-      <c r="M75" s="125"/>
-      <c r="N75" s="125"/>
-      <c r="O75" s="125"/>
-      <c r="P75" s="125"/>
-      <c r="Q75" s="125"/>
-      <c r="R75" s="125"/>
-      <c r="S75" s="125"/>
+        <v>1</v>
+      </c>
+      <c r="C71" s="180" t="s">
+        <v>477</v>
+      </c>
+      <c r="D71" s="181"/>
+      <c r="E71" s="181"/>
+      <c r="F71" s="181"/>
+      <c r="G71" s="181"/>
+      <c r="H71" s="181"/>
+      <c r="I71" s="181"/>
+      <c r="J71" s="181"/>
+      <c r="K71" s="111" t="s">
+        <v>490</v>
+      </c>
+      <c r="L71" s="110"/>
+      <c r="M71" s="110"/>
+      <c r="N71" s="110"/>
+      <c r="O71" s="110"/>
+      <c r="P71" s="110"/>
+      <c r="Q71" s="110"/>
+      <c r="R71" s="110"/>
+      <c r="S71" s="110"/>
+    </row>
+    <row r="72" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B72" s="108">
+        <v>2</v>
+      </c>
+      <c r="C72" s="178" t="s">
+        <v>478</v>
+      </c>
+      <c r="D72" s="179"/>
+      <c r="E72" s="179"/>
+      <c r="F72" s="179"/>
+      <c r="G72" s="179"/>
+      <c r="H72" s="179"/>
+      <c r="I72" s="179"/>
+      <c r="J72" s="179"/>
+      <c r="K72" s="112" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B73" s="108">
+        <v>3</v>
+      </c>
+      <c r="C73" s="180" t="s">
+        <v>479</v>
+      </c>
+      <c r="D73" s="181"/>
+      <c r="E73" s="181"/>
+      <c r="F73" s="181"/>
+      <c r="G73" s="181"/>
+      <c r="H73" s="181"/>
+      <c r="I73" s="181"/>
+      <c r="J73" s="181"/>
+      <c r="K73" s="111" t="s">
+        <v>485</v>
+      </c>
+      <c r="L73" s="110"/>
+      <c r="M73" s="110"/>
+      <c r="N73" s="110"/>
+      <c r="O73" s="110"/>
+      <c r="P73" s="110"/>
+      <c r="Q73" s="110"/>
+      <c r="R73" s="110"/>
+      <c r="S73" s="110"/>
+    </row>
+    <row r="74" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B74" s="108">
+        <v>4</v>
+      </c>
+      <c r="C74" s="178" t="s">
+        <v>483</v>
+      </c>
+      <c r="D74" s="179"/>
+      <c r="E74" s="179"/>
+      <c r="F74" s="179"/>
+      <c r="G74" s="179"/>
+      <c r="H74" s="179"/>
+      <c r="I74" s="179"/>
+      <c r="J74" s="179"/>
+      <c r="K74" s="112" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B75" s="108">
+        <v>5</v>
+      </c>
+      <c r="C75" s="180" t="s">
+        <v>480</v>
+      </c>
+      <c r="D75" s="181"/>
+      <c r="E75" s="181"/>
+      <c r="F75" s="181"/>
+      <c r="G75" s="181"/>
+      <c r="H75" s="181"/>
+      <c r="I75" s="181"/>
+      <c r="J75" s="181"/>
+      <c r="K75" s="111" t="s">
+        <v>487</v>
+      </c>
+      <c r="L75" s="110"/>
+      <c r="M75" s="110"/>
+      <c r="N75" s="110"/>
+      <c r="O75" s="110"/>
+      <c r="P75" s="110"/>
+      <c r="Q75" s="110"/>
+      <c r="R75" s="110"/>
+      <c r="S75" s="110"/>
     </row>
     <row r="76" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
       <c r="B76" s="108">
+        <v>6</v>
+      </c>
+      <c r="C76" s="178" t="s">
+        <v>481</v>
+      </c>
+      <c r="D76" s="179"/>
+      <c r="E76" s="179"/>
+      <c r="F76" s="179"/>
+      <c r="G76" s="179"/>
+      <c r="H76" s="179"/>
+      <c r="I76" s="179"/>
+      <c r="J76" s="179"/>
+      <c r="K76" s="112" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" ht="22.5" x14ac:dyDescent="0.6">
+      <c r="B79" s="184" t="s">
+        <v>489</v>
+      </c>
+      <c r="C79" s="184"/>
+      <c r="D79" s="184"/>
+      <c r="E79" s="184"/>
+      <c r="F79" s="184"/>
+    </row>
+    <row r="80" spans="2:19" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B80" s="109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" s="182"/>
+      <c r="E80" s="182"/>
+      <c r="F80" s="182"/>
+      <c r="G80" s="182"/>
+      <c r="H80" s="182"/>
+      <c r="I80" s="182"/>
+      <c r="J80" s="182"/>
+      <c r="K80" s="183" t="s">
+        <v>482</v>
+      </c>
+      <c r="L80" s="183"/>
+      <c r="M80" s="183"/>
+      <c r="N80" s="183"/>
+      <c r="O80" s="183"/>
+      <c r="P80" s="183"/>
+      <c r="Q80" s="183"/>
+      <c r="R80" s="183"/>
+      <c r="S80" s="183"/>
+    </row>
+    <row r="81" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B81" s="108">
         <v>1</v>
       </c>
-      <c r="C76" s="122" t="s">
+      <c r="C81" s="180" t="s">
         <v>491</v>
       </c>
-      <c r="D76" s="123"/>
-      <c r="E76" s="123"/>
-      <c r="F76" s="123"/>
-      <c r="G76" s="123"/>
-      <c r="H76" s="123"/>
-      <c r="I76" s="123"/>
-      <c r="J76" s="123"/>
-      <c r="K76" s="111" t="s">
+      <c r="D81" s="181"/>
+      <c r="E81" s="181"/>
+      <c r="F81" s="181"/>
+      <c r="G81" s="181"/>
+      <c r="H81" s="181"/>
+      <c r="I81" s="181"/>
+      <c r="J81" s="181"/>
+      <c r="K81" s="111" t="s">
         <v>496</v>
       </c>
-      <c r="L76" s="110"/>
-      <c r="M76" s="110"/>
-      <c r="N76" s="110"/>
-      <c r="O76" s="110"/>
-      <c r="P76" s="110"/>
-      <c r="Q76" s="110"/>
-      <c r="R76" s="110"/>
-      <c r="S76" s="110"/>
-    </row>
-    <row r="77" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B77" s="108">
+      <c r="L81" s="110"/>
+      <c r="M81" s="110"/>
+      <c r="N81" s="110"/>
+      <c r="O81" s="110"/>
+      <c r="P81" s="110"/>
+      <c r="Q81" s="110"/>
+      <c r="R81" s="110"/>
+      <c r="S81" s="110"/>
+    </row>
+    <row r="82" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B82" s="108">
         <v>2</v>
       </c>
-      <c r="C77" s="120" t="s">
+      <c r="C82" s="178" t="s">
         <v>492</v>
       </c>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="121"/>
-      <c r="G77" s="121"/>
-      <c r="H77" s="121"/>
-      <c r="I77" s="121"/>
-      <c r="J77" s="121"/>
-      <c r="K77" s="112" t="s">
+      <c r="D82" s="179"/>
+      <c r="E82" s="179"/>
+      <c r="F82" s="179"/>
+      <c r="G82" s="179"/>
+      <c r="H82" s="179"/>
+      <c r="I82" s="179"/>
+      <c r="J82" s="179"/>
+      <c r="K82" s="112" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="78" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B78" s="108">
+    <row r="83" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B83" s="108">
         <v>3</v>
       </c>
-      <c r="C78" s="122" t="s">
+      <c r="C83" s="180" t="s">
         <v>493</v>
       </c>
-      <c r="D78" s="123"/>
-      <c r="E78" s="123"/>
-      <c r="F78" s="123"/>
-      <c r="G78" s="123"/>
-      <c r="H78" s="123"/>
-      <c r="I78" s="123"/>
-      <c r="J78" s="123"/>
-      <c r="K78" s="111"/>
-      <c r="L78" s="110"/>
-      <c r="M78" s="110"/>
-      <c r="N78" s="110"/>
-      <c r="O78" s="110"/>
-      <c r="P78" s="110"/>
-      <c r="Q78" s="110"/>
-      <c r="R78" s="110"/>
-      <c r="S78" s="110"/>
-    </row>
-    <row r="79" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B79" s="108">
+      <c r="D83" s="181"/>
+      <c r="E83" s="181"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
+      <c r="K83" s="111"/>
+      <c r="L83" s="110"/>
+      <c r="M83" s="110"/>
+      <c r="N83" s="110"/>
+      <c r="O83" s="110"/>
+      <c r="P83" s="110"/>
+      <c r="Q83" s="110"/>
+      <c r="R83" s="110"/>
+      <c r="S83" s="110"/>
+    </row>
+    <row r="84" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B84" s="108">
         <v>4</v>
       </c>
-      <c r="C79" s="120" t="s">
+      <c r="C84" s="178" t="s">
         <v>494</v>
       </c>
-      <c r="D79" s="121"/>
-      <c r="E79" s="121"/>
-      <c r="F79" s="121"/>
-      <c r="G79" s="121"/>
-      <c r="H79" s="121"/>
-      <c r="I79" s="121"/>
-      <c r="J79" s="121"/>
-      <c r="K79" s="112"/>
-    </row>
-    <row r="80" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B80" s="108">
+      <c r="D84" s="179"/>
+      <c r="E84" s="179"/>
+      <c r="F84" s="179"/>
+      <c r="G84" s="179"/>
+      <c r="H84" s="179"/>
+      <c r="I84" s="179"/>
+      <c r="J84" s="179"/>
+      <c r="K84" s="112"/>
+    </row>
+    <row r="85" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B85" s="108">
         <v>5</v>
       </c>
-      <c r="C80" s="122" t="s">
+      <c r="C85" s="180" t="s">
         <v>495</v>
       </c>
-      <c r="D80" s="123"/>
-      <c r="E80" s="123"/>
-      <c r="F80" s="123"/>
-      <c r="G80" s="123"/>
-      <c r="H80" s="123"/>
-      <c r="I80" s="123"/>
-      <c r="J80" s="123"/>
-      <c r="K80" s="111" t="s">
+      <c r="D85" s="181"/>
+      <c r="E85" s="181"/>
+      <c r="F85" s="181"/>
+      <c r="G85" s="181"/>
+      <c r="H85" s="181"/>
+      <c r="I85" s="181"/>
+      <c r="J85" s="181"/>
+      <c r="K85" s="111" t="s">
         <v>499</v>
       </c>
-      <c r="L80" s="110"/>
-      <c r="M80" s="110"/>
-      <c r="N80" s="110"/>
-      <c r="O80" s="110"/>
-      <c r="P80" s="110"/>
-      <c r="Q80" s="110"/>
-      <c r="R80" s="110"/>
-      <c r="S80" s="110"/>
-    </row>
-    <row r="81" spans="2:11" ht="22.5" x14ac:dyDescent="0.5">
-      <c r="B81" s="108">
+      <c r="L85" s="110"/>
+      <c r="M85" s="110"/>
+      <c r="N85" s="110"/>
+      <c r="O85" s="110"/>
+      <c r="P85" s="110"/>
+      <c r="Q85" s="110"/>
+      <c r="R85" s="110"/>
+      <c r="S85" s="110"/>
+    </row>
+    <row r="86" spans="2:19" ht="22.5" x14ac:dyDescent="0.5">
+      <c r="B86" s="108">
         <v>6</v>
       </c>
-      <c r="C81" s="120" t="s">
+      <c r="C86" s="178" t="s">
         <v>498</v>
       </c>
-      <c r="D81" s="121"/>
-      <c r="E81" s="121"/>
-      <c r="F81" s="121"/>
-      <c r="G81" s="121"/>
-      <c r="H81" s="121"/>
-      <c r="I81" s="121"/>
-      <c r="J81" s="121"/>
-      <c r="K81" s="112"/>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B84" s="127" t="s">
+      <c r="D86" s="179"/>
+      <c r="E86" s="179"/>
+      <c r="F86" s="179"/>
+      <c r="G86" s="179"/>
+      <c r="H86" s="179"/>
+      <c r="I86" s="179"/>
+      <c r="J86" s="179"/>
+      <c r="K86" s="112"/>
+    </row>
+    <row r="89" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="B89" s="187" t="s">
         <v>519</v>
       </c>
-      <c r="C84" s="127"/>
-      <c r="D84" s="127"/>
-      <c r="E84" s="127"/>
-      <c r="F84" s="113"/>
-      <c r="G84" s="113"/>
-      <c r="H84" s="113"/>
-      <c r="I84" s="113"/>
-      <c r="J84" s="113"/>
-      <c r="K84" s="113"/>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B85" s="127"/>
-      <c r="C85" s="127"/>
-      <c r="D85" s="127"/>
-      <c r="E85" s="127"/>
-      <c r="F85" s="113"/>
-      <c r="G85" s="113"/>
-      <c r="H85" s="113"/>
-      <c r="I85" s="113"/>
-      <c r="J85" s="113"/>
-      <c r="K85" s="113"/>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="C86" s="113"/>
-      <c r="D86" s="113"/>
-      <c r="E86" s="113"/>
-      <c r="F86" s="113"/>
-      <c r="G86" s="113"/>
-      <c r="H86" s="113"/>
-      <c r="I86" s="113"/>
-      <c r="J86" s="113"/>
-      <c r="K86" s="113"/>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="C87" s="113"/>
-      <c r="D87" s="113"/>
-      <c r="E87" s="113"/>
-      <c r="F87" s="113"/>
-      <c r="G87" s="113"/>
-      <c r="H87" s="113"/>
-      <c r="I87" s="113"/>
-      <c r="J87" s="113"/>
-      <c r="K87" s="113"/>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="C88" s="113"/>
-      <c r="D88" s="113"/>
-      <c r="E88" s="113"/>
-      <c r="F88" s="113"/>
-      <c r="G88" s="113"/>
-      <c r="H88" s="113"/>
-      <c r="I88" s="113"/>
-      <c r="J88" s="113"/>
-      <c r="K88" s="113"/>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="I93" s="162" t="s">
+      <c r="C89" s="187"/>
+      <c r="D89" s="187"/>
+      <c r="E89" s="187"/>
+      <c r="F89" s="113"/>
+      <c r="G89" s="113"/>
+      <c r="H89" s="113"/>
+      <c r="I89" s="113"/>
+      <c r="J89" s="113"/>
+      <c r="K89" s="113"/>
+    </row>
+    <row r="90" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="B90" s="187"/>
+      <c r="C90" s="187"/>
+      <c r="D90" s="187"/>
+      <c r="E90" s="187"/>
+      <c r="F90" s="113"/>
+      <c r="G90" s="113"/>
+      <c r="H90" s="113"/>
+      <c r="I90" s="113"/>
+      <c r="J90" s="113"/>
+      <c r="K90" s="113"/>
+    </row>
+    <row r="91" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="C91" s="113"/>
+      <c r="D91" s="113"/>
+      <c r="E91" s="113"/>
+      <c r="F91" s="113"/>
+      <c r="G91" s="113"/>
+      <c r="H91" s="113"/>
+      <c r="I91" s="113"/>
+      <c r="J91" s="113"/>
+      <c r="K91" s="113"/>
+    </row>
+    <row r="92" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="C92" s="113"/>
+      <c r="D92" s="113"/>
+      <c r="E92" s="113"/>
+      <c r="F92" s="113"/>
+      <c r="G92" s="113"/>
+      <c r="H92" s="113"/>
+      <c r="I92" s="113"/>
+      <c r="J92" s="113"/>
+      <c r="K92" s="113"/>
+    </row>
+    <row r="93" spans="2:19" x14ac:dyDescent="0.5">
+      <c r="C93" s="113"/>
+      <c r="D93" s="113"/>
+      <c r="E93" s="113"/>
+      <c r="F93" s="113"/>
+      <c r="G93" s="113"/>
+      <c r="H93" s="113"/>
+      <c r="I93" s="113"/>
+      <c r="J93" s="113"/>
+      <c r="K93" s="113"/>
+    </row>
+    <row r="98" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="I98" s="155" t="s">
         <v>523</v>
       </c>
-      <c r="J93" s="162"/>
-      <c r="K93" s="162"/>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="I94" s="164" t="s">
+      <c r="J98" s="155"/>
+      <c r="K98" s="155"/>
+    </row>
+    <row r="99" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="I99" s="157" t="s">
         <v>522</v>
       </c>
-      <c r="J94" s="164"/>
-      <c r="K94" s="164"/>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="I95" s="163" t="s">
+      <c r="J99" s="157"/>
+      <c r="K99" s="157"/>
+    </row>
+    <row r="100" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="I100" s="156" t="s">
         <v>521</v>
       </c>
-      <c r="J95" s="163"/>
-      <c r="K95" s="163"/>
-    </row>
-    <row r="96" spans="2:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="97" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="17" t="s">
+      <c r="J100" s="156"/>
+      <c r="K100" s="156"/>
+    </row>
+    <row r="101" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="102" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="C97" s="160" t="s">
+      <c r="C102" s="142" t="s">
         <v>501</v>
       </c>
-      <c r="D97" s="160"/>
-      <c r="E97" s="160"/>
-      <c r="F97" s="160"/>
-      <c r="G97" s="160"/>
-      <c r="H97" s="160"/>
-      <c r="I97" s="160"/>
-      <c r="J97" s="160"/>
-      <c r="K97" s="160"/>
-      <c r="L97" s="160"/>
-      <c r="M97" s="160"/>
-      <c r="N97" s="160"/>
-      <c r="O97" s="160"/>
-      <c r="P97" s="160"/>
-      <c r="Q97" s="160"/>
-      <c r="R97" s="160"/>
-      <c r="S97" s="160"/>
-      <c r="T97" s="160"/>
-    </row>
-    <row r="98" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C98" s="161" t="s">
+      <c r="D102" s="142"/>
+      <c r="E102" s="142"/>
+      <c r="F102" s="142"/>
+      <c r="G102" s="142"/>
+      <c r="H102" s="142"/>
+      <c r="I102" s="142"/>
+      <c r="J102" s="142"/>
+      <c r="K102" s="142"/>
+      <c r="L102" s="142"/>
+      <c r="M102" s="142"/>
+      <c r="N102" s="142"/>
+      <c r="O102" s="142"/>
+      <c r="P102" s="142"/>
+      <c r="Q102" s="142"/>
+      <c r="R102" s="142"/>
+      <c r="S102" s="142"/>
+      <c r="T102" s="142"/>
+    </row>
+    <row r="103" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C103" s="154" t="s">
         <v>507</v>
       </c>
-      <c r="D98" s="161"/>
-      <c r="E98" s="161"/>
-      <c r="F98" s="161"/>
-      <c r="G98" s="161"/>
-      <c r="H98" s="161"/>
-      <c r="I98" s="161"/>
-      <c r="J98" s="161"/>
-      <c r="K98" s="161"/>
-      <c r="L98" s="161"/>
-      <c r="M98" s="161"/>
-      <c r="N98" s="161"/>
-      <c r="O98" s="161"/>
-      <c r="P98" s="161"/>
-      <c r="Q98" s="161"/>
-      <c r="R98" s="161"/>
-      <c r="S98" s="161"/>
-      <c r="T98" s="161"/>
-    </row>
-    <row r="99" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C99" s="161" t="s">
+      <c r="D103" s="154"/>
+      <c r="E103" s="154"/>
+      <c r="F103" s="154"/>
+      <c r="G103" s="154"/>
+      <c r="H103" s="154"/>
+      <c r="I103" s="154"/>
+      <c r="J103" s="154"/>
+      <c r="K103" s="154"/>
+      <c r="L103" s="154"/>
+      <c r="M103" s="154"/>
+      <c r="N103" s="154"/>
+      <c r="O103" s="154"/>
+      <c r="P103" s="154"/>
+      <c r="Q103" s="154"/>
+      <c r="R103" s="154"/>
+      <c r="S103" s="154"/>
+      <c r="T103" s="154"/>
+    </row>
+    <row r="104" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C104" s="154" t="s">
         <v>508</v>
       </c>
-      <c r="D99" s="161"/>
-      <c r="E99" s="161"/>
-      <c r="F99" s="161"/>
-      <c r="G99" s="161"/>
-      <c r="H99" s="161"/>
-      <c r="I99" s="161"/>
-      <c r="J99" s="161"/>
-      <c r="K99" s="161"/>
-      <c r="L99" s="161"/>
-      <c r="M99" s="161"/>
-      <c r="N99" s="161"/>
-      <c r="O99" s="161"/>
-      <c r="P99" s="161"/>
-      <c r="Q99" s="161"/>
-      <c r="R99" s="161"/>
-      <c r="S99" s="161"/>
-      <c r="T99" s="161"/>
-    </row>
-    <row r="100" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C100" s="161" t="s">
+      <c r="D104" s="154"/>
+      <c r="E104" s="154"/>
+      <c r="F104" s="154"/>
+      <c r="G104" s="154"/>
+      <c r="H104" s="154"/>
+      <c r="I104" s="154"/>
+      <c r="J104" s="154"/>
+      <c r="K104" s="154"/>
+      <c r="L104" s="154"/>
+      <c r="M104" s="154"/>
+      <c r="N104" s="154"/>
+      <c r="O104" s="154"/>
+      <c r="P104" s="154"/>
+      <c r="Q104" s="154"/>
+      <c r="R104" s="154"/>
+      <c r="S104" s="154"/>
+      <c r="T104" s="154"/>
+    </row>
+    <row r="105" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C105" s="154" t="s">
         <v>509</v>
       </c>
-      <c r="D100" s="161"/>
-      <c r="E100" s="161"/>
-      <c r="F100" s="161"/>
-      <c r="G100" s="161"/>
-      <c r="H100" s="161"/>
-      <c r="I100" s="161"/>
-      <c r="J100" s="161"/>
-      <c r="K100" s="161"/>
-      <c r="L100" s="161"/>
-      <c r="M100" s="161"/>
-      <c r="N100" s="161"/>
-      <c r="O100" s="161"/>
-      <c r="P100" s="161"/>
-      <c r="Q100" s="161"/>
-      <c r="R100" s="161"/>
-      <c r="S100" s="161"/>
-      <c r="T100" s="161"/>
-    </row>
-    <row r="101" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C101" s="161" t="s">
+      <c r="D105" s="154"/>
+      <c r="E105" s="154"/>
+      <c r="F105" s="154"/>
+      <c r="G105" s="154"/>
+      <c r="H105" s="154"/>
+      <c r="I105" s="154"/>
+      <c r="J105" s="154"/>
+      <c r="K105" s="154"/>
+      <c r="L105" s="154"/>
+      <c r="M105" s="154"/>
+      <c r="N105" s="154"/>
+      <c r="O105" s="154"/>
+      <c r="P105" s="154"/>
+      <c r="Q105" s="154"/>
+      <c r="R105" s="154"/>
+      <c r="S105" s="154"/>
+      <c r="T105" s="154"/>
+    </row>
+    <row r="106" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C106" s="154" t="s">
         <v>506</v>
       </c>
-      <c r="D101" s="161"/>
-      <c r="E101" s="161"/>
-      <c r="F101" s="161"/>
-      <c r="G101" s="161"/>
-      <c r="H101" s="161"/>
-      <c r="I101" s="161"/>
-      <c r="J101" s="161"/>
-      <c r="K101" s="161"/>
-      <c r="L101" s="161"/>
-      <c r="M101" s="161"/>
-      <c r="N101" s="161"/>
-      <c r="O101" s="161"/>
-      <c r="P101" s="161"/>
-      <c r="Q101" s="161"/>
-      <c r="R101" s="161"/>
-      <c r="S101" s="161"/>
-      <c r="T101" s="161"/>
-    </row>
-    <row r="102" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C102" s="165" t="s">
+      <c r="D106" s="154"/>
+      <c r="E106" s="154"/>
+      <c r="F106" s="154"/>
+      <c r="G106" s="154"/>
+      <c r="H106" s="154"/>
+      <c r="I106" s="154"/>
+      <c r="J106" s="154"/>
+      <c r="K106" s="154"/>
+      <c r="L106" s="154"/>
+      <c r="M106" s="154"/>
+      <c r="N106" s="154"/>
+      <c r="O106" s="154"/>
+      <c r="P106" s="154"/>
+      <c r="Q106" s="154"/>
+      <c r="R106" s="154"/>
+      <c r="S106" s="154"/>
+      <c r="T106" s="154"/>
+    </row>
+    <row r="107" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C107" s="141" t="s">
         <v>510</v>
       </c>
-      <c r="D102" s="165"/>
-      <c r="E102" s="165"/>
-      <c r="F102" s="165"/>
-      <c r="G102" s="165"/>
-      <c r="H102" s="165"/>
-      <c r="I102" s="165"/>
-      <c r="J102" s="165"/>
-      <c r="K102" s="165"/>
-      <c r="L102" s="165"/>
-      <c r="M102" s="165"/>
-      <c r="N102" s="165"/>
-      <c r="O102" s="165"/>
-      <c r="P102" s="165"/>
-      <c r="Q102" s="165"/>
-      <c r="R102" s="165"/>
-      <c r="S102" s="165"/>
-      <c r="T102" s="165"/>
-    </row>
-    <row r="103" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C103" s="165"/>
-      <c r="D103" s="165"/>
-      <c r="E103" s="165"/>
-      <c r="F103" s="165"/>
-      <c r="G103" s="165"/>
-      <c r="H103" s="165"/>
-      <c r="I103" s="165"/>
-      <c r="J103" s="165"/>
-      <c r="K103" s="165"/>
-      <c r="L103" s="165"/>
-      <c r="M103" s="165"/>
-      <c r="N103" s="165"/>
-      <c r="O103" s="165"/>
-      <c r="P103" s="165"/>
-      <c r="Q103" s="165"/>
-      <c r="R103" s="165"/>
-      <c r="S103" s="165"/>
-      <c r="T103" s="165"/>
-    </row>
-    <row r="104" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C104" s="165"/>
-      <c r="D104" s="165"/>
-      <c r="E104" s="165"/>
-      <c r="F104" s="165"/>
-      <c r="G104" s="165"/>
-      <c r="H104" s="165"/>
-      <c r="I104" s="165"/>
-      <c r="J104" s="165"/>
-      <c r="K104" s="165"/>
-      <c r="L104" s="165"/>
-      <c r="M104" s="165"/>
-      <c r="N104" s="165"/>
-      <c r="O104" s="165"/>
-      <c r="P104" s="165"/>
-      <c r="Q104" s="165"/>
-      <c r="R104" s="165"/>
-      <c r="S104" s="165"/>
-      <c r="T104" s="165"/>
-    </row>
-    <row r="105" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="106" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="C106" s="119" t="s">
-        <v>503</v>
-      </c>
-      <c r="D106" s="119"/>
-      <c r="E106" s="119"/>
-      <c r="F106" s="119"/>
-      <c r="G106" s="119"/>
-      <c r="H106" s="119"/>
-      <c r="I106" s="119"/>
-      <c r="J106" s="119"/>
-      <c r="K106" s="119"/>
-      <c r="L106" s="119"/>
-      <c r="M106" s="119"/>
-      <c r="N106" s="119"/>
-      <c r="O106" s="119"/>
-      <c r="P106" s="119"/>
-      <c r="Q106" s="119"/>
-      <c r="R106" s="119"/>
-      <c r="S106" s="119"/>
-      <c r="T106" s="119"/>
-    </row>
-    <row r="107" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C107" s="119" t="s">
-        <v>511</v>
-      </c>
-      <c r="D107" s="119"/>
-      <c r="E107" s="119"/>
-      <c r="F107" s="119"/>
-      <c r="G107" s="119"/>
-      <c r="H107" s="119"/>
-      <c r="I107" s="119"/>
-      <c r="J107" s="119"/>
-      <c r="K107" s="119"/>
-      <c r="L107" s="119"/>
-      <c r="M107" s="119"/>
-      <c r="N107" s="119"/>
-      <c r="O107" s="119"/>
-      <c r="P107" s="119"/>
-      <c r="Q107" s="119"/>
-      <c r="R107" s="119"/>
-      <c r="S107" s="119"/>
-      <c r="T107" s="119"/>
+      <c r="D107" s="141"/>
+      <c r="E107" s="141"/>
+      <c r="F107" s="141"/>
+      <c r="G107" s="141"/>
+      <c r="H107" s="141"/>
+      <c r="I107" s="141"/>
+      <c r="J107" s="141"/>
+      <c r="K107" s="141"/>
+      <c r="L107" s="141"/>
+      <c r="M107" s="141"/>
+      <c r="N107" s="141"/>
+      <c r="O107" s="141"/>
+      <c r="P107" s="141"/>
+      <c r="Q107" s="141"/>
+      <c r="R107" s="141"/>
+      <c r="S107" s="141"/>
+      <c r="T107" s="141"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C108" s="119" t="s">
-        <v>512</v>
-      </c>
-      <c r="D108" s="119"/>
-      <c r="E108" s="119"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="119"/>
-      <c r="H108" s="119"/>
-      <c r="I108" s="119"/>
-      <c r="J108" s="119"/>
-      <c r="K108" s="119"/>
-      <c r="L108" s="119"/>
-      <c r="M108" s="119"/>
-      <c r="N108" s="119"/>
-      <c r="O108" s="119"/>
-      <c r="P108" s="119"/>
-      <c r="Q108" s="119"/>
-      <c r="R108" s="119"/>
-      <c r="S108" s="119"/>
-      <c r="T108" s="119"/>
+      <c r="C108" s="141"/>
+      <c r="D108" s="141"/>
+      <c r="E108" s="141"/>
+      <c r="F108" s="141"/>
+      <c r="G108" s="141"/>
+      <c r="H108" s="141"/>
+      <c r="I108" s="141"/>
+      <c r="J108" s="141"/>
+      <c r="K108" s="141"/>
+      <c r="L108" s="141"/>
+      <c r="M108" s="141"/>
+      <c r="N108" s="141"/>
+      <c r="O108" s="141"/>
+      <c r="P108" s="141"/>
+      <c r="Q108" s="141"/>
+      <c r="R108" s="141"/>
+      <c r="S108" s="141"/>
+      <c r="T108" s="141"/>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C109" s="119" t="s">
-        <v>513</v>
-      </c>
-      <c r="D109" s="119"/>
-      <c r="E109" s="119"/>
-      <c r="F109" s="119"/>
-      <c r="G109" s="119"/>
-      <c r="H109" s="119"/>
-      <c r="I109" s="119"/>
-      <c r="J109" s="119"/>
-      <c r="K109" s="119"/>
-      <c r="L109" s="119"/>
-      <c r="M109" s="119"/>
-      <c r="N109" s="119"/>
-      <c r="O109" s="119"/>
-      <c r="P109" s="119"/>
-      <c r="Q109" s="119"/>
-      <c r="R109" s="119"/>
-      <c r="S109" s="119"/>
-      <c r="T109" s="119"/>
+      <c r="C109" s="141"/>
+      <c r="D109" s="141"/>
+      <c r="E109" s="141"/>
+      <c r="F109" s="141"/>
+      <c r="G109" s="141"/>
+      <c r="H109" s="141"/>
+      <c r="I109" s="141"/>
+      <c r="J109" s="141"/>
+      <c r="K109" s="141"/>
+      <c r="L109" s="141"/>
+      <c r="M109" s="141"/>
+      <c r="N109" s="141"/>
+      <c r="O109" s="141"/>
+      <c r="P109" s="141"/>
+      <c r="Q109" s="141"/>
+      <c r="R109" s="141"/>
+      <c r="S109" s="141"/>
+      <c r="T109" s="141"/>
     </row>
     <row r="110" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="111" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="C111" s="150" t="s">
+        <v>503</v>
+      </c>
+      <c r="D111" s="150"/>
+      <c r="E111" s="150"/>
+      <c r="F111" s="150"/>
+      <c r="G111" s="150"/>
+      <c r="H111" s="150"/>
+      <c r="I111" s="150"/>
+      <c r="J111" s="150"/>
+      <c r="K111" s="150"/>
+      <c r="L111" s="150"/>
+      <c r="M111" s="150"/>
+      <c r="N111" s="150"/>
+      <c r="O111" s="150"/>
+      <c r="P111" s="150"/>
+      <c r="Q111" s="150"/>
+      <c r="R111" s="150"/>
+      <c r="S111" s="150"/>
+      <c r="T111" s="150"/>
+    </row>
+    <row r="112" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C112" s="150" t="s">
+        <v>511</v>
+      </c>
+      <c r="D112" s="150"/>
+      <c r="E112" s="150"/>
+      <c r="F112" s="150"/>
+      <c r="G112" s="150"/>
+      <c r="H112" s="150"/>
+      <c r="I112" s="150"/>
+      <c r="J112" s="150"/>
+      <c r="K112" s="150"/>
+      <c r="L112" s="150"/>
+      <c r="M112" s="150"/>
+      <c r="N112" s="150"/>
+      <c r="O112" s="150"/>
+      <c r="P112" s="150"/>
+      <c r="Q112" s="150"/>
+      <c r="R112" s="150"/>
+      <c r="S112" s="150"/>
+      <c r="T112" s="150"/>
+    </row>
+    <row r="113" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C113" s="150" t="s">
+        <v>512</v>
+      </c>
+      <c r="D113" s="150"/>
+      <c r="E113" s="150"/>
+      <c r="F113" s="150"/>
+      <c r="G113" s="150"/>
+      <c r="H113" s="150"/>
+      <c r="I113" s="150"/>
+      <c r="J113" s="150"/>
+      <c r="K113" s="150"/>
+      <c r="L113" s="150"/>
+      <c r="M113" s="150"/>
+      <c r="N113" s="150"/>
+      <c r="O113" s="150"/>
+      <c r="P113" s="150"/>
+      <c r="Q113" s="150"/>
+      <c r="R113" s="150"/>
+      <c r="S113" s="150"/>
+      <c r="T113" s="150"/>
+    </row>
+    <row r="114" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C114" s="150" t="s">
+        <v>513</v>
+      </c>
+      <c r="D114" s="150"/>
+      <c r="E114" s="150"/>
+      <c r="F114" s="150"/>
+      <c r="G114" s="150"/>
+      <c r="H114" s="150"/>
+      <c r="I114" s="150"/>
+      <c r="J114" s="150"/>
+      <c r="K114" s="150"/>
+      <c r="L114" s="150"/>
+      <c r="M114" s="150"/>
+      <c r="N114" s="150"/>
+      <c r="O114" s="150"/>
+      <c r="P114" s="150"/>
+      <c r="Q114" s="150"/>
+      <c r="R114" s="150"/>
+      <c r="S114" s="150"/>
+      <c r="T114" s="150"/>
+    </row>
+    <row r="115" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="116" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="C111" s="160" t="s">
+      <c r="C116" s="142" t="s">
         <v>505</v>
       </c>
-      <c r="D111" s="160"/>
-      <c r="E111" s="160"/>
-      <c r="F111" s="160"/>
-      <c r="G111" s="160"/>
-      <c r="H111" s="160"/>
-      <c r="I111" s="160"/>
-      <c r="J111" s="160"/>
-      <c r="K111" s="160"/>
-      <c r="L111" s="160"/>
-      <c r="M111" s="160"/>
-      <c r="N111" s="160"/>
-      <c r="O111" s="160"/>
-      <c r="P111" s="160"/>
-      <c r="Q111" s="160"/>
-      <c r="R111" s="160"/>
-      <c r="S111" s="160"/>
-      <c r="T111" s="160"/>
-    </row>
-    <row r="112" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C112" s="119" t="s">
+      <c r="D116" s="142"/>
+      <c r="E116" s="142"/>
+      <c r="F116" s="142"/>
+      <c r="G116" s="142"/>
+      <c r="H116" s="142"/>
+      <c r="I116" s="142"/>
+      <c r="J116" s="142"/>
+      <c r="K116" s="142"/>
+      <c r="L116" s="142"/>
+      <c r="M116" s="142"/>
+      <c r="N116" s="142"/>
+      <c r="O116" s="142"/>
+      <c r="P116" s="142"/>
+      <c r="Q116" s="142"/>
+      <c r="R116" s="142"/>
+      <c r="S116" s="142"/>
+      <c r="T116" s="142"/>
+    </row>
+    <row r="117" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C117" s="150" t="s">
         <v>515</v>
       </c>
-      <c r="D112" s="119"/>
-      <c r="E112" s="119"/>
-      <c r="F112" s="119"/>
-      <c r="G112" s="119"/>
-      <c r="H112" s="119"/>
-      <c r="I112" s="119"/>
-      <c r="J112" s="119"/>
-      <c r="K112" s="119"/>
-      <c r="L112" s="119"/>
-      <c r="M112" s="119"/>
-      <c r="N112" s="119"/>
-      <c r="O112" s="119"/>
-      <c r="P112" s="119"/>
-      <c r="Q112" s="119"/>
-      <c r="R112" s="119"/>
-      <c r="S112" s="119"/>
-      <c r="T112" s="119"/>
-    </row>
-    <row r="113" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C113" s="119" t="s">
+      <c r="D117" s="150"/>
+      <c r="E117" s="150"/>
+      <c r="F117" s="150"/>
+      <c r="G117" s="150"/>
+      <c r="H117" s="150"/>
+      <c r="I117" s="150"/>
+      <c r="J117" s="150"/>
+      <c r="K117" s="150"/>
+      <c r="L117" s="150"/>
+      <c r="M117" s="150"/>
+      <c r="N117" s="150"/>
+      <c r="O117" s="150"/>
+      <c r="P117" s="150"/>
+      <c r="Q117" s="150"/>
+      <c r="R117" s="150"/>
+      <c r="S117" s="150"/>
+      <c r="T117" s="150"/>
+    </row>
+    <row r="118" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C118" s="150" t="s">
         <v>514</v>
       </c>
-      <c r="D113" s="119"/>
-      <c r="E113" s="119"/>
-      <c r="F113" s="119"/>
-      <c r="G113" s="119"/>
-      <c r="H113" s="119"/>
-      <c r="I113" s="119"/>
-      <c r="J113" s="119"/>
-      <c r="K113" s="119"/>
-      <c r="L113" s="119"/>
-      <c r="M113" s="119"/>
-      <c r="N113" s="119"/>
-      <c r="O113" s="119"/>
-      <c r="P113" s="119"/>
-      <c r="Q113" s="119"/>
-      <c r="R113" s="119"/>
-      <c r="S113" s="119"/>
-      <c r="T113" s="119"/>
-    </row>
-    <row r="114" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C114" s="119" t="s">
+      <c r="D118" s="150"/>
+      <c r="E118" s="150"/>
+      <c r="F118" s="150"/>
+      <c r="G118" s="150"/>
+      <c r="H118" s="150"/>
+      <c r="I118" s="150"/>
+      <c r="J118" s="150"/>
+      <c r="K118" s="150"/>
+      <c r="L118" s="150"/>
+      <c r="M118" s="150"/>
+      <c r="N118" s="150"/>
+      <c r="O118" s="150"/>
+      <c r="P118" s="150"/>
+      <c r="Q118" s="150"/>
+      <c r="R118" s="150"/>
+      <c r="S118" s="150"/>
+      <c r="T118" s="150"/>
+    </row>
+    <row r="119" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C119" s="150" t="s">
         <v>516</v>
       </c>
-      <c r="D114" s="119"/>
-      <c r="E114" s="119"/>
-      <c r="F114" s="119"/>
-      <c r="G114" s="119"/>
-      <c r="H114" s="119"/>
-      <c r="I114" s="119"/>
-      <c r="J114" s="119"/>
-      <c r="K114" s="119"/>
-      <c r="L114" s="119"/>
-      <c r="M114" s="119"/>
-      <c r="N114" s="119"/>
-      <c r="O114" s="119"/>
-      <c r="P114" s="119"/>
-      <c r="Q114" s="119"/>
-      <c r="R114" s="119"/>
-      <c r="S114" s="119"/>
-      <c r="T114" s="119"/>
-    </row>
-    <row r="115" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C115" s="119" t="s">
+      <c r="D119" s="150"/>
+      <c r="E119" s="150"/>
+      <c r="F119" s="150"/>
+      <c r="G119" s="150"/>
+      <c r="H119" s="150"/>
+      <c r="I119" s="150"/>
+      <c r="J119" s="150"/>
+      <c r="K119" s="150"/>
+      <c r="L119" s="150"/>
+      <c r="M119" s="150"/>
+      <c r="N119" s="150"/>
+      <c r="O119" s="150"/>
+      <c r="P119" s="150"/>
+      <c r="Q119" s="150"/>
+      <c r="R119" s="150"/>
+      <c r="S119" s="150"/>
+      <c r="T119" s="150"/>
+    </row>
+    <row r="120" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C120" s="150" t="s">
         <v>517</v>
       </c>
-      <c r="D115" s="119"/>
-      <c r="E115" s="119"/>
-      <c r="F115" s="119"/>
-      <c r="G115" s="119"/>
-      <c r="H115" s="119"/>
-      <c r="I115" s="119"/>
-      <c r="J115" s="119"/>
-      <c r="K115" s="119"/>
-      <c r="L115" s="119"/>
-      <c r="M115" s="119"/>
-      <c r="N115" s="119"/>
-      <c r="O115" s="119"/>
-      <c r="P115" s="119"/>
-      <c r="Q115" s="119"/>
-      <c r="R115" s="119"/>
-      <c r="S115" s="119"/>
-      <c r="T115" s="119"/>
-    </row>
-    <row r="116" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C116" s="119" t="s">
+      <c r="D120" s="150"/>
+      <c r="E120" s="150"/>
+      <c r="F120" s="150"/>
+      <c r="G120" s="150"/>
+      <c r="H120" s="150"/>
+      <c r="I120" s="150"/>
+      <c r="J120" s="150"/>
+      <c r="K120" s="150"/>
+      <c r="L120" s="150"/>
+      <c r="M120" s="150"/>
+      <c r="N120" s="150"/>
+      <c r="O120" s="150"/>
+      <c r="P120" s="150"/>
+      <c r="Q120" s="150"/>
+      <c r="R120" s="150"/>
+      <c r="S120" s="150"/>
+      <c r="T120" s="150"/>
+    </row>
+    <row r="121" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C121" s="150" t="s">
         <v>518</v>
       </c>
-      <c r="D116" s="119"/>
-      <c r="E116" s="119"/>
-      <c r="F116" s="119"/>
-      <c r="G116" s="119"/>
-      <c r="H116" s="119"/>
-      <c r="I116" s="119"/>
-      <c r="J116" s="119"/>
-      <c r="K116" s="119"/>
-      <c r="L116" s="119"/>
-      <c r="M116" s="119"/>
-      <c r="N116" s="119"/>
-      <c r="O116" s="119"/>
-      <c r="P116" s="119"/>
-      <c r="Q116" s="119"/>
-      <c r="R116" s="119"/>
-      <c r="S116" s="119"/>
-      <c r="T116" s="119"/>
-    </row>
-    <row r="117" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C117" s="119" t="s">
+      <c r="D121" s="150"/>
+      <c r="E121" s="150"/>
+      <c r="F121" s="150"/>
+      <c r="G121" s="150"/>
+      <c r="H121" s="150"/>
+      <c r="I121" s="150"/>
+      <c r="J121" s="150"/>
+      <c r="K121" s="150"/>
+      <c r="L121" s="150"/>
+      <c r="M121" s="150"/>
+      <c r="N121" s="150"/>
+      <c r="O121" s="150"/>
+      <c r="P121" s="150"/>
+      <c r="Q121" s="150"/>
+      <c r="R121" s="150"/>
+      <c r="S121" s="150"/>
+      <c r="T121" s="150"/>
+    </row>
+    <row r="122" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C122" s="150" t="s">
         <v>520</v>
       </c>
-      <c r="D117" s="119"/>
-      <c r="E117" s="119"/>
-      <c r="F117" s="119"/>
-      <c r="G117" s="119"/>
-      <c r="H117" s="119"/>
-      <c r="I117" s="119"/>
-      <c r="J117" s="119"/>
-      <c r="K117" s="119"/>
-      <c r="L117" s="119"/>
-      <c r="M117" s="119"/>
-      <c r="N117" s="119"/>
-      <c r="O117" s="119"/>
-      <c r="P117" s="119"/>
-      <c r="Q117" s="119"/>
-      <c r="R117" s="119"/>
-      <c r="S117" s="119"/>
-      <c r="T117" s="119"/>
-    </row>
-    <row r="119" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B119" s="116" t="s">
+      <c r="D122" s="150"/>
+      <c r="E122" s="150"/>
+      <c r="F122" s="150"/>
+      <c r="G122" s="150"/>
+      <c r="H122" s="150"/>
+      <c r="I122" s="150"/>
+      <c r="J122" s="150"/>
+      <c r="K122" s="150"/>
+      <c r="L122" s="150"/>
+      <c r="M122" s="150"/>
+      <c r="N122" s="150"/>
+      <c r="O122" s="150"/>
+      <c r="P122" s="150"/>
+      <c r="Q122" s="150"/>
+      <c r="R122" s="150"/>
+      <c r="S122" s="150"/>
+      <c r="T122" s="150"/>
+    </row>
+    <row r="124" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B124" s="177" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="116"/>
-      <c r="D119" s="116"/>
-      <c r="E119" s="116"/>
-    </row>
-    <row r="120" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B120" s="116"/>
-      <c r="C120" s="116"/>
-      <c r="D120" s="116"/>
-      <c r="E120" s="116"/>
-    </row>
-    <row r="121" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B121" s="116"/>
-      <c r="C121" s="116"/>
-      <c r="D121" s="116"/>
-      <c r="E121" s="116"/>
-    </row>
-    <row r="134" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="L134" s="154" t="s">
+      <c r="C124" s="177"/>
+      <c r="D124" s="177"/>
+      <c r="E124" s="177"/>
+    </row>
+    <row r="125" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B125" s="177"/>
+      <c r="C125" s="177"/>
+      <c r="D125" s="177"/>
+      <c r="E125" s="177"/>
+    </row>
+    <row r="126" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B126" s="177"/>
+      <c r="C126" s="177"/>
+      <c r="D126" s="177"/>
+      <c r="E126" s="177"/>
+    </row>
+    <row r="139" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="L139" s="144" t="s">
         <v>529</v>
       </c>
-      <c r="M134" s="154"/>
-      <c r="N134" s="154"/>
-      <c r="O134" s="155"/>
-    </row>
-    <row r="135" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="L135" s="156" t="s">
+      <c r="M139" s="144"/>
+      <c r="N139" s="144"/>
+      <c r="O139" s="145"/>
+    </row>
+    <row r="140" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="L140" s="146" t="s">
         <v>528</v>
       </c>
-      <c r="M135" s="156"/>
-      <c r="N135" s="156"/>
-      <c r="O135" s="157"/>
-    </row>
-    <row r="136" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="L136" s="158" t="s">
+      <c r="M140" s="146"/>
+      <c r="N140" s="146"/>
+      <c r="O140" s="147"/>
+    </row>
+    <row r="141" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="L141" s="148" t="s">
         <v>527</v>
       </c>
-      <c r="M136" s="158"/>
-      <c r="N136" s="158"/>
-      <c r="O136" s="159"/>
-    </row>
-    <row r="137" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="138" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B138" s="17" t="s">
+      <c r="M141" s="148"/>
+      <c r="N141" s="148"/>
+      <c r="O141" s="149"/>
+    </row>
+    <row r="142" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="143" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C138" s="115" t="s">
+      <c r="C143" s="143" t="s">
         <v>524</v>
       </c>
-      <c r="D138" s="115"/>
-      <c r="E138" s="115"/>
-      <c r="F138" s="115"/>
-      <c r="G138" s="115"/>
-      <c r="H138" s="115"/>
-      <c r="I138" s="115"/>
-      <c r="J138" s="115"/>
-      <c r="K138" s="115"/>
-      <c r="L138" s="115"/>
-      <c r="M138" s="115"/>
-      <c r="N138" s="115"/>
-      <c r="O138" s="115"/>
-      <c r="P138" s="115"/>
-      <c r="Q138" s="115"/>
-      <c r="R138" s="115"/>
-      <c r="S138" s="115"/>
-      <c r="T138" s="115"/>
-    </row>
-    <row r="139" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="140" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B140" s="17" t="s">
+      <c r="D143" s="143"/>
+      <c r="E143" s="143"/>
+      <c r="F143" s="143"/>
+      <c r="G143" s="143"/>
+      <c r="H143" s="143"/>
+      <c r="I143" s="143"/>
+      <c r="J143" s="143"/>
+      <c r="K143" s="143"/>
+      <c r="L143" s="143"/>
+      <c r="M143" s="143"/>
+      <c r="N143" s="143"/>
+      <c r="O143" s="143"/>
+      <c r="P143" s="143"/>
+      <c r="Q143" s="143"/>
+      <c r="R143" s="143"/>
+      <c r="S143" s="143"/>
+      <c r="T143" s="143"/>
+    </row>
+    <row r="144" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="145" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="C140" s="115" t="s">
+      <c r="C145" s="143" t="s">
         <v>530</v>
       </c>
-      <c r="D140" s="115"/>
-      <c r="E140" s="115"/>
-      <c r="F140" s="115"/>
-      <c r="G140" s="115"/>
-      <c r="H140" s="115"/>
-      <c r="I140" s="115"/>
-      <c r="J140" s="115"/>
-      <c r="K140" s="115"/>
-      <c r="L140" s="115"/>
-      <c r="M140" s="115"/>
-      <c r="N140" s="115"/>
-      <c r="O140" s="115"/>
-      <c r="P140" s="115"/>
-      <c r="Q140" s="115"/>
-      <c r="R140" s="115"/>
-      <c r="S140" s="115"/>
-      <c r="T140" s="115"/>
-    </row>
-    <row r="141" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="142" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B142" s="17" t="s">
+      <c r="D145" s="143"/>
+      <c r="E145" s="143"/>
+      <c r="F145" s="143"/>
+      <c r="G145" s="143"/>
+      <c r="H145" s="143"/>
+      <c r="I145" s="143"/>
+      <c r="J145" s="143"/>
+      <c r="K145" s="143"/>
+      <c r="L145" s="143"/>
+      <c r="M145" s="143"/>
+      <c r="N145" s="143"/>
+      <c r="O145" s="143"/>
+      <c r="P145" s="143"/>
+      <c r="Q145" s="143"/>
+      <c r="R145" s="143"/>
+      <c r="S145" s="143"/>
+      <c r="T145" s="143"/>
+    </row>
+    <row r="146" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="147" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="C142" s="160" t="s">
+      <c r="C147" s="142" t="s">
         <v>532</v>
       </c>
-      <c r="D142" s="160"/>
-      <c r="E142" s="160"/>
-      <c r="F142" s="160"/>
-      <c r="G142" s="160"/>
-      <c r="H142" s="160"/>
-      <c r="I142" s="160"/>
-      <c r="J142" s="160"/>
-      <c r="K142" s="160"/>
-      <c r="L142" s="160"/>
-      <c r="M142" s="160"/>
-      <c r="N142" s="160"/>
-      <c r="O142" s="160"/>
-      <c r="P142" s="160"/>
-      <c r="Q142" s="160"/>
-      <c r="R142" s="160"/>
-      <c r="S142" s="160"/>
-      <c r="T142" s="160"/>
-    </row>
-    <row r="143" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C143" s="165" t="s">
+      <c r="D147" s="142"/>
+      <c r="E147" s="142"/>
+      <c r="F147" s="142"/>
+      <c r="G147" s="142"/>
+      <c r="H147" s="142"/>
+      <c r="I147" s="142"/>
+      <c r="J147" s="142"/>
+      <c r="K147" s="142"/>
+      <c r="L147" s="142"/>
+      <c r="M147" s="142"/>
+      <c r="N147" s="142"/>
+      <c r="O147" s="142"/>
+      <c r="P147" s="142"/>
+      <c r="Q147" s="142"/>
+      <c r="R147" s="142"/>
+      <c r="S147" s="142"/>
+      <c r="T147" s="142"/>
+    </row>
+    <row r="148" spans="2:20" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C148" s="141" t="s">
         <v>541</v>
       </c>
-      <c r="D143" s="165"/>
-      <c r="E143" s="165"/>
-      <c r="F143" s="165"/>
-      <c r="G143" s="165"/>
-      <c r="H143" s="165"/>
-      <c r="I143" s="165"/>
-      <c r="J143" s="165"/>
-      <c r="K143" s="165"/>
-      <c r="L143" s="165"/>
-      <c r="M143" s="165"/>
-      <c r="N143" s="165"/>
-      <c r="O143" s="165"/>
-      <c r="P143" s="165"/>
-      <c r="Q143" s="165"/>
-      <c r="R143" s="165"/>
-      <c r="S143" s="165"/>
-      <c r="T143" s="165"/>
-    </row>
-    <row r="144" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C144" s="165"/>
-      <c r="D144" s="165"/>
-      <c r="E144" s="165"/>
-      <c r="F144" s="165"/>
-      <c r="G144" s="165"/>
-      <c r="H144" s="165"/>
-      <c r="I144" s="165"/>
-      <c r="J144" s="165"/>
-      <c r="K144" s="165"/>
-      <c r="L144" s="165"/>
-      <c r="M144" s="165"/>
-      <c r="N144" s="165"/>
-      <c r="O144" s="165"/>
-      <c r="P144" s="165"/>
-      <c r="Q144" s="165"/>
-      <c r="R144" s="165"/>
-      <c r="S144" s="165"/>
-      <c r="T144" s="165"/>
-    </row>
-    <row r="145" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C145" s="165"/>
-      <c r="D145" s="165"/>
-      <c r="E145" s="165"/>
-      <c r="F145" s="165"/>
-      <c r="G145" s="165"/>
-      <c r="H145" s="165"/>
-      <c r="I145" s="165"/>
-      <c r="J145" s="165"/>
-      <c r="K145" s="165"/>
-      <c r="L145" s="165"/>
-      <c r="M145" s="165"/>
-      <c r="N145" s="165"/>
-      <c r="O145" s="165"/>
-      <c r="P145" s="165"/>
-      <c r="Q145" s="165"/>
-      <c r="R145" s="165"/>
-      <c r="S145" s="165"/>
-      <c r="T145" s="165"/>
-    </row>
-    <row r="146" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C146" s="165"/>
-      <c r="D146" s="165"/>
-      <c r="E146" s="165"/>
-      <c r="F146" s="165"/>
-      <c r="G146" s="165"/>
-      <c r="H146" s="165"/>
-      <c r="I146" s="165"/>
-      <c r="J146" s="165"/>
-      <c r="K146" s="165"/>
-      <c r="L146" s="165"/>
-      <c r="M146" s="165"/>
-      <c r="N146" s="165"/>
-      <c r="O146" s="165"/>
-      <c r="P146" s="165"/>
-      <c r="Q146" s="165"/>
-      <c r="R146" s="165"/>
-      <c r="S146" s="165"/>
-      <c r="T146" s="165"/>
-    </row>
-    <row r="147" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C147" s="166" t="s">
+      <c r="D148" s="141"/>
+      <c r="E148" s="141"/>
+      <c r="F148" s="141"/>
+      <c r="G148" s="141"/>
+      <c r="H148" s="141"/>
+      <c r="I148" s="141"/>
+      <c r="J148" s="141"/>
+      <c r="K148" s="141"/>
+      <c r="L148" s="141"/>
+      <c r="M148" s="141"/>
+      <c r="N148" s="141"/>
+      <c r="O148" s="141"/>
+      <c r="P148" s="141"/>
+      <c r="Q148" s="141"/>
+      <c r="R148" s="141"/>
+      <c r="S148" s="141"/>
+      <c r="T148" s="141"/>
+    </row>
+    <row r="149" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C149" s="141"/>
+      <c r="D149" s="141"/>
+      <c r="E149" s="141"/>
+      <c r="F149" s="141"/>
+      <c r="G149" s="141"/>
+      <c r="H149" s="141"/>
+      <c r="I149" s="141"/>
+      <c r="J149" s="141"/>
+      <c r="K149" s="141"/>
+      <c r="L149" s="141"/>
+      <c r="M149" s="141"/>
+      <c r="N149" s="141"/>
+      <c r="O149" s="141"/>
+      <c r="P149" s="141"/>
+      <c r="Q149" s="141"/>
+      <c r="R149" s="141"/>
+      <c r="S149" s="141"/>
+      <c r="T149" s="141"/>
+    </row>
+    <row r="150" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C150" s="141"/>
+      <c r="D150" s="141"/>
+      <c r="E150" s="141"/>
+      <c r="F150" s="141"/>
+      <c r="G150" s="141"/>
+      <c r="H150" s="141"/>
+      <c r="I150" s="141"/>
+      <c r="J150" s="141"/>
+      <c r="K150" s="141"/>
+      <c r="L150" s="141"/>
+      <c r="M150" s="141"/>
+      <c r="N150" s="141"/>
+      <c r="O150" s="141"/>
+      <c r="P150" s="141"/>
+      <c r="Q150" s="141"/>
+      <c r="R150" s="141"/>
+      <c r="S150" s="141"/>
+      <c r="T150" s="141"/>
+    </row>
+    <row r="151" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C151" s="141"/>
+      <c r="D151" s="141"/>
+      <c r="E151" s="141"/>
+      <c r="F151" s="141"/>
+      <c r="G151" s="141"/>
+      <c r="H151" s="141"/>
+      <c r="I151" s="141"/>
+      <c r="J151" s="141"/>
+      <c r="K151" s="141"/>
+      <c r="L151" s="141"/>
+      <c r="M151" s="141"/>
+      <c r="N151" s="141"/>
+      <c r="O151" s="141"/>
+      <c r="P151" s="141"/>
+      <c r="Q151" s="141"/>
+      <c r="R151" s="141"/>
+      <c r="S151" s="141"/>
+      <c r="T151" s="141"/>
+    </row>
+    <row r="152" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C152" s="140" t="s">
         <v>533</v>
       </c>
-      <c r="D147" s="166"/>
-      <c r="E147" s="166"/>
-      <c r="F147" s="166"/>
-      <c r="G147" s="166"/>
-      <c r="H147" s="166"/>
-      <c r="I147" s="166"/>
-      <c r="J147" s="166"/>
-      <c r="K147" s="166"/>
-      <c r="L147" s="166"/>
-      <c r="M147" s="166"/>
-      <c r="N147" s="166"/>
-      <c r="O147" s="166"/>
-      <c r="P147" s="166"/>
-      <c r="Q147" s="166"/>
-      <c r="R147" s="166"/>
-      <c r="S147" s="166"/>
-      <c r="T147" s="166"/>
-    </row>
-    <row r="148" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C148" s="166" t="s">
+      <c r="D152" s="140"/>
+      <c r="E152" s="140"/>
+      <c r="F152" s="140"/>
+      <c r="G152" s="140"/>
+      <c r="H152" s="140"/>
+      <c r="I152" s="140"/>
+      <c r="J152" s="140"/>
+      <c r="K152" s="140"/>
+      <c r="L152" s="140"/>
+      <c r="M152" s="140"/>
+      <c r="N152" s="140"/>
+      <c r="O152" s="140"/>
+      <c r="P152" s="140"/>
+      <c r="Q152" s="140"/>
+      <c r="R152" s="140"/>
+      <c r="S152" s="140"/>
+      <c r="T152" s="140"/>
+    </row>
+    <row r="153" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C153" s="140" t="s">
         <v>534</v>
       </c>
-      <c r="D148" s="166"/>
-      <c r="E148" s="166"/>
-      <c r="F148" s="166"/>
-      <c r="G148" s="166"/>
-      <c r="H148" s="166"/>
-      <c r="I148" s="166"/>
-      <c r="J148" s="166"/>
-      <c r="K148" s="166"/>
-      <c r="L148" s="166"/>
-      <c r="M148" s="166"/>
-      <c r="N148" s="166"/>
-      <c r="O148" s="166"/>
-      <c r="P148" s="166"/>
-      <c r="Q148" s="166"/>
-      <c r="R148" s="166"/>
-      <c r="S148" s="166"/>
-      <c r="T148" s="166"/>
-    </row>
-    <row r="149" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C149" s="166" t="s">
+      <c r="D153" s="140"/>
+      <c r="E153" s="140"/>
+      <c r="F153" s="140"/>
+      <c r="G153" s="140"/>
+      <c r="H153" s="140"/>
+      <c r="I153" s="140"/>
+      <c r="J153" s="140"/>
+      <c r="K153" s="140"/>
+      <c r="L153" s="140"/>
+      <c r="M153" s="140"/>
+      <c r="N153" s="140"/>
+      <c r="O153" s="140"/>
+      <c r="P153" s="140"/>
+      <c r="Q153" s="140"/>
+      <c r="R153" s="140"/>
+      <c r="S153" s="140"/>
+      <c r="T153" s="140"/>
+    </row>
+    <row r="154" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C154" s="140" t="s">
         <v>535</v>
       </c>
-      <c r="D149" s="166"/>
-      <c r="E149" s="166"/>
-      <c r="F149" s="166"/>
-      <c r="G149" s="166"/>
-      <c r="H149" s="166"/>
-      <c r="I149" s="166"/>
-      <c r="J149" s="166"/>
-      <c r="K149" s="166"/>
-      <c r="L149" s="166"/>
-      <c r="M149" s="166"/>
-      <c r="N149" s="166"/>
-      <c r="O149" s="166"/>
-      <c r="P149" s="166"/>
-      <c r="Q149" s="166"/>
-      <c r="R149" s="166"/>
-      <c r="S149" s="166"/>
-      <c r="T149" s="166"/>
-    </row>
-    <row r="150" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="151" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B151" s="17" t="s">
+      <c r="D154" s="140"/>
+      <c r="E154" s="140"/>
+      <c r="F154" s="140"/>
+      <c r="G154" s="140"/>
+      <c r="H154" s="140"/>
+      <c r="I154" s="140"/>
+      <c r="J154" s="140"/>
+      <c r="K154" s="140"/>
+      <c r="L154" s="140"/>
+      <c r="M154" s="140"/>
+      <c r="N154" s="140"/>
+      <c r="O154" s="140"/>
+      <c r="P154" s="140"/>
+      <c r="Q154" s="140"/>
+      <c r="R154" s="140"/>
+      <c r="S154" s="140"/>
+      <c r="T154" s="140"/>
+    </row>
+    <row r="155" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="156" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B156" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="C151" s="160" t="s">
+      <c r="C156" s="142" t="s">
         <v>537</v>
       </c>
-      <c r="D151" s="160"/>
-      <c r="E151" s="160"/>
-      <c r="F151" s="160"/>
-      <c r="G151" s="160"/>
-      <c r="H151" s="160"/>
-      <c r="I151" s="160"/>
-      <c r="J151" s="160"/>
-      <c r="K151" s="160"/>
-      <c r="L151" s="160"/>
-      <c r="M151" s="160"/>
-      <c r="N151" s="160"/>
-      <c r="O151" s="160"/>
-      <c r="P151" s="160"/>
-      <c r="Q151" s="160"/>
-      <c r="R151" s="160"/>
-      <c r="S151" s="160"/>
-      <c r="T151" s="160"/>
-    </row>
-    <row r="152" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C152" s="165" t="s">
+      <c r="D156" s="142"/>
+      <c r="E156" s="142"/>
+      <c r="F156" s="142"/>
+      <c r="G156" s="142"/>
+      <c r="H156" s="142"/>
+      <c r="I156" s="142"/>
+      <c r="J156" s="142"/>
+      <c r="K156" s="142"/>
+      <c r="L156" s="142"/>
+      <c r="M156" s="142"/>
+      <c r="N156" s="142"/>
+      <c r="O156" s="142"/>
+      <c r="P156" s="142"/>
+      <c r="Q156" s="142"/>
+      <c r="R156" s="142"/>
+      <c r="S156" s="142"/>
+      <c r="T156" s="142"/>
+    </row>
+    <row r="157" spans="2:20" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C157" s="141" t="s">
         <v>538</v>
       </c>
-      <c r="D152" s="165"/>
-      <c r="E152" s="165"/>
-      <c r="F152" s="165"/>
-      <c r="G152" s="165"/>
-      <c r="H152" s="165"/>
-      <c r="I152" s="165"/>
-      <c r="J152" s="165"/>
-      <c r="K152" s="165"/>
-      <c r="L152" s="165"/>
-      <c r="M152" s="165"/>
-      <c r="N152" s="165"/>
-      <c r="O152" s="165"/>
-      <c r="P152" s="165"/>
-      <c r="Q152" s="165"/>
-      <c r="R152" s="165"/>
-      <c r="S152" s="165"/>
-      <c r="T152" s="165"/>
-    </row>
-    <row r="153" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C153" s="165"/>
-      <c r="D153" s="165"/>
-      <c r="E153" s="165"/>
-      <c r="F153" s="165"/>
-      <c r="G153" s="165"/>
-      <c r="H153" s="165"/>
-      <c r="I153" s="165"/>
-      <c r="J153" s="165"/>
-      <c r="K153" s="165"/>
-      <c r="L153" s="165"/>
-      <c r="M153" s="165"/>
-      <c r="N153" s="165"/>
-      <c r="O153" s="165"/>
-      <c r="P153" s="165"/>
-      <c r="Q153" s="165"/>
-      <c r="R153" s="165"/>
-      <c r="S153" s="165"/>
-      <c r="T153" s="165"/>
-    </row>
-    <row r="154" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C154" s="166" t="s">
+      <c r="D157" s="141"/>
+      <c r="E157" s="141"/>
+      <c r="F157" s="141"/>
+      <c r="G157" s="141"/>
+      <c r="H157" s="141"/>
+      <c r="I157" s="141"/>
+      <c r="J157" s="141"/>
+      <c r="K157" s="141"/>
+      <c r="L157" s="141"/>
+      <c r="M157" s="141"/>
+      <c r="N157" s="141"/>
+      <c r="O157" s="141"/>
+      <c r="P157" s="141"/>
+      <c r="Q157" s="141"/>
+      <c r="R157" s="141"/>
+      <c r="S157" s="141"/>
+      <c r="T157" s="141"/>
+    </row>
+    <row r="158" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C158" s="141"/>
+      <c r="D158" s="141"/>
+      <c r="E158" s="141"/>
+      <c r="F158" s="141"/>
+      <c r="G158" s="141"/>
+      <c r="H158" s="141"/>
+      <c r="I158" s="141"/>
+      <c r="J158" s="141"/>
+      <c r="K158" s="141"/>
+      <c r="L158" s="141"/>
+      <c r="M158" s="141"/>
+      <c r="N158" s="141"/>
+      <c r="O158" s="141"/>
+      <c r="P158" s="141"/>
+      <c r="Q158" s="141"/>
+      <c r="R158" s="141"/>
+      <c r="S158" s="141"/>
+      <c r="T158" s="141"/>
+    </row>
+    <row r="159" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C159" s="140" t="s">
         <v>539</v>
       </c>
-      <c r="D154" s="166"/>
-      <c r="E154" s="166"/>
-      <c r="F154" s="166"/>
-      <c r="G154" s="166"/>
-      <c r="H154" s="166"/>
-      <c r="I154" s="166"/>
-      <c r="J154" s="166"/>
-      <c r="K154" s="166"/>
-      <c r="L154" s="166"/>
-      <c r="M154" s="166"/>
-      <c r="N154" s="166"/>
-      <c r="O154" s="166"/>
-      <c r="P154" s="166"/>
-      <c r="Q154" s="166"/>
-      <c r="R154" s="166"/>
-      <c r="S154" s="166"/>
-      <c r="T154" s="166"/>
-    </row>
-    <row r="155" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C155" s="166" t="s">
+      <c r="D159" s="140"/>
+      <c r="E159" s="140"/>
+      <c r="F159" s="140"/>
+      <c r="G159" s="140"/>
+      <c r="H159" s="140"/>
+      <c r="I159" s="140"/>
+      <c r="J159" s="140"/>
+      <c r="K159" s="140"/>
+      <c r="L159" s="140"/>
+      <c r="M159" s="140"/>
+      <c r="N159" s="140"/>
+      <c r="O159" s="140"/>
+      <c r="P159" s="140"/>
+      <c r="Q159" s="140"/>
+      <c r="R159" s="140"/>
+      <c r="S159" s="140"/>
+      <c r="T159" s="140"/>
+    </row>
+    <row r="160" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C160" s="140" t="s">
         <v>540</v>
       </c>
-      <c r="D155" s="166"/>
-      <c r="E155" s="166"/>
-      <c r="F155" s="166"/>
-      <c r="G155" s="166"/>
-      <c r="H155" s="166"/>
-      <c r="I155" s="166"/>
-      <c r="J155" s="166"/>
-      <c r="K155" s="166"/>
-      <c r="L155" s="166"/>
-      <c r="M155" s="166"/>
-      <c r="N155" s="166"/>
-      <c r="O155" s="166"/>
-      <c r="P155" s="166"/>
-      <c r="Q155" s="166"/>
-      <c r="R155" s="166"/>
-      <c r="S155" s="166"/>
-      <c r="T155" s="166"/>
-    </row>
-    <row r="156" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="157" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B157" s="17" t="s">
+      <c r="D160" s="140"/>
+      <c r="E160" s="140"/>
+      <c r="F160" s="140"/>
+      <c r="G160" s="140"/>
+      <c r="H160" s="140"/>
+      <c r="I160" s="140"/>
+      <c r="J160" s="140"/>
+      <c r="K160" s="140"/>
+      <c r="L160" s="140"/>
+      <c r="M160" s="140"/>
+      <c r="N160" s="140"/>
+      <c r="O160" s="140"/>
+      <c r="P160" s="140"/>
+      <c r="Q160" s="140"/>
+      <c r="R160" s="140"/>
+      <c r="S160" s="140"/>
+      <c r="T160" s="140"/>
+    </row>
+    <row r="161" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="162" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B162" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="C157" s="160" t="s">
+      <c r="C162" s="142" t="s">
         <v>543</v>
       </c>
-      <c r="D157" s="160"/>
-      <c r="E157" s="160"/>
-      <c r="F157" s="160"/>
-      <c r="G157" s="160"/>
-      <c r="H157" s="160"/>
-      <c r="I157" s="160"/>
-      <c r="J157" s="160"/>
-      <c r="K157" s="160"/>
-      <c r="L157" s="160"/>
-      <c r="M157" s="160"/>
-      <c r="N157" s="160"/>
-      <c r="O157" s="160"/>
-      <c r="P157" s="160"/>
-      <c r="Q157" s="160"/>
-      <c r="R157" s="160"/>
-      <c r="S157" s="160"/>
-      <c r="T157" s="160"/>
-    </row>
-    <row r="158" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="C158" s="166" t="s">
+      <c r="D162" s="142"/>
+      <c r="E162" s="142"/>
+      <c r="F162" s="142"/>
+      <c r="G162" s="142"/>
+      <c r="H162" s="142"/>
+      <c r="I162" s="142"/>
+      <c r="J162" s="142"/>
+      <c r="K162" s="142"/>
+      <c r="L162" s="142"/>
+      <c r="M162" s="142"/>
+      <c r="N162" s="142"/>
+      <c r="O162" s="142"/>
+      <c r="P162" s="142"/>
+      <c r="Q162" s="142"/>
+      <c r="R162" s="142"/>
+      <c r="S162" s="142"/>
+      <c r="T162" s="142"/>
+    </row>
+    <row r="163" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="C163" s="140" t="s">
         <v>545</v>
       </c>
-      <c r="D158" s="166"/>
-      <c r="E158" s="166"/>
-      <c r="F158" s="166"/>
-      <c r="G158" s="166"/>
-      <c r="H158" s="166"/>
-      <c r="I158" s="166"/>
-      <c r="J158" s="166"/>
-      <c r="K158" s="166"/>
-      <c r="L158" s="166"/>
-      <c r="M158" s="166"/>
-      <c r="N158" s="166"/>
-      <c r="O158" s="166"/>
-      <c r="P158" s="166"/>
-      <c r="Q158" s="166"/>
-      <c r="R158" s="166"/>
-      <c r="S158" s="166"/>
-      <c r="T158" s="166"/>
-    </row>
-    <row r="159" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C159" s="166" t="s">
+      <c r="D163" s="140"/>
+      <c r="E163" s="140"/>
+      <c r="F163" s="140"/>
+      <c r="G163" s="140"/>
+      <c r="H163" s="140"/>
+      <c r="I163" s="140"/>
+      <c r="J163" s="140"/>
+      <c r="K163" s="140"/>
+      <c r="L163" s="140"/>
+      <c r="M163" s="140"/>
+      <c r="N163" s="140"/>
+      <c r="O163" s="140"/>
+      <c r="P163" s="140"/>
+      <c r="Q163" s="140"/>
+      <c r="R163" s="140"/>
+      <c r="S163" s="140"/>
+      <c r="T163" s="140"/>
+    </row>
+    <row r="164" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C164" s="140" t="s">
         <v>544</v>
       </c>
-      <c r="D159" s="166"/>
-      <c r="E159" s="166"/>
-      <c r="F159" s="166"/>
-      <c r="G159" s="166"/>
-      <c r="H159" s="166"/>
-      <c r="I159" s="166"/>
-      <c r="J159" s="166"/>
-      <c r="K159" s="166"/>
-      <c r="L159" s="166"/>
-      <c r="M159" s="166"/>
-      <c r="N159" s="166"/>
-      <c r="O159" s="166"/>
-      <c r="P159" s="166"/>
-      <c r="Q159" s="166"/>
-      <c r="R159" s="166"/>
-      <c r="S159" s="166"/>
-      <c r="T159" s="166"/>
-    </row>
-    <row r="160" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C160" s="165" t="s">
+      <c r="D164" s="140"/>
+      <c r="E164" s="140"/>
+      <c r="F164" s="140"/>
+      <c r="G164" s="140"/>
+      <c r="H164" s="140"/>
+      <c r="I164" s="140"/>
+      <c r="J164" s="140"/>
+      <c r="K164" s="140"/>
+      <c r="L164" s="140"/>
+      <c r="M164" s="140"/>
+      <c r="N164" s="140"/>
+      <c r="O164" s="140"/>
+      <c r="P164" s="140"/>
+      <c r="Q164" s="140"/>
+      <c r="R164" s="140"/>
+      <c r="S164" s="140"/>
+      <c r="T164" s="140"/>
+    </row>
+    <row r="165" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C165" s="141" t="s">
         <v>546</v>
       </c>
-      <c r="D160" s="165"/>
-      <c r="E160" s="165"/>
-      <c r="F160" s="165"/>
-      <c r="G160" s="165"/>
-      <c r="H160" s="165"/>
-      <c r="I160" s="165"/>
-      <c r="J160" s="165"/>
-      <c r="K160" s="165"/>
-      <c r="L160" s="165"/>
-      <c r="M160" s="165"/>
-      <c r="N160" s="165"/>
-      <c r="O160" s="165"/>
-      <c r="P160" s="165"/>
-      <c r="Q160" s="165"/>
-      <c r="R160" s="165"/>
-      <c r="S160" s="165"/>
-      <c r="T160" s="165"/>
-    </row>
-    <row r="161" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C161" s="165"/>
-      <c r="D161" s="165"/>
-      <c r="E161" s="165"/>
-      <c r="F161" s="165"/>
-      <c r="G161" s="165"/>
-      <c r="H161" s="165"/>
-      <c r="I161" s="165"/>
-      <c r="J161" s="165"/>
-      <c r="K161" s="165"/>
-      <c r="L161" s="165"/>
-      <c r="M161" s="165"/>
-      <c r="N161" s="165"/>
-      <c r="O161" s="165"/>
-      <c r="P161" s="165"/>
-      <c r="Q161" s="165"/>
-      <c r="R161" s="165"/>
-      <c r="S161" s="165"/>
-      <c r="T161" s="165"/>
-    </row>
-    <row r="162" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="C162" s="166" t="s">
+      <c r="D165" s="141"/>
+      <c r="E165" s="141"/>
+      <c r="F165" s="141"/>
+      <c r="G165" s="141"/>
+      <c r="H165" s="141"/>
+      <c r="I165" s="141"/>
+      <c r="J165" s="141"/>
+      <c r="K165" s="141"/>
+      <c r="L165" s="141"/>
+      <c r="M165" s="141"/>
+      <c r="N165" s="141"/>
+      <c r="O165" s="141"/>
+      <c r="P165" s="141"/>
+      <c r="Q165" s="141"/>
+      <c r="R165" s="141"/>
+      <c r="S165" s="141"/>
+      <c r="T165" s="141"/>
+    </row>
+    <row r="166" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C166" s="141"/>
+      <c r="D166" s="141"/>
+      <c r="E166" s="141"/>
+      <c r="F166" s="141"/>
+      <c r="G166" s="141"/>
+      <c r="H166" s="141"/>
+      <c r="I166" s="141"/>
+      <c r="J166" s="141"/>
+      <c r="K166" s="141"/>
+      <c r="L166" s="141"/>
+      <c r="M166" s="141"/>
+      <c r="N166" s="141"/>
+      <c r="O166" s="141"/>
+      <c r="P166" s="141"/>
+      <c r="Q166" s="141"/>
+      <c r="R166" s="141"/>
+      <c r="S166" s="141"/>
+      <c r="T166" s="141"/>
+    </row>
+    <row r="167" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C167" s="140" t="s">
         <v>547</v>
       </c>
-      <c r="D162" s="166"/>
-      <c r="E162" s="166"/>
-      <c r="F162" s="166"/>
-      <c r="G162" s="166"/>
-      <c r="H162" s="166"/>
-      <c r="I162" s="166"/>
-      <c r="J162" s="166"/>
-      <c r="K162" s="166"/>
-      <c r="L162" s="166"/>
-      <c r="M162" s="166"/>
-      <c r="N162" s="166"/>
-      <c r="O162" s="166"/>
-      <c r="P162" s="166"/>
-      <c r="Q162" s="166"/>
-      <c r="R162" s="166"/>
-      <c r="S162" s="166"/>
-      <c r="T162" s="166"/>
-    </row>
-    <row r="164" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B164" s="169" t="s">
+      <c r="D167" s="140"/>
+      <c r="E167" s="140"/>
+      <c r="F167" s="140"/>
+      <c r="G167" s="140"/>
+      <c r="H167" s="140"/>
+      <c r="I167" s="140"/>
+      <c r="J167" s="140"/>
+      <c r="K167" s="140"/>
+      <c r="L167" s="140"/>
+      <c r="M167" s="140"/>
+      <c r="N167" s="140"/>
+      <c r="O167" s="140"/>
+      <c r="P167" s="140"/>
+      <c r="Q167" s="140"/>
+      <c r="R167" s="140"/>
+      <c r="S167" s="140"/>
+      <c r="T167" s="140"/>
+    </row>
+    <row r="169" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B169" s="137" t="s">
         <v>548</v>
       </c>
-      <c r="C164" s="169"/>
-      <c r="D164" s="117" t="s">
+      <c r="C169" s="137"/>
+      <c r="D169" s="138" t="s">
         <v>549</v>
       </c>
-      <c r="E164" s="117"/>
-      <c r="F164" s="117"/>
-      <c r="G164" s="117"/>
-      <c r="H164" s="117"/>
-      <c r="I164" s="117"/>
-      <c r="J164" s="117"/>
-      <c r="K164" s="117"/>
-      <c r="L164" s="117"/>
-      <c r="M164" s="117"/>
-      <c r="N164" s="117"/>
-      <c r="O164" s="117"/>
-      <c r="P164" s="117"/>
-      <c r="Q164" s="117"/>
-      <c r="R164" s="117"/>
-      <c r="S164" s="117"/>
-      <c r="T164" s="117"/>
-    </row>
-    <row r="166" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B166" s="114" t="s">
+      <c r="E169" s="138"/>
+      <c r="F169" s="138"/>
+      <c r="G169" s="138"/>
+      <c r="H169" s="138"/>
+      <c r="I169" s="138"/>
+      <c r="J169" s="138"/>
+      <c r="K169" s="138"/>
+      <c r="L169" s="138"/>
+      <c r="M169" s="138"/>
+      <c r="N169" s="138"/>
+      <c r="O169" s="138"/>
+      <c r="P169" s="138"/>
+      <c r="Q169" s="138"/>
+      <c r="R169" s="138"/>
+      <c r="S169" s="138"/>
+      <c r="T169" s="138"/>
+    </row>
+    <row r="171" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B171" s="114" t="s">
         <v>550</v>
       </c>
-      <c r="C166" s="114"/>
-      <c r="D166" s="114"/>
-      <c r="E166" s="114"/>
-      <c r="F166" s="170" t="s">
+      <c r="C171" s="114"/>
+      <c r="D171" s="114"/>
+      <c r="E171" s="114"/>
+      <c r="F171" s="123" t="s">
         <v>552</v>
       </c>
-      <c r="G166" s="170"/>
-      <c r="H166" s="170"/>
-      <c r="I166" s="170"/>
-      <c r="J166" s="170"/>
-      <c r="K166" s="170"/>
-      <c r="L166" s="170"/>
-      <c r="M166" s="170"/>
-    </row>
-    <row r="167" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="F167" s="168" t="s">
+      <c r="G171" s="123"/>
+      <c r="H171" s="123"/>
+      <c r="I171" s="123"/>
+      <c r="J171" s="123"/>
+      <c r="K171" s="123"/>
+      <c r="L171" s="123"/>
+      <c r="M171" s="123"/>
+    </row>
+    <row r="172" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F172" s="136" t="s">
         <v>551</v>
       </c>
-      <c r="G167" s="168"/>
-      <c r="H167" s="168"/>
-      <c r="I167" s="168"/>
-      <c r="J167" s="168"/>
-      <c r="K167" s="168"/>
-      <c r="L167" s="40" t="s">
+      <c r="G172" s="136"/>
+      <c r="H172" s="136"/>
+      <c r="I172" s="136"/>
+      <c r="J172" s="136"/>
+      <c r="K172" s="136"/>
+      <c r="L172" s="40" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="168" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="F168" s="168" t="s">
+    <row r="173" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F173" s="136" t="s">
         <v>553</v>
       </c>
-      <c r="G168" s="168"/>
-      <c r="H168" s="168"/>
-      <c r="I168" s="168"/>
-      <c r="J168" s="168"/>
-      <c r="K168" s="168"/>
-      <c r="L168" s="40" t="s">
+      <c r="G173" s="136"/>
+      <c r="H173" s="136"/>
+      <c r="I173" s="136"/>
+      <c r="J173" s="136"/>
+      <c r="K173" s="136"/>
+      <c r="L173" s="40" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="169" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="F169" s="168" t="s">
+    <row r="174" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F174" s="136" t="s">
         <v>554</v>
       </c>
-      <c r="G169" s="168"/>
-      <c r="H169" s="168"/>
-      <c r="I169" s="168"/>
-      <c r="J169" s="168"/>
-      <c r="K169" s="168"/>
-    </row>
-    <row r="170" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="F170" s="168" t="s">
+      <c r="G174" s="136"/>
+      <c r="H174" s="136"/>
+      <c r="I174" s="136"/>
+      <c r="J174" s="136"/>
+      <c r="K174" s="136"/>
+    </row>
+    <row r="175" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F175" s="136" t="s">
         <v>555</v>
       </c>
-      <c r="G170" s="168"/>
-      <c r="H170" s="168"/>
-      <c r="I170" s="168"/>
-      <c r="J170" s="168"/>
-      <c r="K170" s="168"/>
-    </row>
-    <row r="172" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="B172" s="167" t="s">
+      <c r="G175" s="136"/>
+      <c r="H175" s="136"/>
+      <c r="I175" s="136"/>
+      <c r="J175" s="136"/>
+      <c r="K175" s="136"/>
+    </row>
+    <row r="177" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="B177" s="135" t="s">
         <v>559</v>
       </c>
-      <c r="C172" s="167"/>
-      <c r="D172" s="117" t="s">
+      <c r="C177" s="135"/>
+      <c r="D177" s="138" t="s">
         <v>558</v>
       </c>
-      <c r="E172" s="117"/>
-      <c r="F172" s="117"/>
-      <c r="G172" s="117"/>
-      <c r="H172" s="117"/>
-      <c r="I172" s="117"/>
-      <c r="J172" s="117"/>
-      <c r="K172" s="117"/>
-      <c r="L172" s="117"/>
-      <c r="M172" s="117"/>
-      <c r="N172" s="117"/>
-      <c r="O172" s="117"/>
-      <c r="P172" s="117"/>
-      <c r="Q172" s="117"/>
-      <c r="R172" s="117"/>
-      <c r="S172" s="117"/>
-      <c r="T172" s="117"/>
-    </row>
-    <row r="173" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D173" s="118" t="s">
+      <c r="E177" s="138"/>
+      <c r="F177" s="138"/>
+      <c r="G177" s="138"/>
+      <c r="H177" s="138"/>
+      <c r="I177" s="138"/>
+      <c r="J177" s="138"/>
+      <c r="K177" s="138"/>
+      <c r="L177" s="138"/>
+      <c r="M177" s="138"/>
+      <c r="N177" s="138"/>
+      <c r="O177" s="138"/>
+      <c r="P177" s="138"/>
+      <c r="Q177" s="138"/>
+      <c r="R177" s="138"/>
+      <c r="S177" s="138"/>
+      <c r="T177" s="138"/>
+    </row>
+    <row r="178" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="D178" s="186" t="s">
         <v>560</v>
       </c>
-      <c r="E173" s="118"/>
-      <c r="F173" s="118"/>
-      <c r="G173" s="118"/>
-      <c r="H173" s="118"/>
-      <c r="I173" s="118"/>
-      <c r="J173" s="118"/>
-      <c r="K173" s="118"/>
-      <c r="L173" s="118"/>
-      <c r="M173" s="118"/>
-      <c r="N173" s="118"/>
-      <c r="O173" s="118"/>
-      <c r="P173" s="118"/>
-      <c r="Q173" s="118"/>
-      <c r="R173" s="118"/>
-      <c r="S173" s="118"/>
-      <c r="T173" s="118"/>
-    </row>
-    <row r="174" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D174" s="118"/>
-      <c r="E174" s="118"/>
-      <c r="F174" s="118"/>
-      <c r="G174" s="118"/>
-      <c r="H174" s="118"/>
-      <c r="I174" s="118"/>
-      <c r="J174" s="118"/>
-      <c r="K174" s="118"/>
-      <c r="L174" s="118"/>
-      <c r="M174" s="118"/>
-      <c r="N174" s="118"/>
-      <c r="O174" s="118"/>
-      <c r="P174" s="118"/>
-      <c r="Q174" s="118"/>
-      <c r="R174" s="118"/>
-      <c r="S174" s="118"/>
-      <c r="T174" s="118"/>
-    </row>
-    <row r="175" spans="2:20" x14ac:dyDescent="0.5">
-      <c r="D175" s="118"/>
-      <c r="E175" s="118"/>
-      <c r="F175" s="118"/>
-      <c r="G175" s="118"/>
-      <c r="H175" s="118"/>
-      <c r="I175" s="118"/>
-      <c r="J175" s="118"/>
-      <c r="K175" s="118"/>
-      <c r="L175" s="118"/>
-      <c r="M175" s="118"/>
-      <c r="N175" s="118"/>
-      <c r="O175" s="118"/>
-      <c r="P175" s="118"/>
-      <c r="Q175" s="118"/>
-      <c r="R175" s="118"/>
-      <c r="S175" s="118"/>
-      <c r="T175" s="118"/>
+      <c r="E178" s="186"/>
+      <c r="F178" s="186"/>
+      <c r="G178" s="186"/>
+      <c r="H178" s="186"/>
+      <c r="I178" s="186"/>
+      <c r="J178" s="186"/>
+      <c r="K178" s="186"/>
+      <c r="L178" s="186"/>
+      <c r="M178" s="186"/>
+      <c r="N178" s="186"/>
+      <c r="O178" s="186"/>
+      <c r="P178" s="186"/>
+      <c r="Q178" s="186"/>
+      <c r="R178" s="186"/>
+      <c r="S178" s="186"/>
+      <c r="T178" s="186"/>
+    </row>
+    <row r="179" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="D179" s="186"/>
+      <c r="E179" s="186"/>
+      <c r="F179" s="186"/>
+      <c r="G179" s="186"/>
+      <c r="H179" s="186"/>
+      <c r="I179" s="186"/>
+      <c r="J179" s="186"/>
+      <c r="K179" s="186"/>
+      <c r="L179" s="186"/>
+      <c r="M179" s="186"/>
+      <c r="N179" s="186"/>
+      <c r="O179" s="186"/>
+      <c r="P179" s="186"/>
+      <c r="Q179" s="186"/>
+      <c r="R179" s="186"/>
+      <c r="S179" s="186"/>
+      <c r="T179" s="186"/>
+    </row>
+    <row r="180" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="D180" s="186"/>
+      <c r="E180" s="186"/>
+      <c r="F180" s="186"/>
+      <c r="G180" s="186"/>
+      <c r="H180" s="186"/>
+      <c r="I180" s="186"/>
+      <c r="J180" s="186"/>
+      <c r="K180" s="186"/>
+      <c r="L180" s="186"/>
+      <c r="M180" s="186"/>
+      <c r="N180" s="186"/>
+      <c r="O180" s="186"/>
+      <c r="P180" s="186"/>
+      <c r="Q180" s="186"/>
+      <c r="R180" s="186"/>
+      <c r="S180" s="186"/>
+      <c r="T180" s="186"/>
+    </row>
+    <row r="183" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="B183" s="175" t="s">
+        <v>563</v>
+      </c>
+      <c r="C183" s="175"/>
+      <c r="D183" s="175"/>
+      <c r="E183" s="175"/>
+    </row>
+    <row r="184" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="B184" s="175"/>
+      <c r="C184" s="175"/>
+      <c r="D184" s="175"/>
+      <c r="E184" s="175"/>
+    </row>
+    <row r="186" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B186" s="164" t="s">
+        <v>564</v>
+      </c>
+      <c r="C186" s="164"/>
+      <c r="D186" s="185" t="s">
+        <v>565</v>
+      </c>
+      <c r="E186" s="185"/>
+      <c r="F186" s="185"/>
+      <c r="G186" s="185"/>
+      <c r="H186" s="185"/>
+      <c r="I186" s="185"/>
+      <c r="J186" s="185"/>
+      <c r="K186" s="185"/>
+      <c r="L186" s="185"/>
+      <c r="M186" s="185"/>
+      <c r="N186" s="185"/>
+      <c r="O186" s="185"/>
+      <c r="P186" s="185"/>
+      <c r="Q186" s="185"/>
+      <c r="R186" s="185"/>
+      <c r="S186" s="185"/>
+      <c r="T186" s="185"/>
+      <c r="U186" s="85"/>
+    </row>
+    <row r="187" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="B187" s="76"/>
+      <c r="C187" s="76"/>
+      <c r="D187" s="185"/>
+      <c r="E187" s="185"/>
+      <c r="F187" s="185"/>
+      <c r="G187" s="185"/>
+      <c r="H187" s="185"/>
+      <c r="I187" s="185"/>
+      <c r="J187" s="185"/>
+      <c r="K187" s="185"/>
+      <c r="L187" s="185"/>
+      <c r="M187" s="185"/>
+      <c r="N187" s="185"/>
+      <c r="O187" s="185"/>
+      <c r="P187" s="185"/>
+      <c r="Q187" s="185"/>
+      <c r="R187" s="185"/>
+      <c r="S187" s="185"/>
+      <c r="T187" s="185"/>
+      <c r="U187" s="85"/>
+    </row>
+    <row r="188" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="D188" s="185" t="s">
+        <v>566</v>
+      </c>
+      <c r="E188" s="185"/>
+      <c r="F188" s="185"/>
+      <c r="G188" s="185"/>
+      <c r="H188" s="185"/>
+      <c r="I188" s="185"/>
+      <c r="J188" s="185"/>
+      <c r="K188" s="185"/>
+      <c r="L188" s="185"/>
+      <c r="M188" s="185"/>
+      <c r="N188" s="185"/>
+      <c r="O188" s="185"/>
+      <c r="P188" s="185"/>
+      <c r="Q188" s="185"/>
+      <c r="R188" s="185"/>
+      <c r="S188" s="185"/>
+      <c r="T188" s="185"/>
+    </row>
+    <row r="191" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="B191" s="169" t="s">
+        <v>567</v>
+      </c>
+      <c r="C191" s="170"/>
+      <c r="D191" s="191" t="s">
+        <v>568</v>
+      </c>
+      <c r="E191" s="191"/>
+      <c r="F191" s="116" t="s">
+        <v>572</v>
+      </c>
+      <c r="G191" s="116"/>
+      <c r="H191" s="119"/>
+      <c r="I191" s="120"/>
+      <c r="J191" s="120"/>
+      <c r="K191" s="120"/>
+      <c r="L191" s="118"/>
+      <c r="M191" s="118"/>
+      <c r="N191" s="118"/>
+      <c r="O191" s="118"/>
+      <c r="P191" s="118"/>
+      <c r="Q191" s="118"/>
+      <c r="R191" s="118"/>
+      <c r="S191" s="118"/>
+      <c r="T191" s="118"/>
+    </row>
+    <row r="192" spans="2:21" x14ac:dyDescent="0.5">
+      <c r="D192" s="191" t="s">
+        <v>569</v>
+      </c>
+      <c r="E192" s="191"/>
+      <c r="F192" s="116" t="s">
+        <v>574</v>
+      </c>
+      <c r="G192" s="116"/>
+      <c r="H192" s="119"/>
+      <c r="I192" s="120"/>
+      <c r="J192" s="120"/>
+      <c r="K192" s="120"/>
+      <c r="L192" s="118"/>
+      <c r="M192" s="118"/>
+      <c r="N192" s="118"/>
+      <c r="O192" s="118"/>
+      <c r="P192" s="118"/>
+      <c r="Q192" s="118"/>
+      <c r="R192" s="118"/>
+      <c r="S192" s="118"/>
+      <c r="T192" s="118"/>
+    </row>
+    <row r="193" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D193" s="191" t="s">
+        <v>570</v>
+      </c>
+      <c r="E193" s="191"/>
+      <c r="F193" s="116" t="s">
+        <v>575</v>
+      </c>
+      <c r="G193" s="116"/>
+      <c r="H193" s="119"/>
+      <c r="I193" s="120"/>
+      <c r="J193" s="120"/>
+      <c r="K193" s="120"/>
+      <c r="L193" s="118"/>
+      <c r="M193" s="118"/>
+      <c r="N193" s="118"/>
+      <c r="O193" s="118"/>
+      <c r="P193" s="118"/>
+      <c r="Q193" s="118"/>
+      <c r="R193" s="118"/>
+      <c r="S193" s="118"/>
+      <c r="T193" s="118"/>
+    </row>
+    <row r="194" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D194" s="191" t="s">
+        <v>571</v>
+      </c>
+      <c r="E194" s="191"/>
+      <c r="F194" s="116" t="s">
+        <v>573</v>
+      </c>
+      <c r="G194" s="116"/>
+      <c r="H194" s="119"/>
+      <c r="I194" s="120"/>
+      <c r="J194" s="120"/>
+      <c r="K194" s="120"/>
+      <c r="L194" s="118"/>
+      <c r="M194" s="118"/>
+      <c r="N194" s="118"/>
+      <c r="O194" s="118"/>
+      <c r="P194" s="118"/>
+      <c r="Q194" s="118"/>
+      <c r="R194" s="118"/>
+      <c r="S194" s="118"/>
+      <c r="T194" s="118"/>
+    </row>
+    <row r="196" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="197" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B197" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C197" s="128" t="s">
+        <v>580</v>
+      </c>
+      <c r="D197" s="128"/>
+      <c r="E197" s="128"/>
+      <c r="F197" s="128"/>
+      <c r="G197" s="128"/>
+      <c r="H197" s="128"/>
+      <c r="I197" s="128"/>
+      <c r="J197" s="128"/>
+      <c r="K197" s="128"/>
+      <c r="L197" s="128"/>
+      <c r="M197" s="128"/>
+      <c r="N197" s="128"/>
+      <c r="O197" s="128"/>
+      <c r="P197" s="128"/>
+      <c r="Q197" s="128"/>
+      <c r="R197" s="128"/>
+      <c r="S197" s="128"/>
+      <c r="T197" s="128"/>
+    </row>
+    <row r="198" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B198" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C198" s="128" t="s">
+        <v>581</v>
+      </c>
+      <c r="D198" s="128"/>
+      <c r="E198" s="128"/>
+      <c r="F198" s="128"/>
+      <c r="G198" s="128"/>
+      <c r="H198" s="128"/>
+      <c r="I198" s="128"/>
+      <c r="J198" s="128"/>
+      <c r="K198" s="128"/>
+      <c r="L198" s="128"/>
+      <c r="M198" s="128"/>
+      <c r="N198" s="128"/>
+      <c r="O198" s="128"/>
+      <c r="P198" s="128"/>
+      <c r="Q198" s="128"/>
+      <c r="R198" s="128"/>
+      <c r="S198" s="128"/>
+      <c r="T198" s="128"/>
+    </row>
+    <row r="199" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="200" spans="2:20" ht="20.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K200" s="190" t="s">
+        <v>578</v>
+      </c>
+      <c r="L200" s="190"/>
+      <c r="M200" s="190"/>
+    </row>
+    <row r="201" spans="2:20" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B201" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="C201" s="139" t="s">
+        <v>577</v>
+      </c>
+      <c r="D201" s="139"/>
+      <c r="E201" s="139"/>
+      <c r="F201" s="139"/>
+      <c r="G201" s="139"/>
+      <c r="H201" s="139"/>
+      <c r="I201" s="139"/>
+      <c r="J201" s="139"/>
+      <c r="K201" s="60"/>
+    </row>
+    <row r="202" spans="2:20" ht="20.25" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="K202" s="190" t="s">
+        <v>579</v>
+      </c>
+      <c r="L202" s="190"/>
+      <c r="M202" s="190"/>
+    </row>
+    <row r="205" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B205" s="251" t="s">
+        <v>597</v>
+      </c>
+      <c r="C205" s="251"/>
+      <c r="D205" s="251"/>
+    </row>
+    <row r="206" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D206" s="129" t="s">
+        <v>588</v>
+      </c>
+      <c r="E206" s="129"/>
+      <c r="F206" s="129" t="s">
+        <v>582</v>
+      </c>
+      <c r="G206" s="129"/>
+      <c r="H206" s="129"/>
+      <c r="I206" s="129"/>
+      <c r="J206" s="129"/>
+      <c r="K206" s="129"/>
+      <c r="L206" s="129"/>
+      <c r="M206" s="129"/>
+    </row>
+    <row r="207" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D207" s="250" t="s">
+        <v>184</v>
+      </c>
+      <c r="E207" s="250"/>
+      <c r="F207" s="130" t="s">
+        <v>583</v>
+      </c>
+      <c r="G207" s="130"/>
+      <c r="H207" s="130"/>
+      <c r="I207" s="130"/>
+      <c r="J207" s="130"/>
+      <c r="K207" s="130"/>
+      <c r="L207" s="130"/>
+      <c r="M207" s="130"/>
+    </row>
+    <row r="208" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D208" s="250" t="s">
+        <v>200</v>
+      </c>
+      <c r="E208" s="250"/>
+      <c r="F208" s="131" t="s">
+        <v>584</v>
+      </c>
+      <c r="G208" s="131"/>
+      <c r="H208" s="132" t="s">
+        <v>585</v>
+      </c>
+      <c r="I208" s="132"/>
+      <c r="J208" s="132"/>
+      <c r="K208" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="L208" s="133"/>
+      <c r="M208" s="133"/>
+    </row>
+    <row r="209" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="D209" s="250" t="s">
+        <v>208</v>
+      </c>
+      <c r="E209" s="250"/>
+      <c r="F209" s="132" t="s">
+        <v>585</v>
+      </c>
+      <c r="G209" s="132"/>
+      <c r="H209" s="132"/>
+      <c r="I209" s="133" t="s">
+        <v>586</v>
+      </c>
+      <c r="J209" s="133"/>
+      <c r="K209" s="133"/>
+      <c r="L209" s="134" t="s">
+        <v>587</v>
+      </c>
+      <c r="M209" s="134"/>
+    </row>
+    <row r="211" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B211" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C211" s="125" t="s">
+        <v>589</v>
+      </c>
+      <c r="D211" s="125"/>
+      <c r="E211" s="125"/>
+      <c r="F211" s="125"/>
+      <c r="G211" s="125"/>
+      <c r="H211" s="125"/>
+      <c r="I211" s="125"/>
+      <c r="J211" s="125"/>
+      <c r="K211" s="125"/>
+      <c r="L211" s="125"/>
+      <c r="M211" s="125"/>
+      <c r="N211" s="125"/>
+      <c r="O211" s="125"/>
+      <c r="P211" s="125"/>
+      <c r="Q211" s="125"/>
+      <c r="R211" s="125"/>
+      <c r="S211" s="125"/>
+      <c r="T211" s="125"/>
+    </row>
+    <row r="212" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C212" s="125"/>
+      <c r="D212" s="125"/>
+      <c r="E212" s="125"/>
+      <c r="F212" s="125"/>
+      <c r="G212" s="125"/>
+      <c r="H212" s="125"/>
+      <c r="I212" s="125"/>
+      <c r="J212" s="125"/>
+      <c r="K212" s="125"/>
+      <c r="L212" s="125"/>
+      <c r="M212" s="125"/>
+      <c r="N212" s="125"/>
+      <c r="O212" s="125"/>
+      <c r="P212" s="125"/>
+      <c r="Q212" s="125"/>
+      <c r="R212" s="125"/>
+      <c r="S212" s="125"/>
+      <c r="T212" s="125"/>
+    </row>
+    <row r="214" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B214" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C214" s="125" t="s">
+        <v>590</v>
+      </c>
+      <c r="D214" s="125"/>
+      <c r="E214" s="125"/>
+      <c r="F214" s="125"/>
+      <c r="G214" s="125"/>
+      <c r="H214" s="125"/>
+      <c r="I214" s="125"/>
+      <c r="J214" s="125"/>
+      <c r="K214" s="125"/>
+      <c r="L214" s="125"/>
+      <c r="M214" s="125"/>
+      <c r="N214" s="125"/>
+      <c r="O214" s="125"/>
+      <c r="P214" s="125"/>
+      <c r="Q214" s="125"/>
+      <c r="R214" s="125"/>
+      <c r="S214" s="125"/>
+      <c r="T214" s="125"/>
+    </row>
+    <row r="215" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C215" s="125"/>
+      <c r="D215" s="125"/>
+      <c r="E215" s="125"/>
+      <c r="F215" s="125"/>
+      <c r="G215" s="125"/>
+      <c r="H215" s="125"/>
+      <c r="I215" s="125"/>
+      <c r="J215" s="125"/>
+      <c r="K215" s="125"/>
+      <c r="L215" s="125"/>
+      <c r="M215" s="125"/>
+      <c r="N215" s="125"/>
+      <c r="O215" s="125"/>
+      <c r="P215" s="125"/>
+      <c r="Q215" s="125"/>
+      <c r="R215" s="125"/>
+      <c r="S215" s="125"/>
+      <c r="T215" s="125"/>
+    </row>
+    <row r="216" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C216" s="125"/>
+      <c r="D216" s="125"/>
+      <c r="E216" s="125"/>
+      <c r="F216" s="125"/>
+      <c r="G216" s="125"/>
+      <c r="H216" s="125"/>
+      <c r="I216" s="125"/>
+      <c r="J216" s="125"/>
+      <c r="K216" s="125"/>
+      <c r="L216" s="125"/>
+      <c r="M216" s="125"/>
+      <c r="N216" s="125"/>
+      <c r="O216" s="125"/>
+      <c r="P216" s="125"/>
+      <c r="Q216" s="125"/>
+      <c r="R216" s="125"/>
+      <c r="S216" s="125"/>
+      <c r="T216" s="125"/>
+    </row>
+    <row r="218" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B218" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C218" s="125" t="s">
+        <v>595</v>
+      </c>
+      <c r="D218" s="125"/>
+      <c r="E218" s="125"/>
+      <c r="F218" s="125"/>
+      <c r="G218" s="125"/>
+      <c r="H218" s="125"/>
+      <c r="I218" s="125"/>
+      <c r="J218" s="125"/>
+      <c r="K218" s="125"/>
+      <c r="L218" s="125"/>
+      <c r="M218" s="125"/>
+      <c r="N218" s="125"/>
+      <c r="O218" s="125"/>
+      <c r="P218" s="125"/>
+      <c r="Q218" s="125"/>
+      <c r="R218" s="125"/>
+      <c r="S218" s="125"/>
+      <c r="T218" s="125"/>
+    </row>
+    <row r="219" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C219" s="125"/>
+      <c r="D219" s="125"/>
+      <c r="E219" s="125"/>
+      <c r="F219" s="125"/>
+      <c r="G219" s="125"/>
+      <c r="H219" s="125"/>
+      <c r="I219" s="125"/>
+      <c r="J219" s="125"/>
+      <c r="K219" s="125"/>
+      <c r="L219" s="125"/>
+      <c r="M219" s="125"/>
+      <c r="N219" s="125"/>
+      <c r="O219" s="125"/>
+      <c r="P219" s="125"/>
+      <c r="Q219" s="125"/>
+      <c r="R219" s="125"/>
+      <c r="S219" s="125"/>
+      <c r="T219" s="125"/>
+    </row>
+    <row r="220" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C220" s="125"/>
+      <c r="D220" s="125"/>
+      <c r="E220" s="125"/>
+      <c r="F220" s="125"/>
+      <c r="G220" s="125"/>
+      <c r="H220" s="125"/>
+      <c r="I220" s="125"/>
+      <c r="J220" s="125"/>
+      <c r="K220" s="125"/>
+      <c r="L220" s="125"/>
+      <c r="M220" s="125"/>
+      <c r="N220" s="125"/>
+      <c r="O220" s="125"/>
+      <c r="P220" s="125"/>
+      <c r="Q220" s="125"/>
+      <c r="R220" s="125"/>
+      <c r="S220" s="125"/>
+      <c r="T220" s="125"/>
+    </row>
+    <row r="222" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B222" s="126" t="s">
+        <v>594</v>
+      </c>
+      <c r="C222" s="127"/>
+      <c r="D222" s="127"/>
+      <c r="E222" s="127"/>
+      <c r="F222" s="127"/>
+      <c r="G222" s="128" t="s">
+        <v>591</v>
+      </c>
+      <c r="H222" s="128"/>
+      <c r="I222" s="128"/>
+      <c r="J222" s="128"/>
+      <c r="K222" s="128"/>
+      <c r="L222" s="128"/>
+      <c r="M222" s="128"/>
+      <c r="N222" s="128"/>
+      <c r="O222" s="128"/>
+      <c r="P222" s="128"/>
+      <c r="Q222" s="128"/>
+      <c r="R222" s="128"/>
+      <c r="S222" s="128"/>
+      <c r="T222" s="128"/>
+    </row>
+    <row r="223" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="G223" s="122" t="s">
+        <v>592</v>
+      </c>
+      <c r="H223" s="122"/>
+      <c r="I223" s="122"/>
+      <c r="J223" s="122"/>
+      <c r="K223" s="122"/>
+      <c r="L223" s="115"/>
+      <c r="M223" s="115"/>
+      <c r="N223" s="115"/>
+      <c r="O223" s="115"/>
+      <c r="P223" s="115"/>
+      <c r="Q223" s="115"/>
+      <c r="R223" s="115"/>
+      <c r="S223" s="115"/>
+      <c r="T223" s="115"/>
+    </row>
+    <row r="224" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="G224" s="122" t="s">
+        <v>593</v>
+      </c>
+      <c r="H224" s="122"/>
+      <c r="I224" s="122"/>
+      <c r="J224" s="122"/>
+      <c r="K224" s="122"/>
+      <c r="L224" s="115"/>
+      <c r="M224" s="115"/>
+      <c r="N224" s="115"/>
+      <c r="O224" s="115"/>
+      <c r="P224" s="115"/>
+      <c r="Q224" s="115"/>
+      <c r="R224" s="115"/>
+      <c r="S224" s="115"/>
+      <c r="T224" s="115"/>
+    </row>
+    <row r="226" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B226" s="114" t="s">
+        <v>550</v>
+      </c>
+      <c r="C226" s="114"/>
+      <c r="D226" s="114"/>
+      <c r="E226" s="114"/>
+      <c r="F226" s="124" t="s">
+        <v>596</v>
+      </c>
+      <c r="G226" s="124"/>
+      <c r="H226" s="124"/>
+      <c r="I226" s="124"/>
+      <c r="J226" s="124"/>
+      <c r="K226" s="124"/>
+      <c r="L226" s="124"/>
+      <c r="M226" s="124"/>
+      <c r="N226" s="124"/>
+      <c r="O226" s="124"/>
+      <c r="P226" s="124"/>
+      <c r="Q226" s="124"/>
+      <c r="R226" s="124"/>
+      <c r="S226" s="124"/>
+      <c r="T226" s="124"/>
+    </row>
+    <row r="227" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F227" s="124"/>
+      <c r="G227" s="124"/>
+      <c r="H227" s="124"/>
+      <c r="I227" s="124"/>
+      <c r="J227" s="124"/>
+      <c r="K227" s="124"/>
+      <c r="L227" s="124"/>
+      <c r="M227" s="124"/>
+      <c r="N227" s="124"/>
+      <c r="O227" s="124"/>
+      <c r="P227" s="124"/>
+      <c r="Q227" s="124"/>
+      <c r="R227" s="124"/>
+      <c r="S227" s="124"/>
+      <c r="T227" s="124"/>
+    </row>
+    <row r="228" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="F228" s="124"/>
+      <c r="G228" s="124"/>
+      <c r="H228" s="124"/>
+      <c r="I228" s="124"/>
+      <c r="J228" s="124"/>
+      <c r="K228" s="124"/>
+      <c r="L228" s="124"/>
+      <c r="M228" s="124"/>
+      <c r="N228" s="124"/>
+      <c r="O228" s="124"/>
+      <c r="P228" s="124"/>
+      <c r="Q228" s="124"/>
+      <c r="R228" s="124"/>
+      <c r="S228" s="124"/>
+      <c r="T228" s="124"/>
+    </row>
+    <row r="230" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B230" s="251" t="s">
+        <v>603</v>
+      </c>
+      <c r="C230" s="251"/>
+      <c r="D230" s="251"/>
+    </row>
+    <row r="231" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C231" s="129" t="s">
+        <v>588</v>
+      </c>
+      <c r="D231" s="129"/>
+      <c r="E231" s="129" t="s">
+        <v>582</v>
+      </c>
+      <c r="F231" s="129"/>
+      <c r="G231" s="129"/>
+      <c r="H231" s="129"/>
+      <c r="I231" s="129"/>
+      <c r="J231" s="129"/>
+      <c r="K231" s="129"/>
+      <c r="L231" s="129"/>
+      <c r="M231" s="129"/>
+    </row>
+    <row r="232" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C232" s="250" t="s">
+        <v>184</v>
+      </c>
+      <c r="D232" s="250"/>
+      <c r="E232" s="246" t="s">
+        <v>598</v>
+      </c>
+      <c r="F232" s="246"/>
+      <c r="G232" s="246"/>
+      <c r="H232" s="246"/>
+      <c r="I232" s="246"/>
+      <c r="J232" s="246"/>
+      <c r="K232" s="246"/>
+      <c r="L232" s="246"/>
+      <c r="M232" s="246"/>
+    </row>
+    <row r="233" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C233" s="250" t="s">
+        <v>200</v>
+      </c>
+      <c r="D233" s="250"/>
+      <c r="E233" s="131" t="s">
+        <v>599</v>
+      </c>
+      <c r="F233" s="131"/>
+      <c r="G233" s="131"/>
+      <c r="H233" s="247" t="s">
+        <v>600</v>
+      </c>
+      <c r="I233" s="247"/>
+      <c r="J233" s="247"/>
+      <c r="K233" s="248" t="s">
+        <v>601</v>
+      </c>
+      <c r="L233" s="248"/>
+      <c r="M233" s="248"/>
+    </row>
+    <row r="234" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C234" s="250" t="s">
+        <v>208</v>
+      </c>
+      <c r="D234" s="250"/>
+      <c r="E234" s="247" t="s">
+        <v>600</v>
+      </c>
+      <c r="F234" s="247"/>
+      <c r="G234" s="247"/>
+      <c r="H234" s="248" t="s">
+        <v>601</v>
+      </c>
+      <c r="I234" s="248"/>
+      <c r="J234" s="248"/>
+      <c r="K234" s="249" t="s">
+        <v>602</v>
+      </c>
+      <c r="L234" s="249"/>
+      <c r="M234" s="249"/>
+    </row>
+    <row r="236" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B236" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C236" s="125" t="s">
+        <v>604</v>
+      </c>
+      <c r="D236" s="125"/>
+      <c r="E236" s="125"/>
+      <c r="F236" s="125"/>
+      <c r="G236" s="125"/>
+      <c r="H236" s="125"/>
+      <c r="I236" s="125"/>
+      <c r="J236" s="125"/>
+      <c r="K236" s="125"/>
+      <c r="L236" s="125"/>
+      <c r="M236" s="125"/>
+      <c r="N236" s="125"/>
+      <c r="O236" s="125"/>
+      <c r="P236" s="125"/>
+      <c r="Q236" s="125"/>
+      <c r="R236" s="125"/>
+      <c r="S236" s="125"/>
+      <c r="T236" s="125"/>
+    </row>
+    <row r="237" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="C237" s="125"/>
+      <c r="D237" s="125"/>
+      <c r="E237" s="125"/>
+      <c r="F237" s="125"/>
+      <c r="G237" s="125"/>
+      <c r="H237" s="125"/>
+      <c r="I237" s="125"/>
+      <c r="J237" s="125"/>
+      <c r="K237" s="125"/>
+      <c r="L237" s="125"/>
+      <c r="M237" s="125"/>
+      <c r="N237" s="125"/>
+      <c r="O237" s="125"/>
+      <c r="P237" s="125"/>
+      <c r="Q237" s="125"/>
+      <c r="R237" s="125"/>
+      <c r="S237" s="125"/>
+      <c r="T237" s="125"/>
+    </row>
+    <row r="239" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B239" s="175" t="s">
+        <v>605</v>
+      </c>
+      <c r="C239" s="175"/>
+      <c r="D239" s="175"/>
+      <c r="E239" s="175"/>
+    </row>
+    <row r="240" spans="2:20" x14ac:dyDescent="0.5">
+      <c r="B240" s="175"/>
+      <c r="C240" s="175"/>
+      <c r="D240" s="175"/>
+      <c r="E240" s="175"/>
     </row>
   </sheetData>
-  <mergeCells count="116">
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="F170:K170"/>
-    <mergeCell ref="F169:K169"/>
-    <mergeCell ref="F168:K168"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="F166:M166"/>
-    <mergeCell ref="F167:K167"/>
-    <mergeCell ref="D164:T164"/>
-    <mergeCell ref="C158:T158"/>
-    <mergeCell ref="C159:T159"/>
-    <mergeCell ref="C160:T161"/>
-    <mergeCell ref="C162:T162"/>
-    <mergeCell ref="C154:T154"/>
-    <mergeCell ref="C155:T155"/>
-    <mergeCell ref="C152:T153"/>
-    <mergeCell ref="C157:T157"/>
-    <mergeCell ref="C143:T146"/>
+  <mergeCells count="166">
+    <mergeCell ref="C236:T237"/>
+    <mergeCell ref="B239:E240"/>
+    <mergeCell ref="C234:D234"/>
+    <mergeCell ref="E234:G234"/>
+    <mergeCell ref="H234:J234"/>
+    <mergeCell ref="K234:M234"/>
+    <mergeCell ref="E231:M231"/>
+    <mergeCell ref="F207:M207"/>
+    <mergeCell ref="H233:J233"/>
+    <mergeCell ref="K233:M233"/>
+    <mergeCell ref="E233:G233"/>
+    <mergeCell ref="E232:M232"/>
+    <mergeCell ref="C231:D231"/>
+    <mergeCell ref="C232:D232"/>
+    <mergeCell ref="C233:D233"/>
+    <mergeCell ref="C167:T167"/>
+    <mergeCell ref="C165:T166"/>
+    <mergeCell ref="C164:T164"/>
+    <mergeCell ref="C163:T163"/>
+    <mergeCell ref="D22:T23"/>
+    <mergeCell ref="D177:T177"/>
+    <mergeCell ref="D178:T180"/>
+    <mergeCell ref="C80:J80"/>
+    <mergeCell ref="B89:E90"/>
+    <mergeCell ref="C117:T117"/>
+    <mergeCell ref="C118:T118"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="C120:T120"/>
+    <mergeCell ref="C71:J71"/>
+    <mergeCell ref="C72:J72"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B1:H2"/>
+    <mergeCell ref="B4:E5"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="C143:T143"/>
+    <mergeCell ref="B124:E126"/>
+    <mergeCell ref="C121:T121"/>
+    <mergeCell ref="C74:J74"/>
+    <mergeCell ref="C75:J75"/>
+    <mergeCell ref="C76:J76"/>
+    <mergeCell ref="C70:J70"/>
+    <mergeCell ref="K70:S70"/>
+    <mergeCell ref="C73:J73"/>
+    <mergeCell ref="K80:S80"/>
+    <mergeCell ref="C81:J81"/>
+    <mergeCell ref="C82:J82"/>
+    <mergeCell ref="C83:J83"/>
+    <mergeCell ref="C84:J84"/>
+    <mergeCell ref="C85:J85"/>
+    <mergeCell ref="C86:J86"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="D54:T55"/>
+    <mergeCell ref="B54:C55"/>
+    <mergeCell ref="D44:T46"/>
+    <mergeCell ref="B44:C46"/>
+    <mergeCell ref="C57:T57"/>
+    <mergeCell ref="B59:C60"/>
+    <mergeCell ref="D59:T60"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:T8"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="D10:T11"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="C19:T20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B25:C27"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D33:T34"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="C145:T145"/>
+    <mergeCell ref="L139:O139"/>
+    <mergeCell ref="L140:O140"/>
+    <mergeCell ref="L141:O141"/>
     <mergeCell ref="C147:T147"/>
-    <mergeCell ref="C148:T148"/>
-    <mergeCell ref="C149:T149"/>
-    <mergeCell ref="C151:T151"/>
-    <mergeCell ref="C140:T140"/>
-    <mergeCell ref="L134:O134"/>
-    <mergeCell ref="L135:O135"/>
-    <mergeCell ref="L136:O136"/>
-    <mergeCell ref="C142:T142"/>
-    <mergeCell ref="C117:T117"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="C122:T122"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="C116:T116"/>
+    <mergeCell ref="C103:T103"/>
+    <mergeCell ref="C104:T104"/>
+    <mergeCell ref="C105:T105"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="C102:T102"/>
     <mergeCell ref="C111:T111"/>
-    <mergeCell ref="C98:T98"/>
-    <mergeCell ref="C99:T99"/>
-    <mergeCell ref="C100:T100"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="C97:T97"/>
     <mergeCell ref="C106:T106"/>
-    <mergeCell ref="C101:T101"/>
-    <mergeCell ref="C102:T104"/>
-    <mergeCell ref="C107:T107"/>
-    <mergeCell ref="C108:T108"/>
-    <mergeCell ref="C109:T109"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B20:C22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D28:T29"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:T3"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:T6"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D17:T18"/>
-    <mergeCell ref="C14:T15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D49:T50"/>
-    <mergeCell ref="B49:C50"/>
-    <mergeCell ref="D39:T41"/>
-    <mergeCell ref="B39:C41"/>
-    <mergeCell ref="C52:T52"/>
-    <mergeCell ref="B54:C55"/>
-    <mergeCell ref="D54:T55"/>
-    <mergeCell ref="C115:T115"/>
-    <mergeCell ref="C66:J66"/>
-    <mergeCell ref="C67:J67"/>
-    <mergeCell ref="D59:G59"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="C138:T138"/>
-    <mergeCell ref="B119:E121"/>
-    <mergeCell ref="D172:T172"/>
-    <mergeCell ref="D173:T175"/>
-    <mergeCell ref="C116:T116"/>
-    <mergeCell ref="C69:J69"/>
-    <mergeCell ref="C70:J70"/>
-    <mergeCell ref="C71:J71"/>
-    <mergeCell ref="C65:J65"/>
-    <mergeCell ref="K65:S65"/>
-    <mergeCell ref="C68:J68"/>
-    <mergeCell ref="K75:S75"/>
-    <mergeCell ref="C76:J76"/>
-    <mergeCell ref="C77:J77"/>
-    <mergeCell ref="C78:J78"/>
-    <mergeCell ref="C79:J79"/>
-    <mergeCell ref="C80:J80"/>
-    <mergeCell ref="C81:J81"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="C75:J75"/>
-    <mergeCell ref="B84:E85"/>
+    <mergeCell ref="C107:T109"/>
     <mergeCell ref="C112:T112"/>
     <mergeCell ref="C113:T113"/>
     <mergeCell ref="C114:T114"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="C159:T159"/>
+    <mergeCell ref="C160:T160"/>
+    <mergeCell ref="C157:T158"/>
+    <mergeCell ref="C162:T162"/>
+    <mergeCell ref="C148:T151"/>
+    <mergeCell ref="C152:T152"/>
+    <mergeCell ref="C153:T153"/>
+    <mergeCell ref="C154:T154"/>
+    <mergeCell ref="C156:T156"/>
+    <mergeCell ref="D206:E206"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="F175:K175"/>
+    <mergeCell ref="F174:K174"/>
+    <mergeCell ref="F173:K173"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="F171:M171"/>
+    <mergeCell ref="F172:K172"/>
+    <mergeCell ref="D169:T169"/>
+    <mergeCell ref="C201:J201"/>
+    <mergeCell ref="B183:E184"/>
+    <mergeCell ref="D186:T187"/>
+    <mergeCell ref="D188:T188"/>
+    <mergeCell ref="B186:C186"/>
+    <mergeCell ref="C197:T197"/>
+    <mergeCell ref="C198:T198"/>
+    <mergeCell ref="K200:M200"/>
+    <mergeCell ref="K202:M202"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="D191:E191"/>
+    <mergeCell ref="D192:E192"/>
+    <mergeCell ref="D193:E193"/>
+    <mergeCell ref="D194:E194"/>
+    <mergeCell ref="B205:D205"/>
+    <mergeCell ref="F206:M206"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="H208:J208"/>
+    <mergeCell ref="K208:M208"/>
+    <mergeCell ref="L209:M209"/>
+    <mergeCell ref="I209:K209"/>
+    <mergeCell ref="F209:H209"/>
+    <mergeCell ref="F226:T228"/>
+    <mergeCell ref="C211:T212"/>
+    <mergeCell ref="C214:T216"/>
+    <mergeCell ref="C218:T220"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="G222:T222"/>
+    <mergeCell ref="D207:E207"/>
+    <mergeCell ref="D208:E208"/>
+    <mergeCell ref="D209:E209"/>
+    <mergeCell ref="B230:D230"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>